--- a/pharma.xlsx
+++ b/pharma.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E251"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,7 +410,7 @@
         <v>code_postal</v>
       </c>
       <c r="D1" t="str">
-        <v xml:space="preserve">ville </v>
+        <v>ville</v>
       </c>
       <c r="E1" t="str">
         <v>pays</v>
@@ -418,16 +418,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Grande Pharmacie De Roche-la-molière</v>
+        <v>Pharmacie De L'abbaye</v>
       </c>
       <c r="B2" t="str">
-        <v>6 Impasse Jean Bouin</v>
+        <v>66Bis Avenue Jeanne D'Arc</v>
       </c>
       <c r="C2" t="str">
-        <v>42230</v>
+        <v>38100</v>
       </c>
       <c r="D2" t="str">
-        <v>ROCHE LA MOLIERE</v>
+        <v>Grenoble</v>
       </c>
       <c r="E2" t="str">
         <v>France</v>
@@ -435,16 +435,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Pharmacie De Fay</v>
+        <v>Pharmacie De La Gare</v>
       </c>
       <c r="B3" t="str">
-        <v>6 Rue Des Maillets</v>
+        <v>74 Avenue Jean Jaures</v>
       </c>
       <c r="C3" t="str">
-        <v>45450</v>
+        <v>78500</v>
       </c>
       <c r="D3" t="str">
-        <v>Fay Aux Loges</v>
+        <v>Sartrouville</v>
       </c>
       <c r="E3" t="str">
         <v>France</v>
@@ -452,16 +452,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Pharmacie De Maupertuis</v>
+        <v>Pharmacie De La Gare</v>
       </c>
       <c r="B4" t="str">
-        <v>37 Avenue Bollee</v>
+        <v>11 Avenue Roger Salengro</v>
       </c>
       <c r="C4" t="str">
-        <v>72000</v>
+        <v>89400</v>
       </c>
       <c r="D4" t="str">
-        <v>Le Mans</v>
+        <v>Migennes</v>
       </c>
       <c r="E4" t="str">
         <v>France</v>
@@ -469,16 +469,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pharmacie Oddo</v>
+        <v>Pharmacie Farines</v>
       </c>
       <c r="B5" t="str">
-        <v>79 Boulevard Oddo</v>
+        <v>6 Avenue Du Mas Deu</v>
       </c>
       <c r="C5" t="str">
-        <v>13015</v>
+        <v>66300</v>
       </c>
       <c r="D5" t="str">
-        <v>MARSEILLE</v>
+        <v>TROUILLAS</v>
       </c>
       <c r="E5" t="str">
         <v>France</v>
@@ -486,16 +486,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Pharmacie De Mouroux</v>
+        <v>Pharmacie Duhaut Espace Santé</v>
       </c>
       <c r="B6" t="str">
-        <v>331 Av Du General De Gaulle</v>
+        <v>9 R Marechal Lattre De Tassigny</v>
       </c>
       <c r="C6" t="str">
-        <v>77120</v>
+        <v>88230</v>
       </c>
       <c r="D6" t="str">
-        <v>Mouroux</v>
+        <v>FRAIZE</v>
       </c>
       <c r="E6" t="str">
         <v>France</v>
@@ -503,16 +503,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pharmacie De La Gare</v>
+        <v>Pharmacie Du Centre</v>
       </c>
       <c r="B7" t="str">
-        <v>54 Rue Jacquemart</v>
+        <v>29 Rue De Paris</v>
       </c>
       <c r="C7" t="str">
-        <v>26100</v>
+        <v>78520</v>
       </c>
       <c r="D7" t="str">
-        <v>ROMANS SUR ISERE</v>
+        <v>Limay</v>
       </c>
       <c r="E7" t="str">
         <v>France</v>
@@ -520,16 +520,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Pharmacie Fourie</v>
+        <v>Pharmacie Royale</v>
       </c>
       <c r="B8" t="str">
-        <v>RUE DE L AUBEPIN</v>
+        <v>2Ter Rue Royale</v>
       </c>
       <c r="C8" t="str">
-        <v>30540</v>
+        <v>92210</v>
       </c>
       <c r="D8" t="str">
-        <v>Milhaud</v>
+        <v>St Cloud</v>
       </c>
       <c r="E8" t="str">
         <v>France</v>
@@ -537,16 +537,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Pharmacie Centrale</v>
+        <v>Pharmacie De Realpanier</v>
       </c>
       <c r="B9" t="str">
-        <v>Place De La Mairie</v>
+        <v>161 Rue Jean Gasset</v>
       </c>
       <c r="C9" t="str">
-        <v>31350</v>
+        <v>84130</v>
       </c>
       <c r="D9" t="str">
-        <v>BOULOGNE SUR GESSE</v>
+        <v>LE PONTET</v>
       </c>
       <c r="E9" t="str">
         <v>France</v>
@@ -554,16 +554,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Pharmacie Péroise</v>
+        <v>Pharmacie Saint Simeon</v>
       </c>
       <c r="B10" t="str">
-        <v>12 Rue De L Hotel De Ville</v>
+        <v>111 Boulevard De Metzingen</v>
       </c>
       <c r="C10" t="str">
-        <v>85540</v>
+        <v>60400</v>
       </c>
       <c r="D10" t="str">
-        <v>Le Champ St Pere</v>
+        <v>Noyon</v>
       </c>
       <c r="E10" t="str">
         <v>France</v>
@@ -571,16 +571,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Pharmacie Vinay Champ De Mars</v>
+        <v>Pharmacie Snc L.o Bonichon</v>
       </c>
       <c r="B11" t="str">
-        <v>13 RUE DU 8 MAI 1945</v>
+        <v>Av. d'Aquitaine</v>
       </c>
       <c r="C11" t="str">
-        <v>38470</v>
+        <v>24490</v>
       </c>
       <c r="D11" t="str">
-        <v>VINAY</v>
+        <v>La Roche Chalais</v>
       </c>
       <c r="E11" t="str">
         <v>France</v>
@@ -588,16 +588,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Pharmacie Nouvelle</v>
+        <v>Pharmacie De La Place Du 14 Juillet</v>
       </c>
       <c r="B12" t="str">
-        <v>7 Rue Amedee VIII De Savoie</v>
+        <v>2 Place Du 14 Juillet</v>
       </c>
       <c r="C12" t="str">
-        <v>74160</v>
+        <v>33130</v>
       </c>
       <c r="D12" t="str">
-        <v>ST JULIEN EN GENEVOIS</v>
+        <v>BEGLES</v>
       </c>
       <c r="E12" t="str">
         <v>France</v>
@@ -605,16 +605,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Pharmacie Du Martroi</v>
+        <v>Pharmacie De La Croix Blanche</v>
       </c>
       <c r="B13" t="str">
-        <v>17 Place Du Martroi</v>
+        <v>41 Avenue Amedee Mercier</v>
       </c>
       <c r="C13" t="str">
-        <v>45190</v>
+        <v>01000</v>
       </c>
       <c r="D13" t="str">
-        <v>Beaugency</v>
+        <v>Bourg En Bresse</v>
       </c>
       <c r="E13" t="str">
         <v>France</v>
@@ -622,16 +622,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Pharmacie du Château</v>
+        <v>Pharmacie De Brienne</v>
       </c>
       <c r="B14" t="str">
-        <v>2 Rue De L Hotel De Ville</v>
+        <v>53 Allee De Brienne</v>
       </c>
       <c r="C14" t="str">
-        <v>72150</v>
+        <v>31000</v>
       </c>
       <c r="D14" t="str">
-        <v>Le Grand Luce</v>
+        <v>TOULOUSE</v>
       </c>
       <c r="E14" t="str">
         <v>France</v>
@@ -639,16 +639,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Pharmacie Lagerge</v>
+        <v>Pharmacie Du Théâtre</v>
       </c>
       <c r="B15" t="str">
-        <v>2 Rue Alphonse Daudet</v>
+        <v>18 Ave Pasteur</v>
       </c>
       <c r="C15" t="str">
-        <v>7120</v>
+        <v>10400</v>
       </c>
       <c r="D15" t="str">
-        <v>Ruoms</v>
+        <v>Nogent Sur Seine</v>
       </c>
       <c r="E15" t="str">
         <v>France</v>
@@ -656,16 +656,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Pharmacie Du Parc</v>
+        <v>Pharmacie Laur</v>
       </c>
       <c r="B16" t="str">
-        <v>2 Avenue Du Minervois</v>
+        <v xml:space="preserve">16 Rue Des Carmes </v>
       </c>
       <c r="C16" t="str">
-        <v>11700</v>
+        <v>24100</v>
       </c>
       <c r="D16" t="str">
-        <v>LA REDORTE</v>
+        <v>Bergerac</v>
       </c>
       <c r="E16" t="str">
         <v>France</v>
@@ -673,16 +673,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Pharmacie Voltaire</v>
+        <v>Pharmacie Raynaud Puech</v>
       </c>
       <c r="B17" t="str">
-        <v>2 Place Des Arts</v>
+        <v>28 Rue Louis Rouvier</v>
       </c>
       <c r="C17" t="str">
-        <v>74200</v>
+        <v>34420</v>
       </c>
       <c r="D17" t="str">
-        <v>THONON LES BAINS</v>
+        <v>VILLENEUVE LES BEZIERS</v>
       </c>
       <c r="E17" t="str">
         <v>France</v>
@@ -690,16 +690,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Pharmacie Du Vaudreuil</v>
+        <v>Pharmacie Satger Apack</v>
       </c>
       <c r="B18" t="str">
-        <v>5 Place Du General De Gaulle</v>
+        <v>Avenue De La Ramadone</v>
       </c>
       <c r="C18" t="str">
-        <v>27100</v>
+        <v>84870</v>
       </c>
       <c r="D18" t="str">
-        <v>Le Vaudreuil</v>
+        <v>LORIOL DU COMTAT</v>
       </c>
       <c r="E18" t="str">
         <v>France</v>
@@ -707,16 +707,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Pharmacie Des Vignerons</v>
+        <v>Grande Pharmacie De Couëron</v>
       </c>
       <c r="B19" t="str">
-        <v>2 Rue Du Marechal Maunoury</v>
+        <v>14 Boulevard De La Liberation</v>
       </c>
       <c r="C19" t="str">
-        <v>94300</v>
+        <v>44220</v>
       </c>
       <c r="D19" t="str">
-        <v>Vincennes</v>
+        <v>Coueron</v>
       </c>
       <c r="E19" t="str">
         <v>France</v>
@@ -724,16 +724,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Pharmacie.F</v>
+        <v>Pharmacie du Jasmin</v>
       </c>
       <c r="B20" t="str">
-        <v>141 Avenue de France</v>
+        <v>59 Rue Haute Saint Paterne</v>
       </c>
       <c r="C20" t="str">
-        <v>75013</v>
+        <v>36100</v>
       </c>
       <c r="D20" t="str">
-        <v>Paris</v>
+        <v>Issoudun</v>
       </c>
       <c r="E20" t="str">
         <v>France</v>
@@ -741,16 +741,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Pharmacie Pineau Caroline</v>
+        <v>Pharmacie Du Village</v>
       </c>
       <c r="B21" t="str">
-        <v>Place De La Mairie</v>
+        <v>48 Rue De Paris</v>
       </c>
       <c r="C21" t="str">
-        <v>46240</v>
+        <v>91090</v>
       </c>
       <c r="D21" t="str">
-        <v>LABASTIDE MURAT</v>
+        <v>Lisses</v>
       </c>
       <c r="E21" t="str">
         <v>France</v>
@@ -758,16 +758,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Pharmacie Val D Auron</v>
+        <v>Pharmacie Lafayette Du Centre</v>
       </c>
       <c r="B22" t="str">
-        <v>Rue Raymond Boisde</v>
+        <v>10 Place Du Square</v>
       </c>
       <c r="C22" t="str">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="D22" t="str">
-        <v>Bourges</v>
+        <v>AURILLAC</v>
       </c>
       <c r="E22" t="str">
         <v>France</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Pharmacie Du Progrès La Fraîcheur</v>
+        <v>Pharmacie Centrale</v>
       </c>
       <c r="B23" t="str">
-        <v>54-46 Avenue Pierre Verdier</v>
+        <v>37 Rue Du General De Gaulle</v>
       </c>
       <c r="C23" t="str">
-        <v>34500</v>
+        <v>78120</v>
       </c>
       <c r="D23" t="str">
-        <v>Béziers</v>
+        <v>Rambouillet</v>
       </c>
       <c r="E23" t="str">
         <v>France</v>
@@ -792,16 +792,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Pharmacie Centrale</v>
+        <v>Pharmacie Des Ors</v>
       </c>
       <c r="B24" t="str">
-        <v>2 Grande Rue</v>
+        <v>Rue De Straubing</v>
       </c>
       <c r="C24" t="str">
-        <v>18270</v>
+        <v>26100</v>
       </c>
       <c r="D24" t="str">
-        <v>CULAN</v>
+        <v>ROMANS SUR ISERE</v>
       </c>
       <c r="E24" t="str">
         <v>France</v>
@@ -809,16 +809,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Pharmacie Du Soleil Rocade</v>
+        <v>Pharmacie Des Platanes</v>
       </c>
       <c r="B25" t="str">
-        <v>115 Boulevard Camille Blanc - Rond Point De L'Europe</v>
+        <v>44 bis av Général de Gaulle</v>
       </c>
       <c r="C25" t="str">
-        <v>34200</v>
+        <v>26130</v>
       </c>
       <c r="D25" t="str">
-        <v>SETE</v>
+        <v>ST PAUL TROIS CHATEAUX</v>
       </c>
       <c r="E25" t="str">
         <v>France</v>
@@ -826,16 +826,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Pharmacie Grand Soleil</v>
+        <v>Pharmacie De La Foret</v>
       </c>
       <c r="B26" t="str">
-        <v>Route Nationale 7</v>
+        <v>79 Avenue De La Foret</v>
       </c>
       <c r="C26" t="str">
-        <v>13670</v>
+        <v>36330</v>
       </c>
       <c r="D26" t="str">
-        <v>ST ANDIOL</v>
+        <v>Le Poinconnet</v>
       </c>
       <c r="E26" t="str">
         <v>France</v>
@@ -843,16 +843,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Pharmacie De La Vallee</v>
+        <v>Pharmacie Sorbette</v>
       </c>
       <c r="B27" t="str">
-        <v>55 Rue De La Vallee</v>
+        <v>135 Grande Rue Saint Michel</v>
       </c>
       <c r="C27" t="str">
-        <v>76600</v>
+        <v>31400</v>
       </c>
       <c r="D27" t="str">
-        <v>Le Havre</v>
+        <v>TOULOUSE</v>
       </c>
       <c r="E27" t="str">
         <v>France</v>
@@ -860,16 +860,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Pharmacie Froidevaux</v>
+        <v>Pharmacie De St Georges De Reinens</v>
       </c>
       <c r="B28" t="str">
-        <v>Place Du Soleil</v>
+        <v>161 Avenue Charles De Gaulle</v>
       </c>
       <c r="C28" t="str">
-        <v>91230</v>
+        <v>69830</v>
       </c>
       <c r="D28" t="str">
-        <v>Montgeron</v>
+        <v>St Georges De Reneins</v>
       </c>
       <c r="E28" t="str">
         <v>France</v>
@@ -877,16 +877,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pharmacie Le Bigot</v>
+        <v>Pharmacie Des Cotes Fleuries</v>
       </c>
       <c r="B29" t="str">
-        <v>Residence Revinco</v>
+        <v xml:space="preserve">67 BD MAURICE POURCHON </v>
       </c>
       <c r="C29" t="str">
-        <v>20290</v>
+        <v>63100</v>
       </c>
       <c r="D29" t="str">
-        <v>Borgo</v>
+        <v>Clermont Ferrand</v>
       </c>
       <c r="E29" t="str">
         <v>France</v>
@@ -894,16 +894,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Pharmacie de Saint Nazaire</v>
+        <v>Pharmacie Peilleron</v>
       </c>
       <c r="B30" t="str">
-        <v>830 Route Nationale 90</v>
+        <v>8 Rue Du Commerce</v>
       </c>
       <c r="C30" t="str">
-        <v>38330</v>
+        <v>10120</v>
       </c>
       <c r="D30" t="str">
-        <v>ST NAZAIRE LES EYMES</v>
+        <v>St Germain</v>
       </c>
       <c r="E30" t="str">
         <v>France</v>
@@ -911,16 +911,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Pharmacie Du Pays Tourrettan</v>
+        <v>Pharmacie De La Croix Blanche</v>
       </c>
       <c r="B31" t="str">
-        <v>Quartier Tassy</v>
+        <v>41 Avenue Amedee Mercier</v>
       </c>
       <c r="C31" t="str">
-        <v>83440</v>
+        <v>01000</v>
       </c>
       <c r="D31" t="str">
-        <v>Tourrettes</v>
+        <v>Bourg En Bresse</v>
       </c>
       <c r="E31" t="str">
         <v>France</v>
@@ -928,33 +928,33 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Pharmacie Des Jacarandas</v>
+        <v>Pharmacie Tolosane</v>
       </c>
       <c r="B32" t="str">
-        <v>28 r Roland Garros Bois Nèfles  Bois de Nefles St Paul</v>
+        <v>20 Avenue Tolosane</v>
       </c>
       <c r="C32" t="str">
-        <v>97411</v>
+        <v>31520</v>
       </c>
       <c r="D32" t="str">
-        <v>Saint Paul</v>
+        <v>Ramonville St Agne</v>
       </c>
       <c r="E32" t="str">
-        <v>La Réunion</v>
+        <v>France</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Pharmacie Du Gatinais</v>
+        <v>Pharmacie D Astaffort</v>
       </c>
       <c r="B33" t="str">
-        <v>41 Rue De La Republique</v>
+        <v>16 Place Andre Routier</v>
       </c>
       <c r="C33" t="str">
-        <v>89150</v>
+        <v>47220</v>
       </c>
       <c r="D33" t="str">
-        <v>St Valerien</v>
+        <v>ASTAFFORT</v>
       </c>
       <c r="E33" t="str">
         <v>France</v>
@@ -962,16 +962,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Pharmacie Monjardet</v>
+        <v>Pharmacie Du Clos</v>
       </c>
       <c r="B34" t="str">
-        <v>5 Rue De L Eglise</v>
+        <v>18 Rue Jules Ferry</v>
       </c>
       <c r="C34" t="str">
-        <v>45460</v>
+        <v>13220</v>
       </c>
       <c r="D34" t="str">
-        <v>Les Bordes</v>
+        <v>CHATEAUNEUF LES MARTIGUES</v>
       </c>
       <c r="E34" t="str">
         <v>France</v>
@@ -979,16 +979,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Pharmacie Cathare</v>
+        <v>Pharmacie Du Theatre</v>
       </c>
       <c r="B35" t="str">
-        <v>1 PL DE LA REPUBLIQUE</v>
+        <v>13 Avenue Du General De Gaulle</v>
       </c>
       <c r="C35" t="str">
-        <v>9300</v>
+        <v>91160</v>
       </c>
       <c r="D35" t="str">
-        <v>Lavelanet</v>
+        <v>Longjumeau</v>
       </c>
       <c r="E35" t="str">
         <v>France</v>
@@ -996,16 +996,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Pharmacie Lenglet</v>
+        <v>Pharmacie De La Concorde</v>
       </c>
       <c r="B36" t="str">
-        <v>17 ter route Nationale</v>
+        <v>18 Rue Paul Vaillant Couturier</v>
       </c>
       <c r="C36" t="str">
-        <v>45130</v>
+        <v>92230</v>
       </c>
       <c r="D36" t="str">
-        <v>St Ay</v>
+        <v>Gennevilliers</v>
       </c>
       <c r="E36" t="str">
         <v>France</v>
@@ -1013,16 +1013,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Pharmacie De L'Aigle</v>
+        <v>Pharmacie Ker'Ys</v>
       </c>
       <c r="B37" t="str">
-        <v>26 Place D'Arme</v>
+        <v>ZONE D'AMENAGEMENT CONCERTE DE TOUBALAN</v>
       </c>
       <c r="C37" t="str">
-        <v>57370</v>
+        <v>29100</v>
       </c>
       <c r="D37" t="str">
-        <v>PHALBOURG</v>
+        <v>DOUARNENEZ</v>
       </c>
       <c r="E37" t="str">
         <v>France</v>
@@ -1030,16 +1030,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Pharmacie Depland</v>
+        <v>Pharmacie Le Coënt</v>
       </c>
       <c r="B38" t="str">
-        <v>60 Chemin De La Garenne</v>
+        <v xml:space="preserve">Zone De Lan Oge - Route De St Brieuc </v>
       </c>
       <c r="C38" t="str">
-        <v>91290</v>
+        <v>22110</v>
       </c>
       <c r="D38" t="str">
-        <v>La Norville</v>
+        <v>Rostrenen</v>
       </c>
       <c r="E38" t="str">
         <v>France</v>
@@ -1047,16 +1047,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Pharmacie Moreau</v>
+        <v>Grande Pharmacie D'angoulême Anciennement "Pharmacie Des Halles"</v>
       </c>
       <c r="B39" t="str">
-        <v>115 Boulevard De La Croix Rousse</v>
+        <v>86 Rue Hergé</v>
       </c>
       <c r="C39" t="str">
-        <v>69004</v>
+        <v>16000</v>
       </c>
       <c r="D39" t="str">
-        <v>Lyon</v>
+        <v>Angoulême</v>
       </c>
       <c r="E39" t="str">
         <v>France</v>
@@ -1064,16 +1064,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Pharmacie De Saint-privat</v>
+        <v>Pharmacie De La Palle</v>
       </c>
       <c r="B40" t="str">
-        <v>4 bis place du marché aux cerises</v>
+        <v>37 Boulevard De La Palle</v>
       </c>
       <c r="C40" t="str">
-        <v>7200</v>
+        <v>42100</v>
       </c>
       <c r="D40" t="str">
-        <v>Saint-privat</v>
+        <v>ST ETIENNE</v>
       </c>
       <c r="E40" t="str">
         <v>France</v>
@@ -1081,16 +1081,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Pharmacie De La Soule</v>
+        <v>Pharmacie Du Pont De Tours</v>
       </c>
       <c r="B41" t="str">
-        <v>35 Boulevard Des Pyrenees</v>
+        <v>42 Rue Charles Beauhaire</v>
       </c>
       <c r="C41" t="str">
-        <v>64130</v>
+        <v>45140</v>
       </c>
       <c r="D41" t="str">
-        <v>Mauleon Licharre</v>
+        <v>Saint-Jean-de-la-Ruelle</v>
       </c>
       <c r="E41" t="str">
         <v>France</v>
@@ -1098,16 +1098,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Pharmacie De Brive-Ouest</v>
+        <v>La Grande Pharmacie Des 3 Graces</v>
       </c>
       <c r="B42" t="str">
-        <v>29 Rue Philibert Lalande</v>
+        <v>12 rue de Bourgogne</v>
       </c>
       <c r="C42" t="str">
-        <v>19100</v>
+        <v>42300</v>
       </c>
       <c r="D42" t="str">
-        <v>BRIVE LA GAILLARDE</v>
+        <v>ROANNE</v>
       </c>
       <c r="E42" t="str">
         <v>France</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Pharmacie Henri Iv</v>
+        <v>Pharmacie De La Badiane</v>
       </c>
       <c r="B43" t="str">
-        <v>23 Boulevard Henri Iv</v>
+        <v>32 Rue De Kingersheim</v>
       </c>
       <c r="C43" t="str">
-        <v>65000</v>
+        <v>68120</v>
       </c>
       <c r="D43" t="str">
-        <v>TARBES</v>
+        <v>Pfastatt</v>
       </c>
       <c r="E43" t="str">
         <v>France</v>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Pharmacie Pasdeloup</v>
+        <v>Pharmacie Milliet Sens</v>
       </c>
       <c r="B44" t="str">
-        <v>6 Avenue Gabriel Dordain</v>
+        <v>Place Estelette</v>
       </c>
       <c r="C44" t="str">
-        <v>18400</v>
+        <v>65230</v>
       </c>
       <c r="D44" t="str">
-        <v>St Florent Sur Cher</v>
+        <v>CASTELNAU MAGNOAC</v>
       </c>
       <c r="E44" t="str">
         <v>France</v>
@@ -1149,16 +1149,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pharmacie Mendes</v>
+        <v>Grande Pharmacie Regionale Kuypers</v>
       </c>
       <c r="B45" t="str">
-        <v>45 Rue Georges Clemenceau</v>
+        <v>13 Rue Porte De Sologne</v>
       </c>
       <c r="C45" t="str">
-        <v>85770</v>
+        <v>45600</v>
       </c>
       <c r="D45" t="str">
-        <v>Vix</v>
+        <v>Sully Sur Loire</v>
       </c>
       <c r="E45" t="str">
         <v>France</v>
@@ -1166,16 +1166,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Pharmacie Du Carreau</v>
+        <v>Grande Pharmacie D'angoulême Anciennement "Pharmacie Des Halles"</v>
       </c>
       <c r="B46" t="str">
-        <v>6 Av. de les Indis</v>
+        <v>86 Rue Hergé</v>
       </c>
       <c r="C46" t="str">
-        <v>66150</v>
+        <v>16000</v>
       </c>
       <c r="D46" t="str">
-        <v>Arles Sur Tech</v>
+        <v>Angoulême</v>
       </c>
       <c r="E46" t="str">
         <v>France</v>
@@ -1183,16 +1183,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Pharmacie Saint Gilles</v>
+        <v>Pharmacie De Saint Montan</v>
       </c>
       <c r="B47" t="str">
-        <v>3 Residence Saint Gilles</v>
+        <v>Quartier Bauvache</v>
       </c>
       <c r="C47" t="str">
-        <v>28130</v>
+        <v>07220</v>
       </c>
       <c r="D47" t="str">
-        <v>Pierres</v>
+        <v>ST MONTAN</v>
       </c>
       <c r="E47" t="str">
         <v>France</v>
@@ -1200,16 +1200,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Pharmacie De L'industrie</v>
+        <v>Pharmacie Anserienne</v>
       </c>
       <c r="B48" t="str">
-        <v>9 BD SANTOS DUMONT</v>
+        <v>65 Route Nationale</v>
       </c>
       <c r="C48" t="str">
-        <v>18000</v>
+        <v>62215</v>
       </c>
       <c r="D48" t="str">
-        <v>Bourges</v>
+        <v>OYE PLAGE</v>
       </c>
       <c r="E48" t="str">
         <v>France</v>
@@ -1217,16 +1217,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Pharmacie De La Mairie</v>
+        <v>Pharmacie Galgon</v>
       </c>
       <c r="B49" t="str">
-        <v>92 Grande Rue Charles De Gaulle</v>
+        <v>1 Avenue Fernand Pillot</v>
       </c>
       <c r="C49" t="str">
-        <v>91250</v>
+        <v>33133</v>
       </c>
       <c r="D49" t="str">
-        <v>SAINTRY SUR SEINE</v>
+        <v>GALGON</v>
       </c>
       <c r="E49" t="str">
         <v>France</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Pharmacie De L'hôtel De Ville</v>
+        <v>Pharmacie Du Martroi</v>
       </c>
       <c r="B50" t="str">
-        <v>60 Avenue De L Hotel De Ville</v>
+        <v>41 Place Du Martroi</v>
       </c>
       <c r="C50" t="str">
-        <v>41600</v>
+        <v>45300</v>
       </c>
       <c r="D50" t="str">
-        <v>Lamotte Beuvron</v>
+        <v>Pithiviers</v>
       </c>
       <c r="E50" t="str">
         <v>France</v>
@@ -1251,24 +1251,3424 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Pharmacie D Artois</v>
+        <v>Pharmacie Charles</v>
       </c>
       <c r="B51" t="str">
-        <v>181 Rue D Artois</v>
+        <v>5 Rue Châlons</v>
       </c>
       <c r="C51" t="str">
-        <v>45160</v>
+        <v>51260</v>
       </c>
       <c r="D51" t="str">
-        <v>Olivet</v>
+        <v>Anglure</v>
       </c>
       <c r="E51" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Pharmacie Rahou</v>
+      </c>
+      <c r="B52" t="str">
+        <v>15 Rue De Saint Nazaire</v>
+      </c>
+      <c r="C52" t="str">
+        <v>44800</v>
+      </c>
+      <c r="D52" t="str">
+        <v>St Herblain</v>
+      </c>
+      <c r="E52" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Pharmacie Bremont</v>
+      </c>
+      <c r="B53" t="str">
+        <v>163 Av. du Général de Gaulle</v>
+      </c>
+      <c r="C53" t="str">
+        <v>47300</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Villeneuve-sur-Lot</v>
+      </c>
+      <c r="E53" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Pharmacie De Noyer</v>
+      </c>
+      <c r="B54" t="str">
+        <v>388 Avenue De Thonon</v>
+      </c>
+      <c r="C54" t="str">
+        <v>74200</v>
+      </c>
+      <c r="D54" t="str">
+        <v>ALLINGES</v>
+      </c>
+      <c r="E54" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Pharmacie Dombasle</v>
+      </c>
+      <c r="B55" t="str">
+        <v>21 Carrefour De La Liberation</v>
+      </c>
+      <c r="C55" t="str">
+        <v>55120</v>
+      </c>
+      <c r="D55" t="str">
+        <v>DOMBASLE EN ARGONNE</v>
+      </c>
+      <c r="E55" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Pharmacie Cognee</v>
+      </c>
+      <c r="B56" t="str">
+        <v>3 RUE DU CHALET</v>
+      </c>
+      <c r="C56" t="str">
+        <v>49270</v>
+      </c>
+      <c r="D56" t="str">
+        <v>MONTREVAULT SUR EVRE</v>
+      </c>
+      <c r="E56" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Pharmacie Du Marché</v>
+      </c>
+      <c r="B57" t="str">
+        <v>12 Avenue Carnot</v>
+      </c>
+      <c r="C57" t="str">
+        <v>78800</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Houilles</v>
+      </c>
+      <c r="E57" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Pharmacie Michaud Gallo</v>
+      </c>
+      <c r="B58" t="str">
+        <v>79 Route Vieille, Av. Jean Rampon</v>
+      </c>
+      <c r="C58" t="str">
+        <v>30140</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Saint Jean du Pin</v>
+      </c>
+      <c r="E58" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Pharmacie Provence Dauphiné</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Avenue Du Dauphine</v>
+      </c>
+      <c r="C59" t="str">
+        <v>26270</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Saulce sur Rhône</v>
+      </c>
+      <c r="E59" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Grande Pharmacie Bel Air</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Centre Commercial Bel Air</v>
+      </c>
+      <c r="C60" t="str">
+        <v>78120</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Rambouillet</v>
+      </c>
+      <c r="E60" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Pharmacie De Paris</v>
+      </c>
+      <c r="B61" t="str">
+        <v>111 Avenue Du General De Gaulle</v>
+      </c>
+      <c r="C61" t="str">
+        <v>44500</v>
+      </c>
+      <c r="D61" t="str">
+        <v>La Baule</v>
+      </c>
+      <c r="E61" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Pharmacie Des Brouzils</v>
+      </c>
+      <c r="B62" t="str">
+        <v>8 Rue Georges Clemenceau</v>
+      </c>
+      <c r="C62" t="str">
+        <v>85260</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Les Brouzils</v>
+      </c>
+      <c r="E62" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Pharmacie Charpentier</v>
+      </c>
+      <c r="B63" t="str">
+        <v>161 Avenue Emile Zola</v>
+      </c>
+      <c r="C63" t="str">
+        <v>79100</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Sainte Verge</v>
+      </c>
+      <c r="E63" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Grande Pharmacie D'angoulême Anciennement "Pharmacie Des Halles"</v>
+      </c>
+      <c r="B64" t="str">
+        <v>86 Rue Hergé</v>
+      </c>
+      <c r="C64" t="str">
+        <v>16000</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Angoulême</v>
+      </c>
+      <c r="E64" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Pharmacie De Chaillot</v>
+      </c>
+      <c r="B65" t="str">
+        <v>118 Route De Bellon</v>
+      </c>
+      <c r="C65" t="str">
+        <v>18100</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Vierzon</v>
+      </c>
+      <c r="E65" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Pharmacie Thaumiaux</v>
+      </c>
+      <c r="B66" t="str">
+        <v>3 Avenue De La Gare</v>
+      </c>
+      <c r="C66" t="str">
+        <v>23100</v>
+      </c>
+      <c r="D66" t="str">
+        <v xml:space="preserve">La Courtine </v>
+      </c>
+      <c r="E66" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Pharmacie De St Alban</v>
+      </c>
+      <c r="B67" t="str">
+        <v>5Bis Promenade Des Magnauds</v>
+      </c>
+      <c r="C67" t="str">
+        <v>38080</v>
+      </c>
+      <c r="D67" t="str">
+        <v>ST ALBAN DE ROCHE</v>
+      </c>
+      <c r="E67" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Pharmacie Roissy 2 F Entre Ciel Et Terre</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Aeroport Charles De Gaulle</v>
+      </c>
+      <c r="C68" t="str">
+        <v>95700</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Roissy En France</v>
+      </c>
+      <c r="E68" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Pharmacie Du Plessis</v>
+      </c>
+      <c r="B69" t="str">
+        <v>140 Rue Nationale</v>
+      </c>
+      <c r="C69" t="str">
+        <v>85280</v>
+      </c>
+      <c r="D69" t="str">
+        <v>La Ferriere</v>
+      </c>
+      <c r="E69" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Pharmacie De Longueil</v>
+      </c>
+      <c r="B70" t="str">
+        <v>33 Avenue Longueil</v>
+      </c>
+      <c r="C70" t="str">
+        <v>78600</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Maisons Laffitte</v>
+      </c>
+      <c r="E70" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Action Pharma</v>
+      </c>
+      <c r="B71" t="str">
+        <v>46 Rue Raymond Laubier</v>
+      </c>
+      <c r="C71" t="str">
+        <v>91410</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Dourdan</v>
+      </c>
+      <c r="E71" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Pharmacie Issenheim</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2 RUE DES CERISIERS</v>
+      </c>
+      <c r="C72" t="str">
+        <v>68500</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Issenheim</v>
+      </c>
+      <c r="E72" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Pharmacie Bischoff</v>
+      </c>
+      <c r="B73" t="str">
+        <v>8 Rue Theodore Deck</v>
+      </c>
+      <c r="C73" t="str">
+        <v>68500</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Guebwiller</v>
+      </c>
+      <c r="E73" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Pharmacie De La Place</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Place Hugues Salel</v>
+      </c>
+      <c r="C74" t="str">
+        <v>46250</v>
+      </c>
+      <c r="D74" t="str">
+        <v>CAZALS</v>
+      </c>
+      <c r="E74" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">Pharmacie Metro Jacques Cartier </v>
+      </c>
+      <c r="B75" t="str">
+        <v>104 Rue De L Alma</v>
+      </c>
+      <c r="C75" t="str">
+        <v>35000</v>
+      </c>
+      <c r="D75" t="str">
+        <v>RENNES</v>
+      </c>
+      <c r="E75" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Pharmacie Champollion</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2 Place Champollion</v>
+      </c>
+      <c r="C76" t="str">
+        <v>46100</v>
+      </c>
+      <c r="D76" t="str">
+        <v>FIGEAC</v>
+      </c>
+      <c r="E76" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Pharmacie Delaplace</v>
+      </c>
+      <c r="B77" t="str">
+        <v>12 Rue Des Ponts</v>
+      </c>
+      <c r="C77" t="str">
+        <v>89120</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Charny</v>
+      </c>
+      <c r="E77" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Pharmacie De La Verniaz</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Espace Leman 2</v>
+      </c>
+      <c r="C78" t="str">
+        <v>74200</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Anthy Sur Leman</v>
+      </c>
+      <c r="E78" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Pharmacie L'héritier</v>
+      </c>
+      <c r="B79" t="str">
+        <v>5 Passage de la Madeleine</v>
+      </c>
+      <c r="C79" t="str">
+        <v>81600</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Gaillac</v>
+      </c>
+      <c r="E79" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Pharmacie De La Gare</v>
+      </c>
+      <c r="B80" t="str">
+        <v>74 Avenue Jean Jaures</v>
+      </c>
+      <c r="C80" t="str">
+        <v>78500</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Sartrouville</v>
+      </c>
+      <c r="E80" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Pharmacie Racine</v>
+      </c>
+      <c r="B81" t="str">
+        <v>26 Place Racine</v>
+      </c>
+      <c r="C81" t="str">
+        <v>78300</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Poissy</v>
+      </c>
+      <c r="E81" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Pharmacie Enjolras - Place Fontanges</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Rue Du 11 Novembre</v>
+      </c>
+      <c r="C82" t="str">
+        <v>12200</v>
+      </c>
+      <c r="D82" t="str">
+        <v>VILLEFRANCHE DE ROUERGUE</v>
+      </c>
+      <c r="E82" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Pharmacie 110</v>
+      </c>
+      <c r="B83" t="str">
+        <v>110Bis Avenue D'italie</v>
+      </c>
+      <c r="C83" t="str">
+        <v>75013</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E83" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Pharmacie De Gracay</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Place Jean Chaudron</v>
+      </c>
+      <c r="C84" t="str">
+        <v>18310</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Gracay</v>
+      </c>
+      <c r="E84" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Pharmacie Clotis</v>
+      </c>
+      <c r="B85" t="str">
+        <v>56 Route Nationale</v>
+      </c>
+      <c r="C85" t="str">
+        <v>66202</v>
+      </c>
+      <c r="D85" t="str">
+        <v>ELNE CEDEX</v>
+      </c>
+      <c r="E85" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Pharmacie Principale de Sevran</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Av Du Commandant Charcot</v>
+      </c>
+      <c r="C86" t="str">
+        <v>93270</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Sevran</v>
+      </c>
+      <c r="E86" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Pharmacie Des Lumières - Labi</v>
+      </c>
+      <c r="B87" t="str">
+        <v>119 Rue Du Chemin Vert</v>
+      </c>
+      <c r="C87" t="str">
+        <v>75011</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E87" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Pharmacie Lamarck</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2 Place Jacques Froment</v>
+      </c>
+      <c r="C88" t="str">
+        <v>75018</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E88" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Pharmacie Monistrol</v>
+      </c>
+      <c r="B89" t="str">
+        <v>64 RUE MONISTROL</v>
+      </c>
+      <c r="C89" t="str">
+        <v>56100</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Lorient</v>
+      </c>
+      <c r="E89" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Pharmacie Chevalier</v>
+      </c>
+      <c r="B90" t="str">
+        <v>45 Rue Du General Leclerc</v>
+      </c>
+      <c r="C90" t="str">
+        <v>88500</v>
+      </c>
+      <c r="D90" t="str">
+        <v>MATTAINCOURT</v>
+      </c>
+      <c r="E90" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Pharmacie De Norelan</v>
+      </c>
+      <c r="B91" t="str">
+        <v>68 AV DE PARME</v>
+      </c>
+      <c r="C91" t="str">
+        <v>01000</v>
+      </c>
+      <c r="D91" t="str">
+        <v>BOURG EN BRESSE</v>
+      </c>
+      <c r="E91" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Pharmacie Principale Elsie</v>
+      </c>
+      <c r="B92" t="str">
+        <v>4 Place Du General De Gaulle</v>
+      </c>
+      <c r="C92" t="str">
+        <v>74160</v>
+      </c>
+      <c r="D92" t="str">
+        <v>ST JULIEN EN GENEVOIS</v>
+      </c>
+      <c r="E92" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Pharmacie De Montreux</v>
+      </c>
+      <c r="B93" t="str">
+        <v>8 Rue Saint Denis</v>
+      </c>
+      <c r="C93" t="str">
+        <v>72300</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Sable Sur Sarthe</v>
+      </c>
+      <c r="E93" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Pharmacie De Molières</v>
+      </c>
+      <c r="B94" t="str">
+        <v>10 Avenue des Promenades</v>
+      </c>
+      <c r="C94" t="str">
+        <v>82220</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Molieres</v>
+      </c>
+      <c r="E94" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Pharmacie Principale</v>
+      </c>
+      <c r="B95" t="str">
+        <v>36 Avenue Raymond Poincare</v>
+      </c>
+      <c r="C95" t="str">
+        <v>19130</v>
+      </c>
+      <c r="D95" t="str">
+        <v>OBJAT</v>
+      </c>
+      <c r="E95" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Pharmacie De L Avenue</v>
+      </c>
+      <c r="B96" t="str">
+        <v>40 Avenue De Romans</v>
+      </c>
+      <c r="C96" t="str">
+        <v>38360</v>
+      </c>
+      <c r="D96" t="str">
+        <v>SASSENAGE</v>
+      </c>
+      <c r="E96" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Pharmacie Majorelle</v>
+      </c>
+      <c r="B97" t="str">
+        <v>287 Route De Vienne</v>
+      </c>
+      <c r="C97" t="str">
+        <v>69200</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Venissieux</v>
+      </c>
+      <c r="E97" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Pharmacie Roge Cavailles</v>
+      </c>
+      <c r="B98" t="str">
+        <v>116 Boulevard Haussmann</v>
+      </c>
+      <c r="C98" t="str">
+        <v>75008</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E98" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Pharmacie Pouyes</v>
+      </c>
+      <c r="B99" t="str">
+        <v>28 Avenue Du General De Gaulle</v>
+      </c>
+      <c r="C99" t="str">
+        <v>46200</v>
+      </c>
+      <c r="D99" t="str">
+        <v>SOUILLAC</v>
+      </c>
+      <c r="E99" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Pharmacie Elysee Village</v>
+      </c>
+      <c r="B100" t="str">
+        <v>18 Avenue De La Jonchere</v>
+      </c>
+      <c r="C100" t="str">
+        <v>78170</v>
+      </c>
+      <c r="D100" t="str">
+        <v>La Celle St Cloud</v>
+      </c>
+      <c r="E100" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>La Grande Pharmacie De Moulins</v>
+      </c>
+      <c r="B101" t="str">
+        <v>25 Place De La Liberte</v>
+      </c>
+      <c r="C101" t="str">
+        <v>03000</v>
+      </c>
+      <c r="D101" t="str">
+        <v>MOULINS</v>
+      </c>
+      <c r="E101" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Pharmacie Dubois</v>
+      </c>
+      <c r="B102" t="str">
+        <v>16 Rue Jean Baptiste Corbel</v>
+      </c>
+      <c r="C102" t="str">
+        <v>22550</v>
+      </c>
+      <c r="D102" t="str">
+        <v>HENANBIHEN</v>
+      </c>
+      <c r="E102" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Pharmacie De La Boisse</v>
+      </c>
+      <c r="B103" t="str">
+        <v>55 Rue de la meule</v>
+      </c>
+      <c r="C103" t="str">
+        <v>01120</v>
+      </c>
+      <c r="D103" t="str">
+        <v>La Boisse</v>
+      </c>
+      <c r="E103" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Pharmacie Iconic</v>
+      </c>
+      <c r="B104" t="str">
+        <v>10 AVENUE THIERS</v>
+      </c>
+      <c r="C104" t="str">
+        <v>06000</v>
+      </c>
+      <c r="D104" t="str">
+        <v>NICE</v>
+      </c>
+      <c r="E104" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Pharmacie Pierre De Bar</v>
+      </c>
+      <c r="B105" t="str">
+        <v>30 bis rue Pierre de Bar</v>
+      </c>
+      <c r="C105" t="str">
+        <v>54240</v>
+      </c>
+      <c r="D105" t="str">
+        <v>JOEUF</v>
+      </c>
+      <c r="E105" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Pharmacie De La Tête D'homme</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2 Rue Du Marechal Foch</v>
+      </c>
+      <c r="C106" t="str">
+        <v>76260</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Eu</v>
+      </c>
+      <c r="E106" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pharmacie Peda</v>
+      </c>
+      <c r="B107" t="str">
+        <v>32 Rue Paul Valentin</v>
+      </c>
+      <c r="C107" t="str">
+        <v>77410</v>
+      </c>
+      <c r="D107" t="str">
+        <v>ANNET SUR MARNE</v>
+      </c>
+      <c r="E107" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Pharmacie Des Acacias</v>
+      </c>
+      <c r="B108" t="str">
+        <v>1 Place Des Acacias</v>
+      </c>
+      <c r="C108" t="str">
+        <v>85400</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Luçon</v>
+      </c>
+      <c r="E108" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Pharmacie Du Pont Cardinet</v>
+      </c>
+      <c r="B109" t="str">
+        <v>1 Rue Jouffroy D'abbans</v>
+      </c>
+      <c r="C109" t="str">
+        <v>75017</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E109" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Pharmacie Du Wahoo</v>
+      </c>
+      <c r="B110" t="str">
+        <v xml:space="preserve"> 40av giraudoux</v>
+      </c>
+      <c r="C110" t="str">
+        <v>66100</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Perpignan</v>
+      </c>
+      <c r="E110" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Pharmacie De L'office Du Tourisme</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2 Place Jean Marcellin</v>
+      </c>
+      <c r="C111" t="str">
+        <v>05000</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Gap</v>
+      </c>
+      <c r="E111" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Grande Pharmacie De La Mairie</v>
+      </c>
+      <c r="B112" t="str">
+        <v>101 Avenue Charles De Gaulle</v>
+      </c>
+      <c r="C112" t="str">
+        <v>69160</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Tassin La Demi Lune</v>
+      </c>
+      <c r="E112" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Pharmacie Del Monestir</v>
+      </c>
+      <c r="B113" t="str">
+        <v>16 Avenue Gilbert Brutus</v>
+      </c>
+      <c r="C113" t="str">
+        <v>66240</v>
+      </c>
+      <c r="D113" t="str">
+        <v>ST ESTEVE</v>
+      </c>
+      <c r="E113" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Pharmacie Du Prepaou</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Allee Des Piboules</v>
+      </c>
+      <c r="C114" t="str">
+        <v>13800</v>
+      </c>
+      <c r="D114" t="str">
+        <v>ISTRES</v>
+      </c>
+      <c r="E114" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Pharmacie Fouassier</v>
+      </c>
+      <c r="B115" t="str">
+        <v>1 Rue Jean Baffier</v>
+      </c>
+      <c r="C115" t="str">
+        <v>18000</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Bourges</v>
+      </c>
+      <c r="E115" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Pharmacie De La Voie Lactée</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Cc Le Ruisseau - Rue Des Pins</v>
+      </c>
+      <c r="C116" t="str">
+        <v>31700</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Beauzelle</v>
+      </c>
+      <c r="E116" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Pharmacie Doree</v>
+      </c>
+      <c r="B117" t="str">
+        <v>19 pl République</v>
+      </c>
+      <c r="C117" t="str">
+        <v>45200</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Montargis</v>
+      </c>
+      <c r="E117" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Pharmacie Centrale</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2 Rue De Huningue</v>
+      </c>
+      <c r="C118" t="str">
+        <v>68300</v>
+      </c>
+      <c r="D118" t="str">
+        <v>ST LOUIS</v>
+      </c>
+      <c r="E118" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Pharmacie Devez Vidal</v>
+      </c>
+      <c r="B119" t="str">
+        <v>1 Place Jean Jaures</v>
+      </c>
+      <c r="C119" t="str">
+        <v>63510</v>
+      </c>
+      <c r="D119" t="str">
+        <v>AULNAT</v>
+      </c>
+      <c r="E119" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Pharmacie Landre</v>
+      </c>
+      <c r="B120" t="str">
+        <v>5 avenue Mar De Lattre de Tassigny</v>
+      </c>
+      <c r="C120" t="str">
+        <v>79320</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Moncoutant</v>
+      </c>
+      <c r="E120" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Pharmacie Gambetta</v>
+      </c>
+      <c r="B121" t="str">
+        <v>15 Place Gambetta</v>
+      </c>
+      <c r="C121" t="str">
+        <v>36000</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Chateauroux</v>
+      </c>
+      <c r="E121" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Pharmacie De Champagné</v>
+      </c>
+      <c r="B122" t="str">
+        <v xml:space="preserve">14 Quater Rue De La Paix </v>
+      </c>
+      <c r="C122" t="str">
+        <v>85450</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Champagné Les Marais</v>
+      </c>
+      <c r="E122" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Grande Pharmacie De L'Europe</v>
+      </c>
+      <c r="B123" t="str">
+        <v>86 Bd Alexandre De Fraissinette</v>
+      </c>
+      <c r="C123" t="str">
+        <v>42100</v>
+      </c>
+      <c r="D123" t="str">
+        <v>ST ETIENNE</v>
+      </c>
+      <c r="E123" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v xml:space="preserve">Pharmacie De La Gare </v>
+      </c>
+      <c r="B124" t="str">
+        <v xml:space="preserve">2 RUE DU GENERAL DE GAULLE </v>
+      </c>
+      <c r="C124" t="str">
+        <v>44210</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Pornic</v>
+      </c>
+      <c r="E124" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Pharmacie De Martinvast</v>
+      </c>
+      <c r="B125" t="str">
+        <v>20 Rue Maurice Brisset</v>
+      </c>
+      <c r="C125" t="str">
+        <v>50690</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Martinvast</v>
+      </c>
+      <c r="E125" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Pharmacie Des Poètes</v>
+      </c>
+      <c r="B126" t="str">
+        <v>59 All. Paul Riquet</v>
+      </c>
+      <c r="C126" t="str">
+        <v>34500</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Béziers</v>
+      </c>
+      <c r="E126" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Pharmacie Des Cévennes</v>
+      </c>
+      <c r="B127" t="str">
+        <v>47 Rue Balard</v>
+      </c>
+      <c r="C127" t="str">
+        <v>75015</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E127" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Pharmacie Centrale Bapaume</v>
+      </c>
+      <c r="B128" t="str">
+        <v>4 Rue De Peronne</v>
+      </c>
+      <c r="C128" t="str">
+        <v>62450</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Bapaume</v>
+      </c>
+      <c r="E128" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Pharmacie du Boulevard</v>
+      </c>
+      <c r="B129" t="str">
+        <v>147 Ter Boulevard De Strasbourg</v>
+      </c>
+      <c r="C129" t="str">
+        <v>94130</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Nogent Sur Marne</v>
+      </c>
+      <c r="E129" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Pharmacie De La Paix</v>
+      </c>
+      <c r="B130" t="str">
+        <v>14Bis Rue Leo Lagrange</v>
+      </c>
+      <c r="C130" t="str">
+        <v>60100</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Creil</v>
+      </c>
+      <c r="E130" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Pharmacie Du Mondony</v>
+      </c>
+      <c r="B131" t="str">
+        <v>12 Avenue Du Vallespir</v>
+      </c>
+      <c r="C131" t="str">
+        <v>66110</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Amelie Les Bains Palalda</v>
+      </c>
+      <c r="E131" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Pharmacie Bobo Durand</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Avenue Des Alizes</v>
+      </c>
+      <c r="C132" t="str">
+        <v>66140</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Canet En Roussillon</v>
+      </c>
+      <c r="E132" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Pharmacie D'Eymet</v>
+      </c>
+      <c r="B133" t="str">
+        <v>45 Boulevard national</v>
+      </c>
+      <c r="C133" t="str">
+        <v>24500</v>
+      </c>
+      <c r="D133" t="str">
+        <v>EYMET</v>
+      </c>
+      <c r="E133" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Pharmacie Marty</v>
+      </c>
+      <c r="B134" t="str">
+        <v>AVENUE DE MONT-LOUIS</v>
+      </c>
+      <c r="C134" t="str">
+        <v>66210</v>
+      </c>
+      <c r="D134" t="str">
+        <v xml:space="preserve">LES ANGLES </v>
+      </c>
+      <c r="E134" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Pharmacie La Castellane</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Place De La Tartane</v>
+      </c>
+      <c r="C135" t="str">
+        <v>13016</v>
+      </c>
+      <c r="D135" t="str">
+        <v>MARSEILLE</v>
+      </c>
+      <c r="E135" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Pharmacie Des Trois Chateaux</v>
+      </c>
+      <c r="B136" t="str">
+        <v>8 Place De La Liberation</v>
+      </c>
+      <c r="C136" t="str">
+        <v>26130</v>
+      </c>
+      <c r="D136" t="str">
+        <v>ST PAUL TROIS CHATEAUX</v>
+      </c>
+      <c r="E136" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pharmacie Du Marcadieu</v>
+      </c>
+      <c r="B137" t="str">
+        <v>9 Place Marcadieu</v>
+      </c>
+      <c r="C137" t="str">
+        <v>65000</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Tarbes</v>
+      </c>
+      <c r="E137" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Pharmacie De La Mairie Sincholle</v>
+      </c>
+      <c r="B138" t="str">
+        <v xml:space="preserve">PLACE PABLO PICASSO 50 rue Ray Charles </v>
+      </c>
+      <c r="C138" t="str">
+        <v>34000</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Montpellier</v>
+      </c>
+      <c r="E138" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Pharmacie Clémenceau</v>
+      </c>
+      <c r="B139" t="str">
+        <v>10 Rue Georges Clemenceau</v>
+      </c>
+      <c r="C139" t="str">
+        <v>78520</v>
+      </c>
+      <c r="D139" t="str">
+        <v>LIMAY</v>
+      </c>
+      <c r="E139" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Pharmacie Auchan Saint Loup</v>
+      </c>
+      <c r="B140" t="str">
+        <v>57 Boulevard Romain Rolland</v>
+      </c>
+      <c r="C140" t="str">
+        <v>13010</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Marseille</v>
+      </c>
+      <c r="E140" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Pharmacie D'exincourt</v>
+      </c>
+      <c r="B141" t="str">
+        <v>19 Rue D Egouttes</v>
+      </c>
+      <c r="C141" t="str">
+        <v>25400</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Exincourt</v>
+      </c>
+      <c r="E141" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Pharmacie Rohrbacher</v>
+      </c>
+      <c r="B142" t="str">
+        <v>12 Rue Du Chene</v>
+      </c>
+      <c r="C142" t="str">
+        <v>67470</v>
+      </c>
+      <c r="D142" t="str">
+        <v>MOTHERN</v>
+      </c>
+      <c r="E142" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Pharmacie Boulert</v>
+      </c>
+      <c r="B143" t="str">
+        <v>109 Boulevard Gabriel Peri</v>
+      </c>
+      <c r="C143" t="str">
+        <v>62210</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Avion</v>
+      </c>
+      <c r="E143" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Pharmacie Diemeringen</v>
+      </c>
+      <c r="B144" t="str">
+        <v>51 Grand Rue</v>
+      </c>
+      <c r="C144" t="str">
+        <v>67430</v>
+      </c>
+      <c r="D144" t="str">
+        <v>DIEMERINGEN</v>
+      </c>
+      <c r="E144" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Pharmacie F. Hairie</v>
+      </c>
+      <c r="B145" t="str">
+        <v>22 Rue De Domfront</v>
+      </c>
+      <c r="C145" t="str">
+        <v>61140</v>
+      </c>
+      <c r="D145" t="str">
+        <v>RIVES D'ANDAINE</v>
+      </c>
+      <c r="E145" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Pharmacie Du Golf</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Avenue De Soissons</v>
+      </c>
+      <c r="C146" t="str">
+        <v>02400</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Chateau Thierry</v>
+      </c>
+      <c r="E146" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Pharmacie Haudebourg Libeau</v>
+      </c>
+      <c r="B147" t="str">
+        <v>8 Gd Pl. Grand Place</v>
+      </c>
+      <c r="C147" t="str">
+        <v>85230</v>
+      </c>
+      <c r="D147" t="str">
+        <v>BEAUVOIR SUR MER</v>
+      </c>
+      <c r="E147" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Pharmacie Stevenoot Rauwel</v>
+      </c>
+      <c r="B148" t="str">
+        <v>25 Place Du General De Gaulle</v>
+      </c>
+      <c r="C148" t="str">
+        <v>59470</v>
+      </c>
+      <c r="D148" t="str">
+        <v>WORMHOUT</v>
+      </c>
+      <c r="E148" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Pharmacie Jean Mermoz</v>
+      </c>
+      <c r="B149" t="str">
+        <v>8 Place Andre Latarjet</v>
+      </c>
+      <c r="C149" t="str">
+        <v>69008</v>
+      </c>
+      <c r="D149" t="str">
+        <v>LYON</v>
+      </c>
+      <c r="E149" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Pharmacie Devriere</v>
+      </c>
+      <c r="B150" t="str">
+        <v>21 Rue De Champagne</v>
+      </c>
+      <c r="C150" t="str">
+        <v>02100</v>
+      </c>
+      <c r="D150" t="str">
+        <v>LESDINS</v>
+      </c>
+      <c r="E150" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Pharmacie Des 3 Chênes</v>
+      </c>
+      <c r="B151" t="str">
+        <v xml:space="preserve"> 23 PLACE ALPHONSE BERGEROT</v>
+      </c>
+      <c r="C151" t="str">
+        <v>59470</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Esquelbecq</v>
+      </c>
+      <c r="E151" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Pharmacie Hebrard</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Rue De La Resistance</v>
+      </c>
+      <c r="C152" t="str">
+        <v>23460</v>
+      </c>
+      <c r="D152" t="str">
+        <v>ROYERE DE VASSIVIERE</v>
+      </c>
+      <c r="E152" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Pharmacie De L Amandier</v>
+      </c>
+      <c r="B153" t="str">
+        <v>26 Rue Rudolph Serkin</v>
+      </c>
+      <c r="C153" t="str">
+        <v>84000</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Avignon</v>
+      </c>
+      <c r="E153" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>Pharmacie Du Pelican</v>
+      </c>
+      <c r="B154" t="str">
+        <v>38 Allee De Craponne</v>
+      </c>
+      <c r="C154" t="str">
+        <v>13330</v>
+      </c>
+      <c r="D154" t="str">
+        <v>PELISSANNE</v>
+      </c>
+      <c r="E154" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Pharmacie Laures Raynaud</v>
+      </c>
+      <c r="B155" t="str">
+        <v>203 LE SAUT DU LOUP</v>
+      </c>
+      <c r="C155" t="str">
+        <v>30340</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Rousson</v>
+      </c>
+      <c r="E155" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Pharmacie Renaud Marchand</v>
+      </c>
+      <c r="B156" t="str">
+        <v>37 Boulevard Gambetta</v>
+      </c>
+      <c r="C156" t="str">
+        <v>03320</v>
+      </c>
+      <c r="D156" t="str">
+        <v>LURCY LEVIS</v>
+      </c>
+      <c r="E156" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Pharmacie Du Grand Parc</v>
+      </c>
+      <c r="B157" t="str">
+        <v>29 Rue Charles De Gaulle</v>
+      </c>
+      <c r="C157" t="str">
+        <v>91070</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Bondoufle</v>
+      </c>
+      <c r="E157" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Pharmacie Du Soleil</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Cc Leclerc - Zac Du Jonchery</v>
+      </c>
+      <c r="C158" t="str">
+        <v>54200</v>
+      </c>
+      <c r="D158" t="str">
+        <v>DOMMARTIN LES TOUL</v>
+      </c>
+      <c r="E158" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pharmacie Du Thaurion</v>
+      </c>
+      <c r="B159" t="str">
+        <v>12 Route D Aubusson</v>
+      </c>
+      <c r="C159" t="str">
+        <v>23250</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Pontarion</v>
+      </c>
+      <c r="E159" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Pharmacie Du Lycée</v>
+      </c>
+      <c r="B160" t="str">
+        <v>106 Boulevard Jean Jaures</v>
+      </c>
+      <c r="C160" t="str">
+        <v>91100</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Corbeil Essonnes</v>
+      </c>
+      <c r="E160" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>Pharmacie Sainte Eve</v>
+      </c>
+      <c r="B161" t="str">
+        <v>33 Boulevard Henri Iv</v>
+      </c>
+      <c r="C161" t="str">
+        <v>28100</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Dreux</v>
+      </c>
+      <c r="E161" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Pharmacie Du Briolet</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Centre Commercial Lo Moral</v>
+      </c>
+      <c r="C162" t="str">
+        <v>11570</v>
+      </c>
+      <c r="D162" t="str">
+        <v>PALAJA</v>
+      </c>
+      <c r="E162" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Pharmacie Pasteur</v>
+      </c>
+      <c r="B163" t="str">
+        <v>143 Avenue Marechal Lyautey</v>
+      </c>
+      <c r="C163" t="str">
+        <v>06000</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Nice</v>
+      </c>
+      <c r="E163" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Pharmacie Des Lissiers</v>
+      </c>
+      <c r="B164" t="str">
+        <v>10 Avenue Des Lissiers</v>
+      </c>
+      <c r="C164" t="str">
+        <v>23200</v>
+      </c>
+      <c r="D164" t="str">
+        <v>AUBUSSON</v>
+      </c>
+      <c r="E164" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Pharmacie Du Marché</v>
+      </c>
+      <c r="B165" t="str">
+        <v>12 Rue Du Levant</v>
+      </c>
+      <c r="C165" t="str">
+        <v>91860</v>
+      </c>
+      <c r="D165" t="str">
+        <v>EPINAY SOUS SENART</v>
+      </c>
+      <c r="E165" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Pharmacie Chazot</v>
+      </c>
+      <c r="B166" t="str">
+        <v>3 Place Du General Espagne</v>
+      </c>
+      <c r="C166" t="str">
+        <v>23200</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Aubusson</v>
+      </c>
+      <c r="E166" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Pharmacie Principale</v>
+      </c>
+      <c r="B167" t="str">
+        <v>26 Rue Foch</v>
+      </c>
+      <c r="C167" t="str">
+        <v>34000</v>
+      </c>
+      <c r="D167" t="str">
+        <v>MONTPELLIER</v>
+      </c>
+      <c r="E167" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Pharmacie Gambetta</v>
+      </c>
+      <c r="B168" t="str">
+        <v>4 PLACE GAMBETTA</v>
+      </c>
+      <c r="C168" t="str">
+        <v>72000</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Le Mans</v>
+      </c>
+      <c r="E168" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>Pharmacie Le Genevois</v>
+      </c>
+      <c r="B169" t="str">
+        <v>10 Rue Des Glieres</v>
+      </c>
+      <c r="C169" t="str">
+        <v>74000</v>
+      </c>
+      <c r="D169" t="str">
+        <v>ANNECY</v>
+      </c>
+      <c r="E169" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Pharmacie Du Valois</v>
+      </c>
+      <c r="B170" t="str">
+        <v>56 Avenue Du President Kennedy</v>
+      </c>
+      <c r="C170" t="str">
+        <v>60800</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Crepy En Valois</v>
+      </c>
+      <c r="E170" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Pharmacie La Gantiere</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Rue Fontaine Du Bac</v>
+      </c>
+      <c r="C171" t="str">
+        <v>63000</v>
+      </c>
+      <c r="D171" t="str">
+        <v>CLERMONT FERRAND</v>
+      </c>
+      <c r="E171" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Pharmacie Anglaise</v>
+      </c>
+      <c r="B172" t="str">
+        <v>62 Avenue Des Champs Elysees</v>
+      </c>
+      <c r="C172" t="str">
+        <v>75008</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E172" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>Pharmacie Des Muguets</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Rue Des Muguets</v>
+      </c>
+      <c r="C173" t="str">
+        <v>38070</v>
+      </c>
+      <c r="D173" t="str">
+        <v>ST QUENTIN FALLAVIER</v>
+      </c>
+      <c r="E173" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>Pharmacie 3B St Quentin</v>
+      </c>
+      <c r="B174" t="str">
+        <v>37 39 Rue D Isle</v>
+      </c>
+      <c r="C174" t="str">
+        <v>02100</v>
+      </c>
+      <c r="D174" t="str">
+        <v>ST QUENTIN</v>
+      </c>
+      <c r="E174" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>Pharmacie De Vesone</v>
+      </c>
+      <c r="B175" t="str">
+        <v>81 Rue Claude Bernard</v>
+      </c>
+      <c r="C175" t="str">
+        <v>24000</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Perigueux</v>
+      </c>
+      <c r="E175" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>Pharmacie Chatelain</v>
+      </c>
+      <c r="B176" t="str">
+        <v>5 Rue Arthur Lamendin</v>
+      </c>
+      <c r="C176" t="str">
+        <v>59293</v>
+      </c>
+      <c r="D176" t="str">
+        <v>NEUVILLE SUR ESCAUT</v>
+      </c>
+      <c r="E176" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Pharmacie Du Centre</v>
+      </c>
+      <c r="B177" t="str">
+        <v>10 Rue Fon De L Hospital</v>
+      </c>
+      <c r="C177" t="str">
+        <v>34430</v>
+      </c>
+      <c r="D177" t="str">
+        <v>ST JEAN DE VEDAS</v>
+      </c>
+      <c r="E177" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Pharmacie Du Palais Des Sports</v>
+      </c>
+      <c r="B178" t="str">
+        <v>1 Avenue Honore Serres</v>
+      </c>
+      <c r="C178" t="str">
+        <v>31000</v>
+      </c>
+      <c r="D178" t="str">
+        <v>TOULOUSE</v>
+      </c>
+      <c r="E178" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Pharmacie Mariani</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Cc Residence Du Parc - 4 Avenue Anatole France</v>
+      </c>
+      <c r="C179" t="str">
+        <v>94600</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Choisy Le Roi</v>
+      </c>
+      <c r="E179" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Pharmacie De Provence</v>
+      </c>
+      <c r="B180" t="str">
+        <v>92 Avenue De Tarascon</v>
+      </c>
+      <c r="C180" t="str">
+        <v>84000</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Avignon</v>
+      </c>
+      <c r="E180" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Pharmacie Du Loing</v>
+      </c>
+      <c r="B181" t="str">
+        <v>43 45 Rue Grande</v>
+      </c>
+      <c r="C181" t="str">
+        <v>77250</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Moret Sur Loing</v>
+      </c>
+      <c r="E181" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Pharmacie Auloge</v>
+      </c>
+      <c r="B182" t="str">
+        <v>1 Avenue Du General De Gaulle</v>
+      </c>
+      <c r="C182" t="str">
+        <v>57570</v>
+      </c>
+      <c r="D182" t="str">
+        <v>CATTENOM</v>
+      </c>
+      <c r="E182" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Pharmacie Des Ecoles</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2 Rue Lucias</v>
+      </c>
+      <c r="C183" t="str">
+        <v>33240</v>
+      </c>
+      <c r="D183" t="str">
+        <v>St Andre De Cubzac</v>
+      </c>
+      <c r="E183" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>Pharmacie Du Progrès</v>
+      </c>
+      <c r="B184" t="str">
+        <v>13 Place du Peuple</v>
+      </c>
+      <c r="C184" t="str">
+        <v>42000</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Saint Etienne</v>
+      </c>
+      <c r="E184" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>Pharmacie Nature</v>
+      </c>
+      <c r="B185" t="str">
+        <v xml:space="preserve">4 rue de la Papeterie </v>
+      </c>
+      <c r="C185" t="str">
+        <v>95610</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Eragny Sur Oise</v>
+      </c>
+      <c r="E185" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Pharmacie De Brax</v>
+      </c>
+      <c r="B186" t="str">
+        <v>175 A Avenue Des Landes</v>
+      </c>
+      <c r="C186" t="str">
+        <v>47310</v>
+      </c>
+      <c r="D186" t="str">
+        <v>BRAX</v>
+      </c>
+      <c r="E186" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Pharmacie Du Val De L'erdre</v>
+      </c>
+      <c r="B187" t="str">
+        <v>9 Rue d'Anjou</v>
+      </c>
+      <c r="C187" t="str">
+        <v>44540</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Vallons-de-L'Erdre</v>
+      </c>
+      <c r="E187" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>Pharmacie De Sion</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Rue Du Marche</v>
+      </c>
+      <c r="C188" t="str">
+        <v>85270</v>
+      </c>
+      <c r="D188" t="str">
+        <v>ST HILAIRE DE RIEZ</v>
+      </c>
+      <c r="E188" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>Pharmacie De Lanveur</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Rue Alfred Dreyfus Centre Commercial Intermarche De Lanveur</v>
+      </c>
+      <c r="C189" t="str">
+        <v>56100</v>
+      </c>
+      <c r="D189" t="str">
+        <v>LORIENT</v>
+      </c>
+      <c r="E189" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Pharmacie De La Poste</v>
+      </c>
+      <c r="B190" t="str">
+        <v>67Bis Route Nationale</v>
+      </c>
+      <c r="C190" t="str">
+        <v>69330</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Jonage</v>
+      </c>
+      <c r="E190" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Pharmacie De Janval</v>
+      </c>
+      <c r="B191" t="str">
+        <v>32 Rue Léon Rogé</v>
+      </c>
+      <c r="C191" t="str">
+        <v>76200</v>
+      </c>
+      <c r="D191" t="str">
+        <v>DIEPPE</v>
+      </c>
+      <c r="E191" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pharmacie De La Poste</v>
+      </c>
+      <c r="B192" t="str">
+        <v>14 Avenue De Verdun</v>
+      </c>
+      <c r="C192" t="str">
+        <v>73100</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Aix Les Bains Cedex</v>
+      </c>
+      <c r="E192" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Pharmacie Paccianus</v>
+      </c>
+      <c r="B193" t="str">
+        <v>31 Avenue De L Olivier</v>
+      </c>
+      <c r="C193" t="str">
+        <v>66300</v>
+      </c>
+      <c r="D193" t="str">
+        <v>BANYULS DELS ASPRES</v>
+      </c>
+      <c r="E193" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Grande Pharmacie Du Rond Point Bourelly</v>
+      </c>
+      <c r="B194" t="str">
+        <v>93 Avenue Geoffroy Perret</v>
+      </c>
+      <c r="C194" t="str">
+        <v>30210</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Remoulins</v>
+      </c>
+      <c r="E194" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Pharmacie Moreau</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Place De La Liberation</v>
+      </c>
+      <c r="C195" t="str">
+        <v>23200</v>
+      </c>
+      <c r="D195" t="str">
+        <v>AUBUSSON</v>
+      </c>
+      <c r="E195" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Pharmacie Lacausse</v>
+      </c>
+      <c r="B196" t="str">
+        <v>3 Route De Tercis</v>
+      </c>
+      <c r="C196" t="str">
+        <v>40100</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Dax</v>
+      </c>
+      <c r="E196" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Pharmacie Du Pont Noir</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2 Rue D Erquelinnes</v>
+      </c>
+      <c r="C197" t="str">
+        <v>59460</v>
+      </c>
+      <c r="D197" t="str">
+        <v>JEUMONT</v>
+      </c>
+      <c r="E197" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Pharmacie Du Marché</v>
+      </c>
+      <c r="B198" t="str">
+        <v>35 Avenue andré Maginot</v>
+      </c>
+      <c r="C198" t="str">
+        <v>01000</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Bourg En Bresse</v>
+      </c>
+      <c r="E198" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Pharmacie Centrale</v>
+      </c>
+      <c r="B199" t="str">
+        <v>19 Boulevard du Portalet</v>
+      </c>
+      <c r="C199" t="str">
+        <v>30500</v>
+      </c>
+      <c r="D199" t="str">
+        <v>St Ambroix</v>
+      </c>
+      <c r="E199" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Pharmacie Saint Martin</v>
+      </c>
+      <c r="B200" t="str">
+        <v>29 Rue Saint Martin</v>
+      </c>
+      <c r="C200" t="str">
+        <v>28100</v>
+      </c>
+      <c r="D200" t="str">
+        <v>DREUX</v>
+      </c>
+      <c r="E200" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Pharmacie Saint Louis</v>
+      </c>
+      <c r="B201" t="str">
+        <v xml:space="preserve">236 avenue des martyrs de la résistance  </v>
+      </c>
+      <c r="C201" t="str">
+        <v>40000</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Mont De Marsan</v>
+      </c>
+      <c r="E201" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Pharmacie Agnes Praden</v>
+      </c>
+      <c r="B202" t="str">
+        <v>198 AV DES FRERES LUMIERE</v>
+      </c>
+      <c r="C202" t="str">
+        <v>30100</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Ales</v>
+      </c>
+      <c r="E202" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Pharmacie Des Aravis</v>
+      </c>
+      <c r="B203" t="str">
+        <v>52 Place Madeleine Lafrance</v>
+      </c>
+      <c r="C203" t="str">
+        <v>74450</v>
+      </c>
+      <c r="D203" t="str">
+        <v>ST JEAN DE SIXT</v>
+      </c>
+      <c r="E203" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Pharmacie De La Bernerie</v>
+      </c>
+      <c r="B204" t="str">
+        <v>21 Rue Du Marechal Foch</v>
+      </c>
+      <c r="C204" t="str">
+        <v>44760</v>
+      </c>
+      <c r="D204" t="str">
+        <v>La Bernerie En Retz</v>
+      </c>
+      <c r="E204" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Pharmacie De Veigy Foncenex</v>
+      </c>
+      <c r="B205" t="str">
+        <v>453 ROUTE DES VOIRONS</v>
+      </c>
+      <c r="C205" t="str">
+        <v>74140</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Veigy Foncenex</v>
+      </c>
+      <c r="E205" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Nouvelle Pharmacie Centrale</v>
+      </c>
+      <c r="B206" t="str">
+        <v>22 Rue Du Markstein</v>
+      </c>
+      <c r="C206" t="str">
+        <v>68270</v>
+      </c>
+      <c r="D206" t="str">
+        <v>WITTENHEIM</v>
+      </c>
+      <c r="E206" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Pharmacie Des Ormeaux</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Boulevard Lucien Dodin</v>
+      </c>
+      <c r="C207" t="str">
+        <v>85300</v>
+      </c>
+      <c r="D207" t="str">
+        <v>CHALLANS</v>
+      </c>
+      <c r="E207" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Pharmacie De Merville</v>
+      </c>
+      <c r="B208" t="str">
+        <v>15 Rue Du 8 Mai 1945</v>
+      </c>
+      <c r="C208" t="str">
+        <v>31330</v>
+      </c>
+      <c r="D208" t="str">
+        <v>MERVILLE</v>
+      </c>
+      <c r="E208" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Pharmacie Du Village</v>
+      </c>
+      <c r="B209" t="str">
+        <v>9 Place De La Republique</v>
+      </c>
+      <c r="C209" t="str">
+        <v>69780</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Mions</v>
+      </c>
+      <c r="E209" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Pharmacie De Bizy</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Cc Carrefour - 5 Boulevard Isambard</v>
+      </c>
+      <c r="C210" t="str">
+        <v>27200</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Vernon</v>
+      </c>
+      <c r="E210" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Nouvelle Pharmacie Du Millénaire</v>
+      </c>
+      <c r="B211" t="str">
+        <v>868 Rue De La Vieille Poste</v>
+      </c>
+      <c r="C211" t="str">
+        <v>34000</v>
+      </c>
+      <c r="D211" t="str">
+        <v>MONTPELLIER</v>
+      </c>
+      <c r="E211" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Pharmacie Lyon Confluence</v>
+      </c>
+      <c r="B212" t="str">
+        <v>4 Rue Casimir Perier</v>
+      </c>
+      <c r="C212" t="str">
+        <v>69002</v>
+      </c>
+      <c r="D212" t="str">
+        <v>LYON</v>
+      </c>
+      <c r="E212" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>M.a Pharmacie</v>
+      </c>
+      <c r="B213" t="str">
+        <v>89 Boulevard Georges Brassens</v>
+      </c>
+      <c r="C213" t="str">
+        <v>12100</v>
+      </c>
+      <c r="D213" t="str">
+        <v>MILLAU</v>
+      </c>
+      <c r="E213" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pharmacie Du Centre</v>
+      </c>
+      <c r="B214" t="str">
+        <v>4-6 rue de la gare</v>
+      </c>
+      <c r="C214" t="str">
+        <v>91650</v>
+      </c>
+      <c r="D214" t="str">
+        <v>BREUILLET</v>
+      </c>
+      <c r="E214" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Pharmacie Du Vitrail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>92 Avenue De La Republique</v>
+      </c>
+      <c r="C215" t="str">
+        <v>69160</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Tassin La Demi Lune</v>
+      </c>
+      <c r="E215" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>Pharmacie Des Clouteries</v>
+      </c>
+      <c r="B216" t="str">
+        <v>12 Place Victor Hugo</v>
+      </c>
+      <c r="C216" t="str">
+        <v>62500</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Saint omer</v>
+      </c>
+      <c r="E216" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Pharmacie Huyghe</v>
+      </c>
+      <c r="B217" t="str">
+        <v>24 Rue Roger Salengro</v>
+      </c>
+      <c r="C217" t="str">
+        <v>59171</v>
+      </c>
+      <c r="D217" t="str">
+        <v>HELESMES</v>
+      </c>
+      <c r="E217" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Pharmacie Des Chaillots</v>
+      </c>
+      <c r="B218" t="str">
+        <v>2 rue Henry Dunant</v>
+      </c>
+      <c r="C218" t="str">
+        <v>89100</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Sens</v>
+      </c>
+      <c r="E218" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Pharmacie De Genis</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Grand Place</v>
+      </c>
+      <c r="C219" t="str">
+        <v>24160</v>
+      </c>
+      <c r="D219" t="str">
+        <v>GENIS</v>
+      </c>
+      <c r="E219" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Pharmacie Sauder</v>
+      </c>
+      <c r="B220" t="str">
+        <v>9 Rue Des Canaris</v>
+      </c>
+      <c r="C220" t="str">
+        <v>57150</v>
+      </c>
+      <c r="D220" t="str">
+        <v>CREUTZWALD</v>
+      </c>
+      <c r="E220" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Pharmacie Boissy 2</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Centre Commercial Boissy 2</v>
+      </c>
+      <c r="C221" t="str">
+        <v>94470</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Boissy St Leger</v>
+      </c>
+      <c r="E221" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Pharmacie Des Alizes</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Place Saint Martin</v>
+      </c>
+      <c r="C222" t="str">
+        <v>53950</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Louverne</v>
+      </c>
+      <c r="E222" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Pharmacie Notre Dame</v>
+      </c>
+      <c r="B223" t="str">
+        <v>5 Place Notre Dame</v>
+      </c>
+      <c r="C223" t="str">
+        <v>76340</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Blangy Sur Bresle</v>
+      </c>
+      <c r="E223" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>Pharmacie Daunou</v>
+      </c>
+      <c r="B224" t="str">
+        <v>12 Boulevard Pierre Daunou</v>
+      </c>
+      <c r="C224" t="str">
+        <v>62200</v>
+      </c>
+      <c r="D224" t="str">
+        <v>BOULOGNE SUR MER</v>
+      </c>
+      <c r="E224" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Pharmacie Ferré</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Za De La Metairie</v>
+      </c>
+      <c r="C225" t="str">
+        <v>85250</v>
+      </c>
+      <c r="D225" t="str">
+        <v>St Fulgent</v>
+      </c>
+      <c r="E225" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Grande Pharmacie De La Rode</v>
+      </c>
+      <c r="B226" t="str">
+        <v>190 Rue Emile Ollivier</v>
+      </c>
+      <c r="C226" t="str">
+        <v>83000</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Toulon</v>
+      </c>
+      <c r="E226" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Pharmacie Du Père Soulas</v>
+      </c>
+      <c r="B227" t="str">
+        <v>1637 avenue du Père Soulas</v>
+      </c>
+      <c r="C227" t="str">
+        <v>34090</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Montpellier</v>
+      </c>
+      <c r="E227" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Pharmacie De La Victoire</v>
+      </c>
+      <c r="B228" t="str">
+        <v>104 Place De La Victoire</v>
+      </c>
+      <c r="C228" t="str">
+        <v>44370</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Loireauxence</v>
+      </c>
+      <c r="E228" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Pharmacie Du Canal</v>
+      </c>
+      <c r="B229" t="str">
+        <v>29 Avenue Andre Bonnet</v>
+      </c>
+      <c r="C229" t="str">
+        <v>82700</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Montech</v>
+      </c>
+      <c r="E229" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Pharmacie Du Patural</v>
+      </c>
+      <c r="B230" t="str">
+        <v>2 Rue Anatole France</v>
+      </c>
+      <c r="C230" t="str">
+        <v>63360</v>
+      </c>
+      <c r="D230" t="str">
+        <v>GERZAT</v>
+      </c>
+      <c r="E230" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Pharmacie Lafayette Chartres</v>
+      </c>
+      <c r="B231" t="str">
+        <v>ROUTE DE PATAY CENTRE COMMERCIAL DES 3 PONTS</v>
+      </c>
+      <c r="C231" t="str">
+        <v>28000</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Chartres</v>
+      </c>
+      <c r="E231" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>La Pharmacie Frechin</v>
+      </c>
+      <c r="B232" t="str">
+        <v>1 Avenue De La Republique</v>
+      </c>
+      <c r="C232" t="str">
+        <v>70200</v>
+      </c>
+      <c r="D232" t="str">
+        <v>LURE</v>
+      </c>
+      <c r="E232" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Pharmacie De La Riviere</v>
+      </c>
+      <c r="B233" t="str">
+        <v>14 Rue Principale</v>
+      </c>
+      <c r="C233" t="str">
+        <v>19520</v>
+      </c>
+      <c r="D233" t="str">
+        <v>MANSAC</v>
+      </c>
+      <c r="E233" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>Pharmacie De L Europe</v>
+      </c>
+      <c r="B234" t="str">
+        <v xml:space="preserve"> 41 AVENUE CHARLES DE GAULLE 15000 AURILLAC</v>
+      </c>
+      <c r="C234" t="str">
+        <v>15000</v>
+      </c>
+      <c r="D234" t="str">
+        <v>AURILLAC</v>
+      </c>
+      <c r="E234" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Pharmacie Nercillac</v>
+      </c>
+      <c r="B235" t="str">
+        <v>274 RTE DE COGNAC</v>
+      </c>
+      <c r="C235" t="str">
+        <v>16200</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Nercillac</v>
+      </c>
+      <c r="E235" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Pharmacie Du Gua</v>
+      </c>
+      <c r="B236" t="str">
+        <v>48 Rue Paul Lafargue</v>
+      </c>
+      <c r="C236" t="str">
+        <v>12110</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Aubin</v>
+      </c>
+      <c r="E236" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Pharmacie Bloch Atelier Santé</v>
+      </c>
+      <c r="B237" t="str">
+        <v>8 Route De Gerardmer</v>
+      </c>
+      <c r="C237" t="str">
+        <v>88600</v>
+      </c>
+      <c r="D237" t="str">
+        <v>BRUYERES</v>
+      </c>
+      <c r="E237" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Pharmacie Les Moissons</v>
+      </c>
+      <c r="B238" t="str">
+        <v>116 Avenue Philippe Bur</v>
+      </c>
+      <c r="C238" t="str">
+        <v>77550</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Moissy Cramayel</v>
+      </c>
+      <c r="E238" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Pharmacie Du Rond Point Jean Mermoz</v>
+      </c>
+      <c r="B239" t="str">
+        <v>3 Avenue Charles De Gaulle</v>
+      </c>
+      <c r="C239" t="str">
+        <v>91220</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Bretigny Sur Orge</v>
+      </c>
+      <c r="E239" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Pharmacie Zelmati</v>
+      </c>
+      <c r="B240" t="str">
+        <v>72 Rue Berthie Albrecht</v>
+      </c>
+      <c r="C240" t="str">
+        <v>95210</v>
+      </c>
+      <c r="D240" t="str">
+        <v>St Gratien</v>
+      </c>
+      <c r="E240" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Pharmacie De La République</v>
+      </c>
+      <c r="B241" t="str">
+        <v>71 Rue De La Republique</v>
+      </c>
+      <c r="C241" t="str">
+        <v>93200</v>
+      </c>
+      <c r="D241" t="str">
+        <v>St Denis</v>
+      </c>
+      <c r="E241" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Pharmacie Huillet</v>
+      </c>
+      <c r="B242" t="str">
+        <v xml:space="preserve">6, route de Banyuls. </v>
+      </c>
+      <c r="C242" t="str">
+        <v>66290</v>
+      </c>
+      <c r="D242" t="str">
+        <v>CERBERE</v>
+      </c>
+      <c r="E242" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Pharmacie Du Square</v>
+      </c>
+      <c r="B243" t="str">
+        <v>2 Rue Emile Fontaine</v>
+      </c>
+      <c r="C243" t="str">
+        <v>91700</v>
+      </c>
+      <c r="D243" t="str">
+        <v>VILLIERS SUR ORGE</v>
+      </c>
+      <c r="E243" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>Pharmacie Fontaine - 62680</v>
+      </c>
+      <c r="B244" t="str">
+        <v>61 Rue Robespierre</v>
+      </c>
+      <c r="C244" t="str">
+        <v>62680</v>
+      </c>
+      <c r="D244" t="str">
+        <v>MERICOURT</v>
+      </c>
+      <c r="E244" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Pharmacie De La Forge</v>
+      </c>
+      <c r="B245" t="str">
+        <v>92 Route De Divonne</v>
+      </c>
+      <c r="C245" t="str">
+        <v>01210</v>
+      </c>
+      <c r="D245" t="str">
+        <v>VERSONNEX</v>
+      </c>
+      <c r="E245" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Pharmacie Maison Neuve Bitton</v>
+      </c>
+      <c r="B246" t="str">
+        <v>La Maison Neuve</v>
+      </c>
+      <c r="C246" t="str">
+        <v>91220</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Bretigny Sur Orge</v>
+      </c>
+      <c r="E246" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Pharmacie Karinthi</v>
+      </c>
+      <c r="B247" t="str">
+        <v>7Bis Avenue Jean Jaures</v>
+      </c>
+      <c r="C247" t="str">
+        <v>63114</v>
+      </c>
+      <c r="D247" t="str">
+        <v>COUDES</v>
+      </c>
+      <c r="E247" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Pharmacie Principale</v>
+      </c>
+      <c r="B248" t="str">
+        <v>56 Rue De La Liberation</v>
+      </c>
+      <c r="C248" t="str">
+        <v>95440</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Ecouen</v>
+      </c>
+      <c r="E248" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Pharmacie De La Barre</v>
+      </c>
+      <c r="B249" t="str">
+        <v>13 RUE MATHIEU</v>
+      </c>
+      <c r="C249" t="str">
+        <v>71000</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Macon</v>
+      </c>
+      <c r="E249" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Pharmacie Centrale</v>
+      </c>
+      <c r="B250" t="str">
+        <v>21 Rue Carnot</v>
+      </c>
+      <c r="C250" t="str">
+        <v>71300</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Montceau Les Mines</v>
+      </c>
+      <c r="E250" t="str">
+        <v>France</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Pharmacie De Bréviandes</v>
+      </c>
+      <c r="B251" t="str">
+        <v>108 Avenue Du Marechal Leclerc</v>
+      </c>
+      <c r="C251" t="str">
+        <v>10450</v>
+      </c>
+      <c r="D251" t="str">
+        <v>BREVIANDES</v>
+      </c>
+      <c r="E251" t="str">
         <v>France</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E251"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/pharma.xlsx
+++ b/pharma.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E216"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,16 +418,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pharmacie De L'abbaye</v>
+        <v>Pharmacie Du Comte Vert</v>
       </c>
       <c r="B2" t="str">
-        <v>66Bis Avenue Jeanne D'Arc</v>
+        <v xml:space="preserve">371 Avenue Du Comte Vert </v>
       </c>
       <c r="C2" t="str">
-        <v>38100</v>
+        <v>73000</v>
       </c>
       <c r="D2" t="str">
-        <v>Grenoble</v>
+        <v>CHAMBERY</v>
       </c>
       <c r="E2" t="str">
         <v>France</v>
@@ -435,16 +435,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Pharmacie De La Gare</v>
+        <v>Grande Pharmacie Des Terreaux</v>
       </c>
       <c r="B3" t="str">
-        <v>74 Avenue Jean Jaures</v>
+        <v xml:space="preserve">511 AV CHARLES DE GAULLE </v>
       </c>
       <c r="C3" t="str">
-        <v>78500</v>
+        <v>01300</v>
       </c>
       <c r="D3" t="str">
-        <v>Sartrouville</v>
+        <v>Belley</v>
       </c>
       <c r="E3" t="str">
         <v>France</v>
@@ -452,16 +452,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Pharmacie De La Gare</v>
+        <v>Pharmacie Calaux</v>
       </c>
       <c r="B4" t="str">
-        <v>11 Avenue Roger Salengro</v>
+        <v xml:space="preserve">Avenue De L'Europe </v>
       </c>
       <c r="C4" t="str">
-        <v>89400</v>
+        <v>18170</v>
       </c>
       <c r="D4" t="str">
-        <v>Migennes</v>
+        <v>Le Chatelet</v>
       </c>
       <c r="E4" t="str">
         <v>France</v>
@@ -469,16 +469,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pharmacie Farines</v>
+        <v>Pharmacie Centrale Grande Synthe</v>
       </c>
       <c r="B5" t="str">
-        <v>6 Avenue Du Mas Deu</v>
+        <v xml:space="preserve">15 PLACE DE L EUROPE </v>
       </c>
       <c r="C5" t="str">
-        <v>66300</v>
+        <v>59760</v>
       </c>
       <c r="D5" t="str">
-        <v>TROUILLAS</v>
+        <v>GRANDE SYNTHE</v>
       </c>
       <c r="E5" t="str">
         <v>France</v>
@@ -486,16 +486,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Pharmacie Duhaut Espace Santé</v>
+        <v>Pharmacie Du Champ De Mars</v>
       </c>
       <c r="B6" t="str">
-        <v>9 R Marechal Lattre De Tassigny</v>
+        <v xml:space="preserve">36 Avenue Victor Hugo </v>
       </c>
       <c r="C6" t="str">
-        <v>88230</v>
+        <v>26000</v>
       </c>
       <c r="D6" t="str">
-        <v>FRAIZE</v>
+        <v>Valence</v>
       </c>
       <c r="E6" t="str">
         <v>France</v>
@@ -503,16 +503,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pharmacie Du Centre</v>
+        <v>Pharmacie Schuman Benoît Jourand</v>
       </c>
       <c r="B7" t="str">
-        <v>29 Rue De Paris</v>
+        <v xml:space="preserve">43-45 Boulevard Robert Schumann </v>
       </c>
       <c r="C7" t="str">
-        <v>78520</v>
+        <v>50100</v>
       </c>
       <c r="D7" t="str">
-        <v>Limay</v>
+        <v>Cherbourg-en-Cotentin</v>
       </c>
       <c r="E7" t="str">
         <v>France</v>
@@ -520,16 +520,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Pharmacie Royale</v>
+        <v>La Grande Pharmacie</v>
       </c>
       <c r="B8" t="str">
-        <v>2Ter Rue Royale</v>
+        <v xml:space="preserve">26 Place Roger Salengro </v>
       </c>
       <c r="C8" t="str">
-        <v>92210</v>
+        <v>62620</v>
       </c>
       <c r="D8" t="str">
-        <v>St Cloud</v>
+        <v>Barlin</v>
       </c>
       <c r="E8" t="str">
         <v>France</v>
@@ -537,16 +537,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Pharmacie De Realpanier</v>
+        <v>Pharmacie Du Grand Pont</v>
       </c>
       <c r="B9" t="str">
-        <v>161 Rue Jean Gasset</v>
+        <v>Place Du Commerce</v>
       </c>
       <c r="C9" t="str">
-        <v>84130</v>
+        <v>42800</v>
       </c>
       <c r="D9" t="str">
-        <v>LE PONTET</v>
+        <v>RIVE DE GIER</v>
       </c>
       <c r="E9" t="str">
         <v>France</v>
@@ -554,16 +554,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Pharmacie Saint Simeon</v>
+        <v>Grande Pharmacie De Beaulieu</v>
       </c>
       <c r="B10" t="str">
-        <v>111 Boulevard De Metzingen</v>
+        <v xml:space="preserve">16 Rue Gaetan Rondeau </v>
       </c>
       <c r="C10" t="str">
-        <v>60400</v>
+        <v>44272</v>
       </c>
       <c r="D10" t="str">
-        <v>Noyon</v>
+        <v>Nantes</v>
       </c>
       <c r="E10" t="str">
         <v>France</v>
@@ -571,16 +571,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Pharmacie Snc L.o Bonichon</v>
+        <v>Pharmacie De Genouillac</v>
       </c>
       <c r="B11" t="str">
-        <v>Av. d'Aquitaine</v>
+        <v xml:space="preserve">3 Grande Rue </v>
       </c>
       <c r="C11" t="str">
-        <v>24490</v>
+        <v>23350</v>
       </c>
       <c r="D11" t="str">
-        <v>La Roche Chalais</v>
+        <v>GENOUILLAC</v>
       </c>
       <c r="E11" t="str">
         <v>France</v>
@@ -588,16 +588,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Pharmacie De La Place Du 14 Juillet</v>
+        <v>Pharmacie Bourret</v>
       </c>
       <c r="B12" t="str">
-        <v>2 Place Du 14 Juillet</v>
+        <v xml:space="preserve">280 Avenue Jean Moulin </v>
       </c>
       <c r="C12" t="str">
-        <v>33130</v>
+        <v>26290</v>
       </c>
       <c r="D12" t="str">
-        <v>BEGLES</v>
+        <v>DONZERE</v>
       </c>
       <c r="E12" t="str">
         <v>France</v>
@@ -605,16 +605,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Pharmacie De La Croix Blanche</v>
+        <v>Pharmacie De La Coupiane</v>
       </c>
       <c r="B13" t="str">
-        <v>41 Avenue Amedee Mercier</v>
+        <v>Mail Jules Muraire</v>
       </c>
       <c r="C13" t="str">
-        <v>01000</v>
+        <v>83160</v>
       </c>
       <c r="D13" t="str">
-        <v>Bourg En Bresse</v>
+        <v>c</v>
       </c>
       <c r="E13" t="str">
         <v>France</v>
@@ -622,16 +622,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Pharmacie De Brienne</v>
+        <v>Pharmacie Du Stade</v>
       </c>
       <c r="B14" t="str">
-        <v>53 Allee De Brienne</v>
+        <v>292 Rue De Verdun</v>
       </c>
       <c r="C14" t="str">
-        <v>31000</v>
+        <v>76600</v>
       </c>
       <c r="D14" t="str">
-        <v>TOULOUSE</v>
+        <v>Le Havre</v>
       </c>
       <c r="E14" t="str">
         <v>France</v>
@@ -639,16 +639,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Pharmacie Du Théâtre</v>
+        <v>Pharmacie Principale De Mareuil</v>
       </c>
       <c r="B15" t="str">
-        <v>18 Ave Pasteur</v>
+        <v xml:space="preserve">Centre Commercial Leclerc - 30 Mail De La Grande Haie </v>
       </c>
       <c r="C15" t="str">
-        <v>10400</v>
+        <v>77100</v>
       </c>
       <c r="D15" t="str">
-        <v>Nogent Sur Seine</v>
+        <v>Mareuil Les Meaux</v>
       </c>
       <c r="E15" t="str">
         <v>France</v>
@@ -656,16 +656,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Pharmacie Laur</v>
+        <v>Pharmacie Des Falaises</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve">16 Rue Des Carmes </v>
+        <v xml:space="preserve">3 Rue Simone Veil </v>
       </c>
       <c r="C16" t="str">
-        <v>24100</v>
+        <v>22470</v>
       </c>
       <c r="D16" t="str">
-        <v>Bergerac</v>
+        <v>Plouezec</v>
       </c>
       <c r="E16" t="str">
         <v>France</v>
@@ -673,16 +673,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Pharmacie Raynaud Puech</v>
+        <v>Pharma 6</v>
       </c>
       <c r="B17" t="str">
-        <v>28 Rue Louis Rouvier</v>
+        <v xml:space="preserve">230 232 Rue De Belfort </v>
       </c>
       <c r="C17" t="str">
-        <v>34420</v>
+        <v>68200</v>
       </c>
       <c r="D17" t="str">
-        <v>VILLENEUVE LES BEZIERS</v>
+        <v>MULHOUSE</v>
       </c>
       <c r="E17" t="str">
         <v>France</v>
@@ -690,16 +690,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Pharmacie Satger Apack</v>
+        <v>Pharmacie Du Belinois</v>
       </c>
       <c r="B18" t="str">
-        <v>Avenue De La Ramadone</v>
+        <v xml:space="preserve">10 Rue Du 8 Mai </v>
       </c>
       <c r="C18" t="str">
-        <v>84870</v>
+        <v>72220</v>
       </c>
       <c r="D18" t="str">
-        <v>LORIOL DU COMTAT</v>
+        <v>Teloche</v>
       </c>
       <c r="E18" t="str">
         <v>France</v>
@@ -707,16 +707,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Grande Pharmacie De Couëron</v>
+        <v>Pharmacie De La Fourche</v>
       </c>
       <c r="B19" t="str">
-        <v>14 Boulevard De La Liberation</v>
+        <v xml:space="preserve">10 Bis Avenue De Saint Ouen </v>
       </c>
       <c r="C19" t="str">
-        <v>44220</v>
+        <v>75018</v>
       </c>
       <c r="D19" t="str">
-        <v>Coueron</v>
+        <v>Paris</v>
       </c>
       <c r="E19" t="str">
         <v>France</v>
@@ -724,16 +724,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Pharmacie du Jasmin</v>
+        <v>Pharmacie De L'etoile</v>
       </c>
       <c r="B20" t="str">
-        <v>59 Rue Haute Saint Paterne</v>
+        <v xml:space="preserve">2 Boulevard De La République, 78410 Aubergenville </v>
       </c>
       <c r="C20" t="str">
-        <v>36100</v>
+        <v>78410</v>
       </c>
       <c r="D20" t="str">
-        <v>Issoudun</v>
+        <v>Aubergenville</v>
       </c>
       <c r="E20" t="str">
         <v>France</v>
@@ -741,16 +741,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Pharmacie Du Village</v>
+        <v>Pharmacie De L Onyx</v>
       </c>
       <c r="B21" t="str">
-        <v>48 Rue De Paris</v>
+        <v xml:space="preserve">111 - 113 Bd Sadi Carnot </v>
       </c>
       <c r="C21" t="str">
-        <v>91090</v>
+        <v>06110</v>
       </c>
       <c r="D21" t="str">
-        <v>Lisses</v>
+        <v>Le Cannet</v>
       </c>
       <c r="E21" t="str">
         <v>France</v>
@@ -758,16 +758,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Pharmacie Lafayette Du Centre</v>
+        <v>Pharmacie Monte Cristo</v>
       </c>
       <c r="B22" t="str">
-        <v>10 Place Du Square</v>
+        <v xml:space="preserve">4 Rue Du General Mangin </v>
       </c>
       <c r="C22" t="str">
-        <v>15000</v>
+        <v>02600</v>
       </c>
       <c r="D22" t="str">
-        <v>AURILLAC</v>
+        <v>Villers cotterêts</v>
       </c>
       <c r="E22" t="str">
         <v>France</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Pharmacie Centrale</v>
+        <v>Pharmacie Des Thermes</v>
       </c>
       <c r="B23" t="str">
-        <v>37 Rue Du General De Gaulle</v>
+        <v xml:space="preserve">RÉSIDENCE DE BOUGAINVILLE 16 AVENUE MARCEL DASSAULT </v>
       </c>
       <c r="C23" t="str">
-        <v>78120</v>
+        <v>17300</v>
       </c>
       <c r="D23" t="str">
-        <v>Rambouillet</v>
+        <v>Rochefort</v>
       </c>
       <c r="E23" t="str">
         <v>France</v>
@@ -792,16 +792,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Pharmacie Des Ors</v>
+        <v>Pharmacie Du Mail</v>
       </c>
       <c r="B24" t="str">
-        <v>Rue De Straubing</v>
+        <v xml:space="preserve">13 Mail Jean De Dunois </v>
       </c>
       <c r="C24" t="str">
-        <v>26100</v>
+        <v>28000</v>
       </c>
       <c r="D24" t="str">
-        <v>ROMANS SUR ISERE</v>
+        <v>Chartres</v>
       </c>
       <c r="E24" t="str">
         <v>France</v>
@@ -809,16 +809,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Pharmacie Des Platanes</v>
+        <v>Pharmacie Saint Fargeau</v>
       </c>
       <c r="B25" t="str">
-        <v>44 bis av Général de Gaulle</v>
+        <v xml:space="preserve">112 Avenue Gambetta </v>
       </c>
       <c r="C25" t="str">
-        <v>26130</v>
+        <v>75020</v>
       </c>
       <c r="D25" t="str">
-        <v>ST PAUL TROIS CHATEAUX</v>
+        <v>Paris</v>
       </c>
       <c r="E25" t="str">
         <v>France</v>
@@ -826,16 +826,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Pharmacie De La Foret</v>
+        <v>Pharmacie Des Cèdres</v>
       </c>
       <c r="B26" t="str">
-        <v>79 Avenue De La Foret</v>
+        <v xml:space="preserve">26 AV DU 18 JUIN </v>
       </c>
       <c r="C26" t="str">
-        <v>36330</v>
+        <v>19100</v>
       </c>
       <c r="D26" t="str">
-        <v>Le Poinconnet</v>
+        <v>BRIVE LA GAILLARDE</v>
       </c>
       <c r="E26" t="str">
         <v>France</v>
@@ -843,16 +843,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Pharmacie Sorbette</v>
+        <v>Pharmacie De L'hôtel De Ville</v>
       </c>
       <c r="B27" t="str">
-        <v>135 Grande Rue Saint Michel</v>
+        <v xml:space="preserve"> 13 Pl. Hôtel de ville </v>
       </c>
       <c r="C27" t="str">
-        <v>31400</v>
+        <v>42000</v>
       </c>
       <c r="D27" t="str">
-        <v>TOULOUSE</v>
+        <v>ST ETIENNE</v>
       </c>
       <c r="E27" t="str">
         <v>France</v>
@@ -860,16 +860,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Pharmacie De St Georges De Reinens</v>
+        <v>Pharmacie Levillain</v>
       </c>
       <c r="B28" t="str">
-        <v>161 Avenue Charles De Gaulle</v>
+        <v>28 Rue De Chalezeule</v>
       </c>
       <c r="C28" t="str">
-        <v>69830</v>
+        <v>25000</v>
       </c>
       <c r="D28" t="str">
-        <v>St Georges De Reneins</v>
+        <v>BESANCON</v>
       </c>
       <c r="E28" t="str">
         <v>France</v>
@@ -877,16 +877,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pharmacie Des Cotes Fleuries</v>
+        <v>Pharmacie Du Castellas</v>
       </c>
       <c r="B29" t="str">
-        <v xml:space="preserve">67 BD MAURICE POURCHON </v>
+        <v xml:space="preserve">27 Avenue De La Liberation </v>
       </c>
       <c r="C29" t="str">
-        <v>63100</v>
+        <v>83136</v>
       </c>
       <c r="D29" t="str">
-        <v>Clermont Ferrand</v>
+        <v>Forcalqueiret</v>
       </c>
       <c r="E29" t="str">
         <v>France</v>
@@ -894,16 +894,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Pharmacie Peilleron</v>
+        <v>Pharmacie Du Pole</v>
       </c>
       <c r="B30" t="str">
-        <v>8 Rue Du Commerce</v>
+        <v xml:space="preserve">7 place de l'Europe  </v>
       </c>
       <c r="C30" t="str">
-        <v>10120</v>
+        <v>53100</v>
       </c>
       <c r="D30" t="str">
-        <v>St Germain</v>
+        <v>Mayenne</v>
       </c>
       <c r="E30" t="str">
         <v>France</v>
@@ -911,16 +911,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Pharmacie De La Croix Blanche</v>
+        <v>Pharmacie Des Gibjoncs</v>
       </c>
       <c r="B31" t="str">
-        <v>41 Avenue Amedee Mercier</v>
+        <v xml:space="preserve">Centre Commercial Cap Nord - Rue Francois Villon </v>
       </c>
       <c r="C31" t="str">
-        <v>01000</v>
+        <v>18000</v>
       </c>
       <c r="D31" t="str">
-        <v>Bourg En Bresse</v>
+        <v>Bourges</v>
       </c>
       <c r="E31" t="str">
         <v>France</v>
@@ -928,16 +928,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Pharmacie Tolosane</v>
+        <v>Pharmacie De L Arche De Noée</v>
       </c>
       <c r="B32" t="str">
-        <v>20 Avenue Tolosane</v>
+        <v xml:space="preserve">749 Route Du Saleve </v>
       </c>
       <c r="C32" t="str">
-        <v>31520</v>
+        <v>74560</v>
       </c>
       <c r="D32" t="str">
-        <v>Ramonville St Agne</v>
+        <v>MONNETIER MORNEX</v>
       </c>
       <c r="E32" t="str">
         <v>France</v>
@@ -945,16 +945,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Pharmacie D Astaffort</v>
+        <v>Pharmacie Du Centre</v>
       </c>
       <c r="B33" t="str">
-        <v>16 Place Andre Routier</v>
+        <v xml:space="preserve">4 Rue du 8 Mai </v>
       </c>
       <c r="C33" t="str">
-        <v>47220</v>
+        <v>93600</v>
       </c>
       <c r="D33" t="str">
-        <v>ASTAFFORT</v>
+        <v>AULNAY SOUS BOIS</v>
       </c>
       <c r="E33" t="str">
         <v>France</v>
@@ -962,16 +962,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Pharmacie Du Clos</v>
+        <v>Pharmacie Mazaudier</v>
       </c>
       <c r="B34" t="str">
-        <v>18 Rue Jules Ferry</v>
+        <v>Avenue Jean Moulin</v>
       </c>
       <c r="C34" t="str">
-        <v>13220</v>
+        <v>48300</v>
       </c>
       <c r="D34" t="str">
-        <v>CHATEAUNEUF LES MARTIGUES</v>
+        <v>LANGOGNE</v>
       </c>
       <c r="E34" t="str">
         <v>France</v>
@@ -979,16 +979,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Pharmacie Du Theatre</v>
+        <v>Pharmacie Du Marché</v>
       </c>
       <c r="B35" t="str">
-        <v>13 Avenue Du General De Gaulle</v>
+        <v xml:space="preserve">7 Place Gaston Bussiere </v>
       </c>
       <c r="C35" t="str">
-        <v>91160</v>
+        <v>93270</v>
       </c>
       <c r="D35" t="str">
-        <v>Longjumeau</v>
+        <v>Sevran</v>
       </c>
       <c r="E35" t="str">
         <v>France</v>
@@ -996,16 +996,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Pharmacie De La Concorde</v>
+        <v>Pharmacie Lexovienne</v>
       </c>
       <c r="B36" t="str">
-        <v>18 Rue Paul Vaillant Couturier</v>
+        <v xml:space="preserve">27 Avenue Du 6 Juin </v>
       </c>
       <c r="C36" t="str">
-        <v>92230</v>
+        <v>14100</v>
       </c>
       <c r="D36" t="str">
-        <v>Gennevilliers</v>
+        <v>LISIEUX</v>
       </c>
       <c r="E36" t="str">
         <v>France</v>
@@ -1013,16 +1013,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Pharmacie Ker'Ys</v>
+        <v>Pharmacie Du Progrès Bezons</v>
       </c>
       <c r="B37" t="str">
-        <v>ZONE D'AMENAGEMENT CONCERTE DE TOUBALAN</v>
+        <v xml:space="preserve">2 Rue Lucien Sampaix </v>
       </c>
       <c r="C37" t="str">
-        <v>29100</v>
+        <v>95870</v>
       </c>
       <c r="D37" t="str">
-        <v>DOUARNENEZ</v>
+        <v>Bezons</v>
       </c>
       <c r="E37" t="str">
         <v>France</v>
@@ -1030,16 +1030,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Pharmacie Le Coënt</v>
+        <v>Pharmacie D'epouville</v>
       </c>
       <c r="B38" t="str">
-        <v xml:space="preserve">Zone De Lan Oge - Route De St Brieuc </v>
+        <v xml:space="preserve">1 Rue Du Commerce </v>
       </c>
       <c r="C38" t="str">
-        <v>22110</v>
+        <v>76133</v>
       </c>
       <c r="D38" t="str">
-        <v>Rostrenen</v>
+        <v>Epouville</v>
       </c>
       <c r="E38" t="str">
         <v>France</v>
@@ -1047,16 +1047,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Grande Pharmacie D'angoulême Anciennement "Pharmacie Des Halles"</v>
+        <v>Pharmacie Danton</v>
       </c>
       <c r="B39" t="str">
-        <v>86 Rue Hergé</v>
+        <v xml:space="preserve">3 Rue Danton </v>
       </c>
       <c r="C39" t="str">
-        <v>16000</v>
+        <v>77330</v>
       </c>
       <c r="D39" t="str">
-        <v>Angoulême</v>
+        <v>Ozoir La Ferriere</v>
       </c>
       <c r="E39" t="str">
         <v>France</v>
@@ -1064,16 +1064,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Pharmacie De La Palle</v>
+        <v>Pharmacie Des Mines</v>
       </c>
       <c r="B40" t="str">
-        <v>37 Boulevard De La Palle</v>
+        <v xml:space="preserve">4 Rue Marie Louise </v>
       </c>
       <c r="C40" t="str">
-        <v>42100</v>
+        <v>68850</v>
       </c>
       <c r="D40" t="str">
-        <v>ST ETIENNE</v>
+        <v>STAFFENFELDEN</v>
       </c>
       <c r="E40" t="str">
         <v>France</v>
@@ -1081,16 +1081,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Pharmacie Du Pont De Tours</v>
+        <v>Grande Pharmacie De Livron</v>
       </c>
       <c r="B41" t="str">
-        <v>42 Rue Charles Beauhaire</v>
+        <v xml:space="preserve">5 Avenue De Provence </v>
       </c>
       <c r="C41" t="str">
-        <v>45140</v>
+        <v>26250</v>
       </c>
       <c r="D41" t="str">
-        <v>Saint-Jean-de-la-Ruelle</v>
+        <v>LIVRON SUR DROME</v>
       </c>
       <c r="E41" t="str">
         <v>France</v>
@@ -1098,16 +1098,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>La Grande Pharmacie Des 3 Graces</v>
+        <v>Pharmacie Du Printemps</v>
       </c>
       <c r="B42" t="str">
-        <v>12 rue de Bourgogne</v>
+        <v xml:space="preserve">348 Avenue De Trevoux </v>
       </c>
       <c r="C42" t="str">
-        <v>42300</v>
+        <v>01000</v>
       </c>
       <c r="D42" t="str">
-        <v>ROANNE</v>
+        <v>Bourg en Bresse</v>
       </c>
       <c r="E42" t="str">
         <v>France</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Pharmacie De La Badiane</v>
+        <v>Pharmacie Siron</v>
       </c>
       <c r="B43" t="str">
-        <v>32 Rue De Kingersheim</v>
+        <v xml:space="preserve">77 Avenue Jean Jaures </v>
       </c>
       <c r="C43" t="str">
-        <v>68120</v>
+        <v>47200</v>
       </c>
       <c r="D43" t="str">
-        <v>Pfastatt</v>
+        <v>MARMANDE</v>
       </c>
       <c r="E43" t="str">
         <v>France</v>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Pharmacie Milliet Sens</v>
+        <v>Pharmacie Sales</v>
       </c>
       <c r="B44" t="str">
-        <v>Place Estelette</v>
+        <v xml:space="preserve">Rue Principale </v>
       </c>
       <c r="C44" t="str">
-        <v>65230</v>
+        <v>12370</v>
       </c>
       <c r="D44" t="str">
-        <v>CASTELNAU MAGNOAC</v>
+        <v>BELMONT SUR RANCE</v>
       </c>
       <c r="E44" t="str">
         <v>France</v>
@@ -1149,16 +1149,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Grande Pharmacie Regionale Kuypers</v>
+        <v>Pharmacie Mederic</v>
       </c>
       <c r="B45" t="str">
-        <v>13 Rue Porte De Sologne</v>
+        <v xml:space="preserve">60 Avenue Mederic </v>
       </c>
       <c r="C45" t="str">
-        <v>45600</v>
+        <v>93160</v>
       </c>
       <c r="D45" t="str">
-        <v>Sully Sur Loire</v>
+        <v>Noisy Le Grand</v>
       </c>
       <c r="E45" t="str">
         <v>France</v>
@@ -1166,16 +1166,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Grande Pharmacie D'angoulême Anciennement "Pharmacie Des Halles"</v>
+        <v>Pharmacie Du Centre</v>
       </c>
       <c r="B46" t="str">
-        <v>86 Rue Hergé</v>
+        <v xml:space="preserve">42 Rue De La Republique </v>
       </c>
       <c r="C46" t="str">
-        <v>16000</v>
+        <v>73200</v>
       </c>
       <c r="D46" t="str">
-        <v>Angoulême</v>
+        <v>Albertville</v>
       </c>
       <c r="E46" t="str">
         <v>France</v>
@@ -1183,16 +1183,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Pharmacie De Saint Montan</v>
+        <v>Pharmacie Cananzi</v>
       </c>
       <c r="B47" t="str">
-        <v>Quartier Bauvache</v>
+        <v xml:space="preserve">121 Rue Marc Delage </v>
       </c>
       <c r="C47" t="str">
-        <v>07220</v>
+        <v>83130</v>
       </c>
       <c r="D47" t="str">
-        <v>ST MONTAN</v>
+        <v>La Garde</v>
       </c>
       <c r="E47" t="str">
         <v>France</v>
@@ -1200,16 +1200,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Pharmacie Anserienne</v>
+        <v>Pharmacie Guillet</v>
       </c>
       <c r="B48" t="str">
-        <v>65 Route Nationale</v>
+        <v xml:space="preserve">47 Boulevard Victor Hugo </v>
       </c>
       <c r="C48" t="str">
-        <v>62215</v>
+        <v>38110</v>
       </c>
       <c r="D48" t="str">
-        <v>OYE PLAGE</v>
+        <v>LA TOUR DU PIN</v>
       </c>
       <c r="E48" t="str">
         <v>France</v>
@@ -1217,16 +1217,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Pharmacie Galgon</v>
+        <v>Pharmacie Thomas</v>
       </c>
       <c r="B49" t="str">
-        <v>1 Avenue Fernand Pillot</v>
+        <v xml:space="preserve">28 B  Av. de la Gare </v>
       </c>
       <c r="C49" t="str">
-        <v>33133</v>
+        <v>63780</v>
       </c>
       <c r="D49" t="str">
-        <v>GALGON</v>
+        <v>ST GEORGES DE MONS</v>
       </c>
       <c r="E49" t="str">
         <v>France</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Pharmacie Du Martroi</v>
+        <v>Pharmacie De L'Isole</v>
       </c>
       <c r="B50" t="str">
-        <v>41 Place Du Martroi</v>
+        <v xml:space="preserve">52 Rue Jean Jaures </v>
       </c>
       <c r="C50" t="str">
-        <v>45300</v>
+        <v>29390</v>
       </c>
       <c r="D50" t="str">
-        <v>Pithiviers</v>
+        <v>SCAER</v>
       </c>
       <c r="E50" t="str">
         <v>France</v>
@@ -1251,16 +1251,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Pharmacie Charles</v>
+        <v>Pharmacie Lafayette De Saint Chamond (De Plaisance)</v>
       </c>
       <c r="B51" t="str">
-        <v>5 Rue Châlons</v>
+        <v xml:space="preserve">14 Rue Gambetta </v>
       </c>
       <c r="C51" t="str">
-        <v>51260</v>
+        <v>42400</v>
       </c>
       <c r="D51" t="str">
-        <v>Anglure</v>
+        <v>ST CHAMOND</v>
       </c>
       <c r="E51" t="str">
         <v>France</v>
@@ -1268,16 +1268,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Pharmacie Rahou</v>
+        <v>Pharmacie Des Etoiles</v>
       </c>
       <c r="B52" t="str">
-        <v>15 Rue De Saint Nazaire</v>
+        <v xml:space="preserve">5 Place Aux Etoiles </v>
       </c>
       <c r="C52" t="str">
-        <v>44800</v>
+        <v>93200</v>
       </c>
       <c r="D52" t="str">
-        <v>St Herblain</v>
+        <v>St Denis</v>
       </c>
       <c r="E52" t="str">
         <v>France</v>
@@ -1285,16 +1285,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Pharmacie Bremont</v>
+        <v>Pharmacie De Saint Jean</v>
       </c>
       <c r="B53" t="str">
-        <v>163 Av. du Général de Gaulle</v>
+        <v xml:space="preserve">Avenue Clement Mille </v>
       </c>
       <c r="C53" t="str">
-        <v>47300</v>
+        <v>13110</v>
       </c>
       <c r="D53" t="str">
-        <v>Villeneuve-sur-Lot</v>
+        <v>PORT DE BOUC</v>
       </c>
       <c r="E53" t="str">
         <v>France</v>
@@ -1302,16 +1302,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Pharmacie De Noyer</v>
+        <v>Pharmacie La Boissiere</v>
       </c>
       <c r="B54" t="str">
-        <v>388 Avenue De Thonon</v>
+        <v xml:space="preserve">145 Boulevard De La Boissiere </v>
       </c>
       <c r="C54" t="str">
-        <v>74200</v>
+        <v>93100</v>
       </c>
       <c r="D54" t="str">
-        <v>ALLINGES</v>
+        <v>Montreuil</v>
       </c>
       <c r="E54" t="str">
         <v>France</v>
@@ -1319,16 +1319,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Pharmacie Dombasle</v>
+        <v>Pharmacie Des M</v>
       </c>
       <c r="B55" t="str">
-        <v>21 Carrefour De La Liberation</v>
+        <v xml:space="preserve">8 Boulevard Du Luxembourg </v>
       </c>
       <c r="C55" t="str">
-        <v>55120</v>
+        <v>50300</v>
       </c>
       <c r="D55" t="str">
-        <v>DOMBASLE EN ARGONNE</v>
+        <v>Avranches</v>
       </c>
       <c r="E55" t="str">
         <v>France</v>
@@ -1336,16 +1336,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pharmacie Cognee</v>
+        <v>Pharmacie Des Trois Clochers</v>
       </c>
       <c r="B56" t="str">
-        <v>3 RUE DU CHALET</v>
+        <v>18 Grande Rue</v>
       </c>
       <c r="C56" t="str">
-        <v>49270</v>
+        <v>22110</v>
       </c>
       <c r="D56" t="str">
-        <v>MONTREVAULT SUR EVRE</v>
+        <v>Glomel</v>
       </c>
       <c r="E56" t="str">
         <v>France</v>
@@ -1353,16 +1353,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Pharmacie Du Marché</v>
+        <v>Pharmacie Place De  La Comedie</v>
       </c>
       <c r="B57" t="str">
-        <v>12 Avenue Carnot</v>
+        <v xml:space="preserve">1, rue de Verdun </v>
       </c>
       <c r="C57" t="str">
-        <v>78800</v>
+        <v>34000</v>
       </c>
       <c r="D57" t="str">
-        <v>Houilles</v>
+        <v>Montpellier</v>
       </c>
       <c r="E57" t="str">
         <v>France</v>
@@ -1370,16 +1370,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pharmacie Michaud Gallo</v>
+        <v>Pharmacie Du Beaujolais Vert</v>
       </c>
       <c r="B58" t="str">
-        <v>79 Route Vieille, Av. Jean Rampon</v>
+        <v xml:space="preserve">90 route de Roanne  </v>
       </c>
       <c r="C58" t="str">
-        <v>30140</v>
+        <v>69240</v>
       </c>
       <c r="D58" t="str">
-        <v>Saint Jean du Pin</v>
+        <v>Thizy Les Bourgs</v>
       </c>
       <c r="E58" t="str">
         <v>France</v>
@@ -1387,16 +1387,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Pharmacie Provence Dauphiné</v>
+        <v>Pharmacie La Courtine</v>
       </c>
       <c r="B59" t="str">
-        <v>Avenue Du Dauphine</v>
+        <v xml:space="preserve">390 Rue Jean Marie Tjibaou </v>
       </c>
       <c r="C59" t="str">
-        <v>26270</v>
+        <v>84000</v>
       </c>
       <c r="D59" t="str">
-        <v>Saulce sur Rhône</v>
+        <v>Avignon</v>
       </c>
       <c r="E59" t="str">
         <v>France</v>
@@ -1404,16 +1404,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Grande Pharmacie Bel Air</v>
+        <v>Pharmacie Des Cigognes</v>
       </c>
       <c r="B60" t="str">
-        <v>Centre Commercial Bel Air</v>
+        <v xml:space="preserve">1 Rue De La Gare </v>
       </c>
       <c r="C60" t="str">
-        <v>78120</v>
+        <v>62490</v>
       </c>
       <c r="D60" t="str">
-        <v>Rambouillet</v>
+        <v>Vitry-en-Artois</v>
       </c>
       <c r="E60" t="str">
         <v>France</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Pharmacie De Paris</v>
+        <v>Grande Pharmacie D'Aulnay</v>
       </c>
       <c r="B61" t="str">
-        <v>111 Avenue Du General De Gaulle</v>
+        <v xml:space="preserve">4 Place Des Etangs </v>
       </c>
       <c r="C61" t="str">
-        <v>44500</v>
+        <v>93600</v>
       </c>
       <c r="D61" t="str">
-        <v>La Baule</v>
+        <v>Aulnay Sous Bois</v>
       </c>
       <c r="E61" t="str">
         <v>France</v>
@@ -1438,16 +1438,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Pharmacie Des Brouzils</v>
+        <v>Pharmacie Du Vernet</v>
       </c>
       <c r="B62" t="str">
-        <v>8 Rue Georges Clemenceau</v>
+        <v xml:space="preserve">72 AV DU GENERAL DE GAULLE  </v>
       </c>
       <c r="C62" t="str">
-        <v>85260</v>
+        <v>18200</v>
       </c>
       <c r="D62" t="str">
-        <v>Les Brouzils</v>
+        <v>St Amand Montrond</v>
       </c>
       <c r="E62" t="str">
         <v>France</v>
@@ -1455,16 +1455,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Pharmacie Charpentier</v>
+        <v>Pharmacie De La Gatine</v>
       </c>
       <c r="B63" t="str">
-        <v>161 Avenue Emile Zola</v>
+        <v xml:space="preserve">10 rue Jean Jaurès </v>
       </c>
       <c r="C63" t="str">
-        <v>79100</v>
+        <v>79200</v>
       </c>
       <c r="D63" t="str">
-        <v>Sainte Verge</v>
+        <v>Parthenay</v>
       </c>
       <c r="E63" t="str">
         <v>France</v>
@@ -1472,16 +1472,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Grande Pharmacie D'angoulême Anciennement "Pharmacie Des Halles"</v>
+        <v>Pharmacie Des Quatre Arbres</v>
       </c>
       <c r="B64" t="str">
-        <v>86 Rue Hergé</v>
+        <v>2 Boulevard Bérnard Gregory</v>
       </c>
       <c r="C64" t="str">
-        <v>16000</v>
+        <v>78990</v>
       </c>
       <c r="D64" t="str">
-        <v>Angoulême</v>
+        <v>Elancourt</v>
       </c>
       <c r="E64" t="str">
         <v>France</v>
@@ -1489,16 +1489,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Pharmacie De Chaillot</v>
+        <v>Pharmacie Des Planes</v>
       </c>
       <c r="B65" t="str">
-        <v>118 Route De Bellon</v>
+        <v>115 Rue Du Village</v>
       </c>
       <c r="C65" t="str">
-        <v>18100</v>
+        <v>01000</v>
       </c>
       <c r="D65" t="str">
-        <v>Vierzon</v>
+        <v>St Denis Les Bourg</v>
       </c>
       <c r="E65" t="str">
         <v>France</v>
@@ -1506,16 +1506,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Pharmacie Thaumiaux</v>
+        <v>Pharmacie Des Eaux Vives</v>
       </c>
       <c r="B66" t="str">
-        <v>3 Avenue De La Gare</v>
+        <v xml:space="preserve">8Bis Avenue Charles De Gaulle </v>
       </c>
       <c r="C66" t="str">
-        <v>23100</v>
+        <v>78230</v>
       </c>
       <c r="D66" t="str">
-        <v xml:space="preserve">La Courtine </v>
+        <v>Le Pecq</v>
       </c>
       <c r="E66" t="str">
         <v>France</v>
@@ -1523,16 +1523,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Pharmacie De St Alban</v>
+        <v>Pharmacie Eraudiere</v>
       </c>
       <c r="B67" t="str">
-        <v>5Bis Promenade Des Magnauds</v>
+        <v>173 Route De Saint Joseph</v>
       </c>
       <c r="C67" t="str">
-        <v>38080</v>
+        <v>44300</v>
       </c>
       <c r="D67" t="str">
-        <v>ST ALBAN DE ROCHE</v>
+        <v>Nantes</v>
       </c>
       <c r="E67" t="str">
         <v>France</v>
@@ -1540,16 +1540,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Pharmacie Roissy 2 F Entre Ciel Et Terre</v>
+        <v>Pharmacie De Lamure</v>
       </c>
       <c r="B68" t="str">
-        <v>Aeroport Charles De Gaulle</v>
+        <v xml:space="preserve">Place De La Mairie </v>
       </c>
       <c r="C68" t="str">
-        <v>95700</v>
+        <v>69870</v>
       </c>
       <c r="D68" t="str">
-        <v>Roissy En France</v>
+        <v>LAMURE SUR AZERGUES</v>
       </c>
       <c r="E68" t="str">
         <v>France</v>
@@ -1557,16 +1557,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Pharmacie Du Plessis</v>
+        <v>Pharmacie Duteil</v>
       </c>
       <c r="B69" t="str">
-        <v>140 Rue Nationale</v>
+        <v>4 Place Du General Leclerc</v>
       </c>
       <c r="C69" t="str">
-        <v>85280</v>
+        <v>76280</v>
       </c>
       <c r="D69" t="str">
-        <v>La Ferriere</v>
+        <v>Criquetot L Esneval</v>
       </c>
       <c r="E69" t="str">
         <v>France</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Pharmacie De Longueil</v>
+        <v>Pharmacie De La Vitarelle</v>
       </c>
       <c r="B70" t="str">
-        <v>33 Avenue Longueil</v>
+        <v>3 Place Georges Abraham</v>
       </c>
       <c r="C70" t="str">
-        <v>78600</v>
+        <v>12300</v>
       </c>
       <c r="D70" t="str">
-        <v>Maisons Laffitte</v>
+        <v>DECAZEVILLE</v>
       </c>
       <c r="E70" t="str">
         <v>France</v>
@@ -1591,16 +1591,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Action Pharma</v>
+        <v>Pharmacie Montredon</v>
       </c>
       <c r="B71" t="str">
-        <v>46 Rue Raymond Laubier</v>
+        <v xml:space="preserve">1 Imp. du Moulin </v>
       </c>
       <c r="C71" t="str">
-        <v>91410</v>
+        <v>11000</v>
       </c>
       <c r="D71" t="str">
-        <v>Dourdan</v>
+        <v xml:space="preserve">Montredon </v>
       </c>
       <c r="E71" t="str">
         <v>France</v>
@@ -1608,16 +1608,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Pharmacie Issenheim</v>
+        <v>Pharmacie Sautel</v>
       </c>
       <c r="B72" t="str">
-        <v>2 RUE DES CERISIERS</v>
+        <v xml:space="preserve">26 Boulevard Andre Sautel </v>
       </c>
       <c r="C72" t="str">
-        <v>68500</v>
+        <v>17000</v>
       </c>
       <c r="D72" t="str">
-        <v>Issenheim</v>
+        <v>LA ROCHELLE</v>
       </c>
       <c r="E72" t="str">
         <v>France</v>
@@ -1625,16 +1625,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Pharmacie Bischoff</v>
+        <v>Pharmacie Du Parvis</v>
       </c>
       <c r="B73" t="str">
-        <v>8 Rue Theodore Deck</v>
+        <v xml:space="preserve">Ccal Les 3 Fontaines </v>
       </c>
       <c r="C73" t="str">
-        <v>68500</v>
+        <v>95000</v>
       </c>
       <c r="D73" t="str">
-        <v>Guebwiller</v>
+        <v>Cergy</v>
       </c>
       <c r="E73" t="str">
         <v>France</v>
@@ -1642,16 +1642,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Pharmacie De La Place</v>
+        <v>Pharmacie Jeanne D'arc</v>
       </c>
       <c r="B74" t="str">
-        <v>Place Hugues Salel</v>
+        <v xml:space="preserve">37 Rue Aristide Briand </v>
       </c>
       <c r="C74" t="str">
-        <v>46250</v>
+        <v>44110</v>
       </c>
       <c r="D74" t="str">
-        <v>CAZALS</v>
+        <v>Châteaubriant</v>
       </c>
       <c r="E74" t="str">
         <v>France</v>
@@ -1659,16 +1659,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">Pharmacie Metro Jacques Cartier </v>
+        <v>Pharmacie Des 2 Églises</v>
       </c>
       <c r="B75" t="str">
-        <v>104 Rue De L Alma</v>
+        <v xml:space="preserve">Route De Bourbourg </v>
       </c>
       <c r="C75" t="str">
-        <v>35000</v>
+        <v>62162</v>
       </c>
       <c r="D75" t="str">
-        <v>RENNES</v>
+        <v>Vieille Eglise</v>
       </c>
       <c r="E75" t="str">
         <v>France</v>
@@ -1676,16 +1676,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Pharmacie Champollion</v>
+        <v>Pharmacie De Saint Germain</v>
       </c>
       <c r="B76" t="str">
-        <v>2 Place Champollion</v>
+        <v>108 Rue Leon Desoyer</v>
       </c>
       <c r="C76" t="str">
-        <v>46100</v>
+        <v>78100</v>
       </c>
       <c r="D76" t="str">
-        <v>FIGEAC</v>
+        <v>St Germain En Laye</v>
       </c>
       <c r="E76" t="str">
         <v>France</v>
@@ -1693,16 +1693,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Pharmacie Delaplace</v>
+        <v>Pharmacie De la Rivière</v>
       </c>
       <c r="B77" t="str">
-        <v>12 Rue Des Ponts</v>
+        <v xml:space="preserve">1 Zone Artisanale La Riviere </v>
       </c>
       <c r="C77" t="str">
-        <v>89120</v>
+        <v>50600</v>
       </c>
       <c r="D77" t="str">
-        <v>Charny</v>
+        <v>PARIGNY</v>
       </c>
       <c r="E77" t="str">
         <v>France</v>
@@ -1710,16 +1710,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Pharmacie De La Verniaz</v>
+        <v>Pharmacie De Saint-fargeau</v>
       </c>
       <c r="B78" t="str">
-        <v>Espace Leman 2</v>
+        <v>9 Place De Tassigny</v>
       </c>
       <c r="C78" t="str">
-        <v>74200</v>
+        <v>89170</v>
       </c>
       <c r="D78" t="str">
-        <v>Anthy Sur Leman</v>
+        <v>St Fargeau</v>
       </c>
       <c r="E78" t="str">
         <v>France</v>
@@ -1727,16 +1727,16 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Pharmacie L'héritier</v>
+        <v>Pharma 78 Pure</v>
       </c>
       <c r="B79" t="str">
-        <v>5 Passage de la Madeleine</v>
+        <v>7 rue Charlie Chaplin</v>
       </c>
       <c r="C79" t="str">
-        <v>81600</v>
+        <v>78390</v>
       </c>
       <c r="D79" t="str">
-        <v>Gaillac</v>
+        <v>Bois d'Arcy</v>
       </c>
       <c r="E79" t="str">
         <v>France</v>
@@ -1744,16 +1744,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Pharmacie De La Gare</v>
+        <v>Pharmacie De Capdenac</v>
       </c>
       <c r="B80" t="str">
-        <v>74 Avenue Jean Jaures</v>
+        <v xml:space="preserve">14 rue de la république </v>
       </c>
       <c r="C80" t="str">
-        <v>78500</v>
+        <v>12700</v>
       </c>
       <c r="D80" t="str">
-        <v>Sartrouville</v>
+        <v>Capdenac Gare</v>
       </c>
       <c r="E80" t="str">
         <v>France</v>
@@ -1761,16 +1761,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Pharmacie Racine</v>
+        <v>Pharmacie De Guemene</v>
       </c>
       <c r="B81" t="str">
-        <v>26 Place Racine</v>
+        <v xml:space="preserve">Rue Jean le Guennec </v>
       </c>
       <c r="C81" t="str">
-        <v>78300</v>
+        <v>56160</v>
       </c>
       <c r="D81" t="str">
-        <v>Poissy</v>
+        <v>Guémené-sur-Scorff</v>
       </c>
       <c r="E81" t="str">
         <v>France</v>
@@ -1778,16 +1778,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Pharmacie Enjolras - Place Fontanges</v>
+        <v>Pharmacie Des Terrasses De L'arche</v>
       </c>
       <c r="B82" t="str">
-        <v>Rue Du 11 Novembre</v>
+        <v>17 Boulevard Des Bouvets</v>
       </c>
       <c r="C82" t="str">
-        <v>12200</v>
+        <v>92000</v>
       </c>
       <c r="D82" t="str">
-        <v>VILLEFRANCHE DE ROUERGUE</v>
+        <v>Nanterre</v>
       </c>
       <c r="E82" t="str">
         <v>France</v>
@@ -1795,16 +1795,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Pharmacie 110</v>
+        <v>Pharmacie Centrale</v>
       </c>
       <c r="B83" t="str">
-        <v>110Bis Avenue D'italie</v>
+        <v xml:space="preserve">37 Rue Des Fusilles </v>
       </c>
       <c r="C83" t="str">
-        <v>75013</v>
+        <v>62420</v>
       </c>
       <c r="D83" t="str">
-        <v>Paris</v>
+        <v>Billy Montigny</v>
       </c>
       <c r="E83" t="str">
         <v>France</v>
@@ -1812,16 +1812,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pharmacie De Gracay</v>
+        <v>Pharmacie Du Cygne</v>
       </c>
       <c r="B84" t="str">
-        <v>Place Jean Chaudron</v>
+        <v>2 Rue Sainte Croix</v>
       </c>
       <c r="C84" t="str">
-        <v>18310</v>
+        <v>57200</v>
       </c>
       <c r="D84" t="str">
-        <v>Gracay</v>
+        <v>SARREGUEMINES</v>
       </c>
       <c r="E84" t="str">
         <v>France</v>
@@ -1829,16 +1829,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pharmacie Clotis</v>
+        <v>Pharmacie Mezerette</v>
       </c>
       <c r="B85" t="str">
-        <v>56 Route Nationale</v>
+        <v>51 RUE DU GENERAL DE GAULLE</v>
       </c>
       <c r="C85" t="str">
-        <v>66202</v>
+        <v>44290</v>
       </c>
       <c r="D85" t="str">
-        <v>ELNE CEDEX</v>
+        <v>GUÉMENÉ-PENFAO</v>
       </c>
       <c r="E85" t="str">
         <v>France</v>
@@ -1846,16 +1846,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Pharmacie Principale de Sevran</v>
+        <v>Pharmacie Des Galeries</v>
       </c>
       <c r="B86" t="str">
-        <v>Av Du Commandant Charcot</v>
+        <v xml:space="preserve">35 RUE JACQUES HUET  </v>
       </c>
       <c r="C86" t="str">
-        <v>93270</v>
+        <v>76400</v>
       </c>
       <c r="D86" t="str">
-        <v>Sevran</v>
+        <v>FECAMP</v>
       </c>
       <c r="E86" t="str">
         <v>France</v>
@@ -1863,16 +1863,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pharmacie Des Lumières - Labi</v>
+        <v>Pharmacie Caramy</v>
       </c>
       <c r="B87" t="str">
-        <v>119 Rue Du Chemin Vert</v>
+        <v>10 Place Carami</v>
       </c>
       <c r="C87" t="str">
-        <v>75011</v>
+        <v>83170</v>
       </c>
       <c r="D87" t="str">
-        <v>Paris</v>
+        <v>Brignoles</v>
       </c>
       <c r="E87" t="str">
         <v>France</v>
@@ -1880,16 +1880,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pharmacie Lamarck</v>
+        <v>Pharmacie Du Parvis</v>
       </c>
       <c r="B88" t="str">
-        <v>2 Place Jacques Froment</v>
+        <v xml:space="preserve">Place Du Parvis Notre Dame </v>
       </c>
       <c r="C88" t="str">
-        <v>75018</v>
+        <v>27400</v>
       </c>
       <c r="D88" t="str">
-        <v>Paris</v>
+        <v>Louviers</v>
       </c>
       <c r="E88" t="str">
         <v>France</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Pharmacie Monistrol</v>
+        <v>Pharmacie Fournier Gentien</v>
       </c>
       <c r="B89" t="str">
-        <v>64 RUE MONISTROL</v>
+        <v xml:space="preserve">21 rue de Danton </v>
       </c>
       <c r="C89" t="str">
-        <v>56100</v>
+        <v>71130</v>
       </c>
       <c r="D89" t="str">
-        <v>Lorient</v>
+        <v>Gueugnon</v>
       </c>
       <c r="E89" t="str">
         <v>France</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Pharmacie Chevalier</v>
+        <v>Pharmacie Viano Joffre</v>
       </c>
       <c r="B90" t="str">
-        <v>45 Rue Du General Leclerc</v>
+        <v xml:space="preserve">12 Place De La Croix De Pierre </v>
       </c>
       <c r="C90" t="str">
-        <v>88500</v>
+        <v>36100</v>
       </c>
       <c r="D90" t="str">
-        <v>MATTAINCOURT</v>
+        <v>Issoudun</v>
       </c>
       <c r="E90" t="str">
         <v>France</v>
@@ -1931,16 +1931,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Pharmacie De Norelan</v>
+        <v>Pharmacie Du Parc</v>
       </c>
       <c r="B91" t="str">
-        <v>68 AV DE PARME</v>
+        <v xml:space="preserve">51 Rue De Paris </v>
       </c>
       <c r="C91" t="str">
-        <v>01000</v>
+        <v>77200</v>
       </c>
       <c r="D91" t="str">
-        <v>BOURG EN BRESSE</v>
+        <v>Torcy</v>
       </c>
       <c r="E91" t="str">
         <v>France</v>
@@ -1948,16 +1948,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Pharmacie Principale Elsie</v>
+        <v>Pharmacie Centrale</v>
       </c>
       <c r="B92" t="str">
-        <v>4 Place Du General De Gaulle</v>
+        <v>12 Promenade Aristide Briand</v>
       </c>
       <c r="C92" t="str">
-        <v>74160</v>
+        <v>21110</v>
       </c>
       <c r="D92" t="str">
-        <v>ST JULIEN EN GENEVOIS</v>
+        <v>GENLIS</v>
       </c>
       <c r="E92" t="str">
         <v>France</v>
@@ -1965,16 +1965,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Pharmacie De Montreux</v>
+        <v>Pharmacie De L'avenue Edouard Michelin</v>
       </c>
       <c r="B93" t="str">
-        <v>8 Rue Saint Denis</v>
+        <v>46Bis Avenue Edouard Michelin</v>
       </c>
       <c r="C93" t="str">
-        <v>72300</v>
+        <v>63100</v>
       </c>
       <c r="D93" t="str">
-        <v>Sable Sur Sarthe</v>
+        <v>Clermont-Ferrand</v>
       </c>
       <c r="E93" t="str">
         <v>France</v>
@@ -1982,16 +1982,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Pharmacie De Molières</v>
+        <v>Pharmacie De Dolomieu</v>
       </c>
       <c r="B94" t="str">
-        <v>10 Avenue des Promenades</v>
+        <v xml:space="preserve">115 Rue Du Navan </v>
       </c>
       <c r="C94" t="str">
-        <v>82220</v>
+        <v>38110</v>
       </c>
       <c r="D94" t="str">
-        <v>Molieres</v>
+        <v>Dolomieu</v>
       </c>
       <c r="E94" t="str">
         <v>France</v>
@@ -1999,16 +1999,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Pharmacie Principale</v>
+        <v>Pharmacie Des Petits Pres</v>
       </c>
       <c r="B95" t="str">
-        <v>36 Avenue Raymond Poincare</v>
+        <v>6 Rue Danton</v>
       </c>
       <c r="C95" t="str">
-        <v>19130</v>
+        <v>78990</v>
       </c>
       <c r="D95" t="str">
-        <v>OBJAT</v>
+        <v>Elancourt</v>
       </c>
       <c r="E95" t="str">
         <v>France</v>
@@ -2016,16 +2016,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Pharmacie De L Avenue</v>
+        <v>Pharmacie Saint Louis</v>
       </c>
       <c r="B96" t="str">
-        <v>40 Avenue De Romans</v>
+        <v xml:space="preserve">11 Rue De Paris </v>
       </c>
       <c r="C96" t="str">
-        <v>38360</v>
+        <v>54440</v>
       </c>
       <c r="D96" t="str">
-        <v>SASSENAGE</v>
+        <v>HERSERANGE</v>
       </c>
       <c r="E96" t="str">
         <v>France</v>
@@ -2033,16 +2033,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Pharmacie Majorelle</v>
+        <v>Pharmacie Saint Jacques</v>
       </c>
       <c r="B97" t="str">
-        <v>287 Route De Vienne</v>
+        <v xml:space="preserve">20 Rue Leon Bourgeois </v>
       </c>
       <c r="C97" t="str">
-        <v>69200</v>
+        <v>51000</v>
       </c>
       <c r="D97" t="str">
-        <v>Venissieux</v>
+        <v>CHALONS EN CHAMPAGNE</v>
       </c>
       <c r="E97" t="str">
         <v>France</v>
@@ -2050,16 +2050,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Pharmacie Roge Cavailles</v>
+        <v>Pharmacie Brunin</v>
       </c>
       <c r="B98" t="str">
-        <v>116 Boulevard Haussmann</v>
+        <v xml:space="preserve">60 voie de lansas </v>
       </c>
       <c r="C98" t="str">
-        <v>75008</v>
+        <v>07170</v>
       </c>
       <c r="D98" t="str">
-        <v>Paris</v>
+        <v>Villeneuve de Berg</v>
       </c>
       <c r="E98" t="str">
         <v>France</v>
@@ -2067,16 +2067,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Pharmacie Pouyes</v>
+        <v>Pharmacie Du Noyer De L Image</v>
       </c>
       <c r="B99" t="str">
-        <v>28 Avenue Du General De Gaulle</v>
+        <v>95 Route D Argenteuil</v>
       </c>
       <c r="C99" t="str">
-        <v>46200</v>
+        <v>95240</v>
       </c>
       <c r="D99" t="str">
-        <v>SOUILLAC</v>
+        <v>Cormeilles En Parisis</v>
       </c>
       <c r="E99" t="str">
         <v>France</v>
@@ -2084,16 +2084,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Pharmacie Elysee Village</v>
+        <v>Pharmacie Bertheaux Pilleux Dreux</v>
       </c>
       <c r="B100" t="str">
-        <v>18 Avenue De La Jonchere</v>
+        <v xml:space="preserve">Rue Des Bas Buissons </v>
       </c>
       <c r="C100" t="str">
-        <v>78170</v>
+        <v>28100</v>
       </c>
       <c r="D100" t="str">
-        <v>La Celle St Cloud</v>
+        <v>DREUX</v>
       </c>
       <c r="E100" t="str">
         <v>France</v>
@@ -2101,16 +2101,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>La Grande Pharmacie De Moulins</v>
+        <v>Pharmacie Du Fief Du Roy</v>
       </c>
       <c r="B101" t="str">
-        <v>25 Place De La Liberte</v>
+        <v>65 Avenue Daniel Hedde</v>
       </c>
       <c r="C101" t="str">
-        <v>03000</v>
+        <v>17200</v>
       </c>
       <c r="D101" t="str">
-        <v>MOULINS</v>
+        <v>ROYAN</v>
       </c>
       <c r="E101" t="str">
         <v>France</v>
@@ -2118,16 +2118,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Pharmacie Dubois</v>
+        <v>Pharmacie De La Sée</v>
       </c>
       <c r="B102" t="str">
-        <v>16 Rue Jean Baptiste Corbel</v>
+        <v xml:space="preserve">10 Rue Des Pèlerins </v>
       </c>
       <c r="C102" t="str">
-        <v>22550</v>
+        <v>50370</v>
       </c>
       <c r="D102" t="str">
-        <v>HENANBIHEN</v>
+        <v>BRECEY</v>
       </c>
       <c r="E102" t="str">
         <v>France</v>
@@ -2135,16 +2135,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Pharmacie De La Boisse</v>
+        <v>La Grande Pharmacie</v>
       </c>
       <c r="B103" t="str">
-        <v>55 Rue de la meule</v>
+        <v xml:space="preserve">Place De La Verrerie </v>
       </c>
       <c r="C103" t="str">
-        <v>01120</v>
+        <v>76100</v>
       </c>
       <c r="D103" t="str">
-        <v>La Boisse</v>
+        <v>ROUEN</v>
       </c>
       <c r="E103" t="str">
         <v>France</v>
@@ -2152,16 +2152,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Pharmacie Iconic</v>
+        <v>Pharmacie Blanc</v>
       </c>
       <c r="B104" t="str">
-        <v>10 AVENUE THIERS</v>
+        <v>16 Pl. Léopold Ollier</v>
       </c>
       <c r="C104" t="str">
-        <v>06000</v>
+        <v>07140</v>
       </c>
       <c r="D104" t="str">
-        <v>NICE</v>
+        <v>Les Vans</v>
       </c>
       <c r="E104" t="str">
         <v>France</v>
@@ -2169,16 +2169,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Pharmacie Pierre De Bar</v>
+        <v>Pharmacie La Jouberte</v>
       </c>
       <c r="B105" t="str">
-        <v>30 bis rue Pierre de Bar</v>
+        <v xml:space="preserve">28, Route De Brignoles </v>
       </c>
       <c r="C105" t="str">
-        <v>54240</v>
+        <v>83143</v>
       </c>
       <c r="D105" t="str">
-        <v>JOEUF</v>
+        <v>Le Val</v>
       </c>
       <c r="E105" t="str">
         <v>France</v>
@@ -2186,16 +2186,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pharmacie De La Tête D'homme</v>
+        <v>Pharmacie Parc De La Noue</v>
       </c>
       <c r="B106" t="str">
-        <v>2 Rue Du Marechal Foch</v>
+        <v xml:space="preserve">Avenue Du Parc De La Noue </v>
       </c>
       <c r="C106" t="str">
-        <v>76260</v>
+        <v>93420</v>
       </c>
       <c r="D106" t="str">
-        <v>Eu</v>
+        <v>VILLEPINTE</v>
       </c>
       <c r="E106" t="str">
         <v>France</v>
@@ -2203,16 +2203,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pharmacie Peda</v>
+        <v>Pharmacie D'allouagne</v>
       </c>
       <c r="B107" t="str">
-        <v>32 Rue Paul Valentin</v>
+        <v xml:space="preserve">23 Rue Du General Leclerc </v>
       </c>
       <c r="C107" t="str">
-        <v>77410</v>
+        <v>62157</v>
       </c>
       <c r="D107" t="str">
-        <v>ANNET SUR MARNE</v>
+        <v>Allouagne</v>
       </c>
       <c r="E107" t="str">
         <v>France</v>
@@ -2220,16 +2220,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Pharmacie Des Acacias</v>
+        <v>Pharmacie Du Faubourg.</v>
       </c>
       <c r="B108" t="str">
-        <v>1 Place Des Acacias</v>
+        <v xml:space="preserve">69 Avenue Fernand Lobbedez </v>
       </c>
       <c r="C108" t="str">
-        <v>85400</v>
+        <v>62000</v>
       </c>
       <c r="D108" t="str">
-        <v>Luçon</v>
+        <v>Arras</v>
       </c>
       <c r="E108" t="str">
         <v>France</v>
@@ -2237,16 +2237,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pharmacie Du Pont Cardinet</v>
+        <v>Pharmacie Delamare</v>
       </c>
       <c r="B109" t="str">
-        <v>1 Rue Jouffroy D'abbans</v>
+        <v xml:space="preserve">2 Rue Guy de Maupassant </v>
       </c>
       <c r="C109" t="str">
-        <v>75017</v>
+        <v>76190</v>
       </c>
       <c r="D109" t="str">
-        <v>Paris</v>
+        <v>Yvetot</v>
       </c>
       <c r="E109" t="str">
         <v>France</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pharmacie Du Wahoo</v>
+        <v>Pharmacie Seignez</v>
       </c>
       <c r="B110" t="str">
-        <v xml:space="preserve"> 40av giraudoux</v>
+        <v xml:space="preserve">54 Route De Tergnier </v>
       </c>
       <c r="C110" t="str">
-        <v>66100</v>
+        <v>02800</v>
       </c>
       <c r="D110" t="str">
-        <v>Perpignan</v>
+        <v>Beautor</v>
       </c>
       <c r="E110" t="str">
         <v>France</v>
@@ -2271,16 +2271,16 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Pharmacie De L'office Du Tourisme</v>
+        <v>Pharmacie Rouxel</v>
       </c>
       <c r="B111" t="str">
-        <v>2 Place Jean Marcellin</v>
+        <v xml:space="preserve">Place Du Docteur Brechoteau </v>
       </c>
       <c r="C111" t="str">
-        <v>05000</v>
+        <v>85220</v>
       </c>
       <c r="D111" t="str">
-        <v>Gap</v>
+        <v>Coex</v>
       </c>
       <c r="E111" t="str">
         <v>France</v>
@@ -2288,16 +2288,16 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Grande Pharmacie De La Mairie</v>
+        <v>Pharmacie Sainte Genevieve</v>
       </c>
       <c r="B112" t="str">
-        <v>101 Avenue Charles De Gaulle</v>
+        <v xml:space="preserve">Route Nationale - C.C Du Château </v>
       </c>
       <c r="C112" t="str">
-        <v>69160</v>
+        <v>60730</v>
       </c>
       <c r="D112" t="str">
-        <v>Tassin La Demi Lune</v>
+        <v>Ste Genevieve</v>
       </c>
       <c r="E112" t="str">
         <v>France</v>
@@ -2305,16 +2305,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Pharmacie Del Monestir</v>
+        <v>Pharmacie 257 Daumesnil</v>
       </c>
       <c r="B113" t="str">
-        <v>16 Avenue Gilbert Brutus</v>
+        <v xml:space="preserve">257 Avenue Daumesnil </v>
       </c>
       <c r="C113" t="str">
-        <v>66240</v>
+        <v>75012</v>
       </c>
       <c r="D113" t="str">
-        <v>ST ESTEVE</v>
+        <v>Paris</v>
       </c>
       <c r="E113" t="str">
         <v>France</v>
@@ -2322,16 +2322,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Pharmacie Du Prepaou</v>
+        <v>Pharmacie Verguet</v>
       </c>
       <c r="B114" t="str">
-        <v>Allee Des Piboules</v>
+        <v>5 Route De La Marche</v>
       </c>
       <c r="C114" t="str">
-        <v>13800</v>
+        <v>23000</v>
       </c>
       <c r="D114" t="str">
-        <v>ISTRES</v>
+        <v>ST SULPICE LE GUERETOIS</v>
       </c>
       <c r="E114" t="str">
         <v>France</v>
@@ -2339,16 +2339,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Pharmacie Fouassier</v>
+        <v>Pharmacie Saint Gery</v>
       </c>
       <c r="B115" t="str">
-        <v>1 Rue Jean Baffier</v>
+        <v>23 Rue Saint-François Xavier, 33170 Gradignan</v>
       </c>
       <c r="C115" t="str">
-        <v>18000</v>
+        <v>33170</v>
       </c>
       <c r="D115" t="str">
-        <v>Bourges</v>
+        <v>Gradignan</v>
       </c>
       <c r="E115" t="str">
         <v>France</v>
@@ -2356,16 +2356,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Pharmacie De La Voie Lactée</v>
+        <v>Pharmacie Hurtado Saint Roch</v>
       </c>
       <c r="B116" t="str">
-        <v>Cc Le Ruisseau - Rue Des Pins</v>
+        <v xml:space="preserve">129 Avenue Saint Roch </v>
       </c>
       <c r="C116" t="str">
-        <v>31700</v>
+        <v>83000</v>
       </c>
       <c r="D116" t="str">
-        <v>Beauzelle</v>
+        <v>Toulon</v>
       </c>
       <c r="E116" t="str">
         <v>France</v>
@@ -2373,16 +2373,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Pharmacie Doree</v>
+        <v>Pharmacie Saint Loubes</v>
       </c>
       <c r="B117" t="str">
-        <v>19 pl République</v>
+        <v>Rond Point De, Rte d'Ambares</v>
       </c>
       <c r="C117" t="str">
-        <v>45200</v>
+        <v xml:space="preserve"> 33450 </v>
       </c>
       <c r="D117" t="str">
-        <v>Montargis</v>
+        <v>Saint-Loubès</v>
       </c>
       <c r="E117" t="str">
         <v>France</v>
@@ -2390,16 +2390,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Pharmacie Centrale</v>
+        <v>Pharmacie Du Plan</v>
       </c>
       <c r="B118" t="str">
-        <v>2 Rue De Huningue</v>
+        <v>1303 Route De Draguignan</v>
       </c>
       <c r="C118" t="str">
-        <v>68300</v>
+        <v>83720</v>
       </c>
       <c r="D118" t="str">
-        <v>ST LOUIS</v>
+        <v>Trans En Provence</v>
       </c>
       <c r="E118" t="str">
         <v>France</v>
@@ -2407,16 +2407,16 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Pharmacie Devez Vidal</v>
+        <v>Pharmacie Du Carteron</v>
       </c>
       <c r="B119" t="str">
-        <v>1 Place Jean Jaures</v>
+        <v xml:space="preserve">30Bis Rue Du Carteron </v>
       </c>
       <c r="C119" t="str">
-        <v>63510</v>
+        <v>49300</v>
       </c>
       <c r="D119" t="str">
-        <v>AULNAT</v>
+        <v>Cholet</v>
       </c>
       <c r="E119" t="str">
         <v>France</v>
@@ -2424,16 +2424,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Pharmacie Landre</v>
+        <v>Pharmacie De Fressanges</v>
       </c>
       <c r="B120" t="str">
-        <v>5 avenue Mar De Lattre de Tassigny</v>
+        <v>1 Avenue Leon Blum</v>
       </c>
       <c r="C120" t="str">
-        <v>79320</v>
+        <v>23000</v>
       </c>
       <c r="D120" t="str">
-        <v>Moncoutant</v>
+        <v>GUERET</v>
       </c>
       <c r="E120" t="str">
         <v>France</v>
@@ -2441,16 +2441,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Pharmacie Gambetta</v>
+        <v>Pharmacie De Saint Priest La Terrasse</v>
       </c>
       <c r="B121" t="str">
-        <v>15 Place Gambetta</v>
+        <v xml:space="preserve">10 Place Massenet </v>
       </c>
       <c r="C121" t="str">
-        <v>36000</v>
+        <v>42270</v>
       </c>
       <c r="D121" t="str">
-        <v>Chateauroux</v>
+        <v>ST PRIEST EN JAREZ</v>
       </c>
       <c r="E121" t="str">
         <v>France</v>
@@ -2458,16 +2458,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Pharmacie De Champagné</v>
+        <v>Pharmacie De La Butte</v>
       </c>
       <c r="B122" t="str">
-        <v xml:space="preserve">14 Quater Rue De La Paix </v>
+        <v xml:space="preserve">177 Avenue Bollee </v>
       </c>
       <c r="C122" t="str">
-        <v>85450</v>
+        <v>72000</v>
       </c>
       <c r="D122" t="str">
-        <v>Champagné Les Marais</v>
+        <v>Le Mans</v>
       </c>
       <c r="E122" t="str">
         <v>France</v>
@@ -2475,16 +2475,16 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Grande Pharmacie De L'Europe</v>
+        <v>Pharmacie Du Marché</v>
       </c>
       <c r="B123" t="str">
-        <v>86 Bd Alexandre De Fraissinette</v>
+        <v xml:space="preserve">79 Rue Du General </v>
       </c>
       <c r="C123" t="str">
-        <v>42100</v>
+        <v>45200</v>
       </c>
       <c r="D123" t="str">
-        <v>ST ETIENNE</v>
+        <v>Montargis</v>
       </c>
       <c r="E123" t="str">
         <v>France</v>
@@ -2492,16 +2492,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">Pharmacie De La Gare </v>
+        <v>Pharmacie Brejassou</v>
       </c>
       <c r="B124" t="str">
-        <v xml:space="preserve">2 RUE DU GENERAL DE GAULLE </v>
+        <v>17 Rue François Mousis</v>
       </c>
       <c r="C124" t="str">
-        <v>44210</v>
+        <v>65000</v>
       </c>
       <c r="D124" t="str">
-        <v>Pornic</v>
+        <v>Tarbes</v>
       </c>
       <c r="E124" t="str">
         <v>France</v>
@@ -2509,16 +2509,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Pharmacie De Martinvast</v>
+        <v>Pharmacie Domange</v>
       </c>
       <c r="B125" t="str">
-        <v>20 Rue Maurice Brisset</v>
+        <v>3 Rue Jean Jaures</v>
       </c>
       <c r="C125" t="str">
-        <v>50690</v>
+        <v>47320</v>
       </c>
       <c r="D125" t="str">
-        <v>Martinvast</v>
+        <v>CLAIRAC</v>
       </c>
       <c r="E125" t="str">
         <v>France</v>
@@ -2526,16 +2526,16 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pharmacie Des Poètes</v>
+        <v>Pharmacie Centrale De Tergnier</v>
       </c>
       <c r="B126" t="str">
-        <v>59 All. Paul Riquet</v>
+        <v xml:space="preserve">11  Boulevard Gambetta </v>
       </c>
       <c r="C126" t="str">
-        <v>34500</v>
+        <v>02700</v>
       </c>
       <c r="D126" t="str">
-        <v>Béziers</v>
+        <v>Tergnier</v>
       </c>
       <c r="E126" t="str">
         <v>France</v>
@@ -2543,16 +2543,16 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Pharmacie Des Cévennes</v>
+        <v>Pharmacie De Colayrac St Cirq</v>
       </c>
       <c r="B127" t="str">
-        <v>47 Rue Balard</v>
+        <v>1006 Avenue De La Liberation</v>
       </c>
       <c r="C127" t="str">
-        <v>75015</v>
+        <v>47450</v>
       </c>
       <c r="D127" t="str">
-        <v>Paris</v>
+        <v>COLAYRAC ST CIRQ</v>
       </c>
       <c r="E127" t="str">
         <v>France</v>
@@ -2560,16 +2560,16 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Pharmacie Centrale Bapaume</v>
+        <v>Pharmacie De La Gravette</v>
       </c>
       <c r="B128" t="str">
-        <v>4 Rue De Peronne</v>
+        <v>6 RUE FRANCOIS MAURIAC</v>
       </c>
       <c r="C128" t="str">
-        <v>62450</v>
+        <v>47200</v>
       </c>
       <c r="D128" t="str">
-        <v>Bapaume</v>
+        <v>MARMANDE</v>
       </c>
       <c r="E128" t="str">
         <v>France</v>
@@ -2577,16 +2577,16 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Pharmacie du Boulevard</v>
+        <v>Pharmacie De La Meurthe</v>
       </c>
       <c r="B129" t="str">
-        <v>147 Ter Boulevard De Strasbourg</v>
+        <v>27 B Avenue Carnot</v>
       </c>
       <c r="C129" t="str">
-        <v>94130</v>
+        <v>54130</v>
       </c>
       <c r="D129" t="str">
-        <v>Nogent Sur Marne</v>
+        <v>ST MAX</v>
       </c>
       <c r="E129" t="str">
         <v>France</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Pharmacie De La Paix</v>
+        <v>Pharmacie Des Gabarres</v>
       </c>
       <c r="B130" t="str">
-        <v>14Bis Rue Leo Lagrange</v>
+        <v xml:space="preserve">15 Place Jean Bureau </v>
       </c>
       <c r="C130" t="str">
-        <v>60100</v>
+        <v>14130</v>
       </c>
       <c r="D130" t="str">
-        <v>Creil</v>
+        <v>Pont L'Eveque</v>
       </c>
       <c r="E130" t="str">
         <v>France</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Pharmacie Du Mondony</v>
+        <v>Pharmacie Orset</v>
       </c>
       <c r="B131" t="str">
-        <v>12 Avenue Du Vallespir</v>
+        <v>625 Avenue Leon Blum</v>
       </c>
       <c r="C131" t="str">
-        <v>66110</v>
+        <v>01500</v>
       </c>
       <c r="D131" t="str">
-        <v>Amelie Les Bains Palalda</v>
+        <v>Amberieu En Bugey</v>
       </c>
       <c r="E131" t="str">
         <v>France</v>
@@ -2628,16 +2628,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Pharmacie Bobo Durand</v>
+        <v>Pharmacie Selarl Du Chateau</v>
       </c>
       <c r="B132" t="str">
-        <v>Avenue Des Alizes</v>
+        <v>1 Pl. Parmentier</v>
       </c>
       <c r="C132" t="str">
-        <v>66140</v>
+        <v>09000</v>
       </c>
       <c r="D132" t="str">
-        <v>Canet En Roussillon</v>
+        <v>Foix</v>
       </c>
       <c r="E132" t="str">
         <v>France</v>
@@ -2645,16 +2645,16 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Pharmacie D'Eymet</v>
+        <v>Pharmacie Vanier</v>
       </c>
       <c r="B133" t="str">
-        <v>45 Boulevard national</v>
+        <v xml:space="preserve">11 rue du commerce </v>
       </c>
       <c r="C133" t="str">
-        <v>24500</v>
+        <v>79160</v>
       </c>
       <c r="D133" t="str">
-        <v>EYMET</v>
+        <v>Coulonges Sur L Autize</v>
       </c>
       <c r="E133" t="str">
         <v>France</v>
@@ -2662,16 +2662,16 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Pharmacie Marty</v>
+        <v>Pharmacie Lou Caleu</v>
       </c>
       <c r="B134" t="str">
-        <v>AVENUE DE MONT-LOUIS</v>
+        <v xml:space="preserve">10 BOULEVARD THEODORE LACOMBE, </v>
       </c>
       <c r="C134" t="str">
-        <v>66210</v>
+        <v>30200</v>
       </c>
       <c r="D134" t="str">
-        <v xml:space="preserve">LES ANGLES </v>
+        <v xml:space="preserve"> BAGNOLS-SUR-CEZE</v>
       </c>
       <c r="E134" t="str">
         <v>France</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Pharmacie La Castellane</v>
+        <v>Pharmacie De La Liberte</v>
       </c>
       <c r="B135" t="str">
-        <v>Place De La Tartane</v>
+        <v>77 Grand Rue</v>
       </c>
       <c r="C135" t="str">
-        <v>13016</v>
+        <v>40190</v>
       </c>
       <c r="D135" t="str">
-        <v>MARSEILLE</v>
+        <v>Villeneuve De Marsan</v>
       </c>
       <c r="E135" t="str">
         <v>France</v>
@@ -2696,16 +2696,16 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Pharmacie Des Trois Chateaux</v>
+        <v>Pharmacie Du Gave</v>
       </c>
       <c r="B136" t="str">
-        <v>8 Place De La Liberation</v>
+        <v>98 Boulevard Charles De Gaulle</v>
       </c>
       <c r="C136" t="str">
-        <v>26130</v>
+        <v>64140</v>
       </c>
       <c r="D136" t="str">
-        <v>ST PAUL TROIS CHATEAUX</v>
+        <v>Lons</v>
       </c>
       <c r="E136" t="str">
         <v>France</v>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pharmacie Du Marcadieu</v>
+        <v>Pharmacie Sefiani</v>
       </c>
       <c r="B137" t="str">
-        <v>9 Place Marcadieu</v>
+        <v xml:space="preserve">19 Rue Marx Dormoy </v>
       </c>
       <c r="C137" t="str">
-        <v>65000</v>
+        <v>75018</v>
       </c>
       <c r="D137" t="str">
-        <v>Tarbes</v>
+        <v>Paris</v>
       </c>
       <c r="E137" t="str">
         <v>France</v>
@@ -2730,16 +2730,16 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Pharmacie De La Mairie Sincholle</v>
+        <v>Pharmacie Du Levant</v>
       </c>
       <c r="B138" t="str">
-        <v xml:space="preserve">PLACE PABLO PICASSO 50 rue Ray Charles </v>
+        <v>70 Route De Doullens</v>
       </c>
       <c r="C138" t="str">
-        <v>34000</v>
+        <v>80100</v>
       </c>
       <c r="D138" t="str">
-        <v>Montpellier</v>
+        <v>Abbeville</v>
       </c>
       <c r="E138" t="str">
         <v>France</v>
@@ -2747,16 +2747,16 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Pharmacie Clémenceau</v>
+        <v>Pharmacie De La Marne</v>
       </c>
       <c r="B139" t="str">
-        <v>10 Rue Georges Clemenceau</v>
+        <v xml:space="preserve">12 Avenue De La Marne </v>
       </c>
       <c r="C139" t="str">
-        <v>78520</v>
+        <v>49300</v>
       </c>
       <c r="D139" t="str">
-        <v>LIMAY</v>
+        <v>Cholet</v>
       </c>
       <c r="E139" t="str">
         <v>France</v>
@@ -2764,16 +2764,16 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Pharmacie Auchan Saint Loup</v>
+        <v>Pharmacie Cioffi</v>
       </c>
       <c r="B140" t="str">
-        <v>57 Boulevard Romain Rolland</v>
+        <v xml:space="preserve">172, Boulevard Gambetta </v>
       </c>
       <c r="C140" t="str">
-        <v>13010</v>
+        <v>02700</v>
       </c>
       <c r="D140" t="str">
-        <v>Marseille</v>
+        <v>Tergnier</v>
       </c>
       <c r="E140" t="str">
         <v>France</v>
@@ -2781,16 +2781,16 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Pharmacie D'exincourt</v>
+        <v>Pharmacie Cornelise</v>
       </c>
       <c r="B141" t="str">
-        <v>19 Rue D Egouttes</v>
+        <v>50 Rue Du General Leclerc</v>
       </c>
       <c r="C141" t="str">
-        <v>25400</v>
+        <v>88190</v>
       </c>
       <c r="D141" t="str">
-        <v>Exincourt</v>
+        <v>GOLBEY</v>
       </c>
       <c r="E141" t="str">
         <v>France</v>
@@ -2798,16 +2798,16 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Pharmacie Rohrbacher</v>
+        <v>Pharmacie Des Capucins</v>
       </c>
       <c r="B142" t="str">
-        <v>12 Rue Du Chene</v>
+        <v>12 Route De Narbonne</v>
       </c>
       <c r="C142" t="str">
-        <v>67470</v>
+        <v>11800</v>
       </c>
       <c r="D142" t="str">
-        <v>MOTHERN</v>
+        <v>TREBES</v>
       </c>
       <c r="E142" t="str">
         <v>France</v>
@@ -2815,16 +2815,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Pharmacie Boulert</v>
+        <v>Pharmacie Malepère</v>
       </c>
       <c r="B143" t="str">
-        <v>109 Boulevard Gabriel Peri</v>
+        <v xml:space="preserve">2 place Nina Simone </v>
       </c>
       <c r="C143" t="str">
-        <v>62210</v>
+        <v>31400</v>
       </c>
       <c r="D143" t="str">
-        <v>Avion</v>
+        <v>Toulouse</v>
       </c>
       <c r="E143" t="str">
         <v>France</v>
@@ -2832,16 +2832,16 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pharmacie Diemeringen</v>
+        <v>Pharmacie Saint Ange</v>
       </c>
       <c r="B144" t="str">
-        <v>51 Grand Rue</v>
+        <v xml:space="preserve">66 Boulevard Du Grau Saint Ange </v>
       </c>
       <c r="C144" t="str">
-        <v>67430</v>
+        <v>66420</v>
       </c>
       <c r="D144" t="str">
-        <v>DIEMERINGEN</v>
+        <v>LE BARCARES</v>
       </c>
       <c r="E144" t="str">
         <v>France</v>
@@ -2849,16 +2849,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pharmacie F. Hairie</v>
+        <v>Pharmacie De Chomerac</v>
       </c>
       <c r="B145" t="str">
-        <v>22 Rue De Domfront</v>
+        <v xml:space="preserve">155 Rue de l'Europe </v>
       </c>
       <c r="C145" t="str">
-        <v>61140</v>
+        <v>07210</v>
       </c>
       <c r="D145" t="str">
-        <v>RIVES D'ANDAINE</v>
+        <v>CHOMERAC</v>
       </c>
       <c r="E145" t="str">
         <v>France</v>
@@ -2866,16 +2866,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pharmacie Du Golf</v>
+        <v>Pharmacie Salaun</v>
       </c>
       <c r="B146" t="str">
-        <v>Avenue De Soissons</v>
+        <v xml:space="preserve">3 Rue Mirabeau </v>
       </c>
       <c r="C146" t="str">
-        <v>02400</v>
+        <v>89140</v>
       </c>
       <c r="D146" t="str">
-        <v>Chateau Thierry</v>
+        <v>Vinneuf</v>
       </c>
       <c r="E146" t="str">
         <v>France</v>
@@ -2883,16 +2883,16 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Pharmacie Haudebourg Libeau</v>
+        <v>Pharmacie De Pujaut</v>
       </c>
       <c r="B147" t="str">
-        <v>8 Gd Pl. Grand Place</v>
+        <v>ROUTE D'AVIGNON</v>
       </c>
       <c r="C147" t="str">
-        <v>85230</v>
+        <v>30131</v>
       </c>
       <c r="D147" t="str">
-        <v>BEAUVOIR SUR MER</v>
+        <v>Pujaut</v>
       </c>
       <c r="E147" t="str">
         <v>France</v>
@@ -2900,16 +2900,16 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Pharmacie Stevenoot Rauwel</v>
+        <v>Pharmacie Du Perrey</v>
       </c>
       <c r="B148" t="str">
-        <v>25 Place Du General De Gaulle</v>
+        <v xml:space="preserve">69 Rue Augustin Normand </v>
       </c>
       <c r="C148" t="str">
-        <v>59470</v>
+        <v>76600</v>
       </c>
       <c r="D148" t="str">
-        <v>WORMHOUT</v>
+        <v>Le Havre</v>
       </c>
       <c r="E148" t="str">
         <v>France</v>
@@ -2917,16 +2917,16 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Pharmacie Jean Mermoz</v>
+        <v>Pharmacie Du Beal Caverni</v>
       </c>
       <c r="B149" t="str">
-        <v>8 Place Andre Latarjet</v>
+        <v>35 Rue Laurent Bertrand</v>
       </c>
       <c r="C149" t="str">
-        <v>69008</v>
+        <v>84320</v>
       </c>
       <c r="D149" t="str">
-        <v>LYON</v>
+        <v>ENTRAIGUES SUR LA SORGUE</v>
       </c>
       <c r="E149" t="str">
         <v>France</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Pharmacie Devriere</v>
+        <v>Pharmacie Xufre</v>
       </c>
       <c r="B150" t="str">
-        <v>21 Rue De Champagne</v>
+        <v xml:space="preserve">46 Pl Du Mal De Lattre De Tassig </v>
       </c>
       <c r="C150" t="str">
-        <v>02100</v>
+        <v>61104</v>
       </c>
       <c r="D150" t="str">
-        <v>LESDINS</v>
+        <v>FLERS CEDEX</v>
       </c>
       <c r="E150" t="str">
         <v>France</v>
@@ -2951,16 +2951,16 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Pharmacie Des 3 Chênes</v>
+        <v>Pharmacie Trouinard</v>
       </c>
       <c r="B151" t="str">
-        <v xml:space="preserve"> 23 PLACE ALPHONSE BERGEROT</v>
+        <v>1 Rue De Champagny</v>
       </c>
       <c r="C151" t="str">
-        <v>59470</v>
+        <v>71120</v>
       </c>
       <c r="D151" t="str">
-        <v>Esquelbecq</v>
+        <v>Charolles</v>
       </c>
       <c r="E151" t="str">
         <v>France</v>
@@ -2968,16 +2968,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Pharmacie Hebrard</v>
+        <v>Pharmacie D'angerville-l'orcher</v>
       </c>
       <c r="B152" t="str">
-        <v>Rue De La Resistance</v>
+        <v>2 Rue De L'If</v>
       </c>
       <c r="C152" t="str">
-        <v>23460</v>
+        <v>76280</v>
       </c>
       <c r="D152" t="str">
-        <v>ROYERE DE VASSIVIERE</v>
+        <v>Angerville L Orcher</v>
       </c>
       <c r="E152" t="str">
         <v>France</v>
@@ -2985,16 +2985,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Pharmacie De L Amandier</v>
+        <v>Pharmacie Des Charmes</v>
       </c>
       <c r="B153" t="str">
-        <v>26 Rue Rudolph Serkin</v>
+        <v xml:space="preserve">324 Rue De La Republique </v>
       </c>
       <c r="C153" t="str">
-        <v>84000</v>
+        <v>60290</v>
       </c>
       <c r="D153" t="str">
-        <v>Avignon</v>
+        <v>Laigneville</v>
       </c>
       <c r="E153" t="str">
         <v>France</v>
@@ -3002,16 +3002,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Pharmacie Du Pelican</v>
+        <v>Pharmacie Du Marché</v>
       </c>
       <c r="B154" t="str">
-        <v>38 Allee De Craponne</v>
+        <v xml:space="preserve">27 Rue Beaurepaire </v>
       </c>
       <c r="C154" t="str">
-        <v>13330</v>
+        <v>77120</v>
       </c>
       <c r="D154" t="str">
-        <v>PELISSANNE</v>
+        <v>Coulommiers</v>
       </c>
       <c r="E154" t="str">
         <v>France</v>
@@ -3019,16 +3019,16 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Pharmacie Laures Raynaud</v>
+        <v>Pharmacie Martinez</v>
       </c>
       <c r="B155" t="str">
-        <v>203 LE SAUT DU LOUP</v>
+        <v>8Bis Avenue De La Montagne Noire</v>
       </c>
       <c r="C155" t="str">
-        <v>30340</v>
+        <v>11600</v>
       </c>
       <c r="D155" t="str">
-        <v>Rousson</v>
+        <v>VILLEGAILHENC</v>
       </c>
       <c r="E155" t="str">
         <v>France</v>
@@ -3036,16 +3036,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pharmacie Renaud Marchand</v>
+        <v>Pharmacie P K 3</v>
       </c>
       <c r="B156" t="str">
-        <v>37 Boulevard Gambetta</v>
+        <v>Géant PK3 La Galerie, Avenue des Sables</v>
       </c>
       <c r="C156" t="str">
-        <v>03320</v>
+        <v>49300</v>
       </c>
       <c r="D156" t="str">
-        <v>LURCY LEVIS</v>
+        <v>Cholet</v>
       </c>
       <c r="E156" t="str">
         <v>France</v>
@@ -3053,16 +3053,16 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Pharmacie Du Grand Parc</v>
+        <v>Pharmacie Des Millets</v>
       </c>
       <c r="B157" t="str">
-        <v>29 Rue Charles De Gaulle</v>
+        <v xml:space="preserve">2 Place de la mairie </v>
       </c>
       <c r="C157" t="str">
-        <v>91070</v>
+        <v>66170</v>
       </c>
       <c r="D157" t="str">
-        <v>Bondoufle</v>
+        <v>Millas</v>
       </c>
       <c r="E157" t="str">
         <v>France</v>
@@ -3070,16 +3070,16 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Pharmacie Du Soleil</v>
+        <v>Pharmacie Des Clochers</v>
       </c>
       <c r="B158" t="str">
-        <v>Cc Leclerc - Zac Du Jonchery</v>
+        <v>35 Avenue De Perpignan</v>
       </c>
       <c r="C158" t="str">
-        <v>54200</v>
+        <v>66300</v>
       </c>
       <c r="D158" t="str">
-        <v>DOMMARTIN LES TOUL</v>
+        <v>PONTEILLA</v>
       </c>
       <c r="E158" t="str">
         <v>France</v>
@@ -3087,16 +3087,16 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pharmacie Du Thaurion</v>
+        <v>Pharmacie De Beaulieu</v>
       </c>
       <c r="B159" t="str">
-        <v>12 Route D Aubusson</v>
+        <v xml:space="preserve">102 Rue Leon Blum </v>
       </c>
       <c r="C159" t="str">
-        <v>23250</v>
+        <v>59150</v>
       </c>
       <c r="D159" t="str">
-        <v>Pontarion</v>
+        <v>Wattrelos</v>
       </c>
       <c r="E159" t="str">
         <v>France</v>
@@ -3104,16 +3104,16 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Pharmacie Du Lycée</v>
+        <v>Pharmacie Des Marronniers</v>
       </c>
       <c r="B160" t="str">
-        <v>106 Boulevard Jean Jaures</v>
+        <v xml:space="preserve">2 Bis Impasse Des Ormes </v>
       </c>
       <c r="C160" t="str">
-        <v>91100</v>
+        <v>78540</v>
       </c>
       <c r="D160" t="str">
-        <v>Corbeil Essonnes</v>
+        <v>Vernouillet</v>
       </c>
       <c r="E160" t="str">
         <v>France</v>
@@ -3121,16 +3121,16 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Pharmacie Sainte Eve</v>
+        <v>Pharmacie Du Clos De Chene</v>
       </c>
       <c r="B161" t="str">
-        <v>33 Boulevard Henri Iv</v>
+        <v xml:space="preserve">Rue du clos Rose </v>
       </c>
       <c r="C161" t="str">
-        <v>28100</v>
+        <v>77144</v>
       </c>
       <c r="D161" t="str">
-        <v>Dreux</v>
+        <v>Montevrain</v>
       </c>
       <c r="E161" t="str">
         <v>France</v>
@@ -3138,16 +3138,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Pharmacie Du Briolet</v>
+        <v>Pharmacie De L'olivier Maubeuge</v>
       </c>
       <c r="B162" t="str">
-        <v>Centre Commercial Lo Moral</v>
+        <v xml:space="preserve">190 Rue De Hautmont </v>
       </c>
       <c r="C162" t="str">
-        <v>11570</v>
+        <v>59600</v>
       </c>
       <c r="D162" t="str">
-        <v>PALAJA</v>
+        <v>Maubeuge</v>
       </c>
       <c r="E162" t="str">
         <v>France</v>
@@ -3155,16 +3155,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Pharmacie Pasteur</v>
+        <v>Grande Pharmacie Du Rond Point</v>
       </c>
       <c r="B163" t="str">
-        <v>143 Avenue Marechal Lyautey</v>
+        <v>33 Boulevard D Alsace Lorraine</v>
       </c>
       <c r="C163" t="str">
-        <v>06000</v>
+        <v>94170</v>
       </c>
       <c r="D163" t="str">
-        <v>Nice</v>
+        <v>Le Perreux Sur Marne</v>
       </c>
       <c r="E163" t="str">
         <v>France</v>
@@ -3172,16 +3172,16 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Pharmacie Des Lissiers</v>
+        <v>Pharmacie Du Centre</v>
       </c>
       <c r="B164" t="str">
-        <v>10 Avenue Des Lissiers</v>
+        <v>3 Place Gambetta</v>
       </c>
       <c r="C164" t="str">
-        <v>23200</v>
+        <v>17390</v>
       </c>
       <c r="D164" t="str">
-        <v>AUBUSSON</v>
+        <v>LA TREMBLADE</v>
       </c>
       <c r="E164" t="str">
         <v>France</v>
@@ -3189,16 +3189,16 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Pharmacie Du Marché</v>
+        <v>Pharmacie Lehmann</v>
       </c>
       <c r="B165" t="str">
-        <v>12 Rue Du Levant</v>
+        <v>30 Cites Des Cannes</v>
       </c>
       <c r="C165" t="str">
-        <v>91860</v>
+        <v>20090</v>
       </c>
       <c r="D165" t="str">
-        <v>EPINAY SOUS SENART</v>
+        <v>Ajaccio</v>
       </c>
       <c r="E165" t="str">
         <v>France</v>
@@ -3206,16 +3206,16 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pharmacie Chazot</v>
+        <v>Pharmacie De La Verzée</v>
       </c>
       <c r="B166" t="str">
-        <v>3 Place Du General Espagne</v>
+        <v>24 Boulevard Du Marechal Foch</v>
       </c>
       <c r="C166" t="str">
-        <v>23200</v>
+        <v>49420</v>
       </c>
       <c r="D166" t="str">
-        <v>Aubusson</v>
+        <v>POUANCE</v>
       </c>
       <c r="E166" t="str">
         <v>France</v>
@@ -3223,16 +3223,16 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pharmacie Principale</v>
+        <v>Pharmacie De Riaillé</v>
       </c>
       <c r="B167" t="str">
-        <v>26 Rue Foch</v>
+        <v>111 Rue De L'Ouche</v>
       </c>
       <c r="C167" t="str">
-        <v>34000</v>
+        <v>44440</v>
       </c>
       <c r="D167" t="str">
-        <v>MONTPELLIER</v>
+        <v>Riaillé</v>
       </c>
       <c r="E167" t="str">
         <v>France</v>
@@ -3240,16 +3240,16 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pharmacie Gambetta</v>
+        <v>Pharmacie Grand Village</v>
       </c>
       <c r="B168" t="str">
-        <v>4 PLACE GAMBETTA</v>
+        <v xml:space="preserve">192 allée des Issards </v>
       </c>
       <c r="C168" t="str">
-        <v>72000</v>
+        <v>30650</v>
       </c>
       <c r="D168" t="str">
-        <v>Le Mans</v>
+        <v>ROCHEFORT DU GARD</v>
       </c>
       <c r="E168" t="str">
         <v>France</v>
@@ -3257,16 +3257,16 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Pharmacie Le Genevois</v>
+        <v>Pharmacie De La Malepere</v>
       </c>
       <c r="B169" t="str">
-        <v>10 Rue Des Glieres</v>
+        <v>Avenue De La Promenade</v>
       </c>
       <c r="C169" t="str">
-        <v>74000</v>
+        <v>11290</v>
       </c>
       <c r="D169" t="str">
-        <v>ANNECY</v>
+        <v>Arzens</v>
       </c>
       <c r="E169" t="str">
         <v>France</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Pharmacie Du Valois</v>
+        <v>Pharmacie Des Alleux</v>
       </c>
       <c r="B170" t="str">
-        <v>56 Avenue Du President Kennedy</v>
+        <v xml:space="preserve">2 rue du Docteur Gorvel </v>
       </c>
       <c r="C170" t="str">
-        <v>60800</v>
+        <v>35140</v>
       </c>
       <c r="D170" t="str">
-        <v>Crepy En Valois</v>
+        <v>Saint-Ouen-Des-Alleux</v>
       </c>
       <c r="E170" t="str">
         <v>France</v>
@@ -3291,16 +3291,16 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Pharmacie La Gantiere</v>
+        <v>Pharmacie Du Tassy</v>
       </c>
       <c r="B171" t="str">
-        <v>Rue Fontaine Du Bac</v>
+        <v xml:space="preserve">Avenue Paul Vaillant Couturier </v>
       </c>
       <c r="C171" t="str">
-        <v>63000</v>
+        <v>13110</v>
       </c>
       <c r="D171" t="str">
-        <v>CLERMONT FERRAND</v>
+        <v>Port De Bouc</v>
       </c>
       <c r="E171" t="str">
         <v>France</v>
@@ -3308,16 +3308,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Pharmacie Anglaise</v>
+        <v>Pharmacie Des Ecoles</v>
       </c>
       <c r="B172" t="str">
-        <v>62 Avenue Des Champs Elysees</v>
+        <v xml:space="preserve">423 Rue Nationale </v>
       </c>
       <c r="C172" t="str">
-        <v>75008</v>
+        <v>62290</v>
       </c>
       <c r="D172" t="str">
-        <v>Paris</v>
+        <v>NOEUX LES MINES</v>
       </c>
       <c r="E172" t="str">
         <v>France</v>
@@ -3325,16 +3325,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Pharmacie Des Muguets</v>
+        <v>Pharmacie Du Parc</v>
       </c>
       <c r="B173" t="str">
-        <v>Rue Des Muguets</v>
+        <v xml:space="preserve">51 Rue De Paris </v>
       </c>
       <c r="C173" t="str">
-        <v>38070</v>
+        <v>77200</v>
       </c>
       <c r="D173" t="str">
-        <v>ST QUENTIN FALLAVIER</v>
+        <v>Torcy</v>
       </c>
       <c r="E173" t="str">
         <v>France</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Pharmacie 3B St Quentin</v>
+        <v>Grande Pharmacie Du Centre Commercial Enval</v>
       </c>
       <c r="B174" t="str">
-        <v>37 39 Rue D Isle</v>
+        <v>Route De Volvic</v>
       </c>
       <c r="C174" t="str">
-        <v>02100</v>
+        <v>63530</v>
       </c>
       <c r="D174" t="str">
-        <v>ST QUENTIN</v>
+        <v>ENVAL</v>
       </c>
       <c r="E174" t="str">
         <v>France</v>
@@ -3359,16 +3359,16 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Pharmacie De Vesone</v>
+        <v>Pharmacie De L'aupiho</v>
       </c>
       <c r="B175" t="str">
-        <v>81 Rue Claude Bernard</v>
+        <v>78 Avenue De La Vallee Des Baux</v>
       </c>
       <c r="C175" t="str">
-        <v>24000</v>
+        <v>13520</v>
       </c>
       <c r="D175" t="str">
-        <v>Perigueux</v>
+        <v>MAUSSANE LES ALPILLES</v>
       </c>
       <c r="E175" t="str">
         <v>France</v>
@@ -3376,16 +3376,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Pharmacie Chatelain</v>
+        <v>Pharmacie Carles Marquet</v>
       </c>
       <c r="B176" t="str">
-        <v>5 Rue Arthur Lamendin</v>
+        <v xml:space="preserve">92 AV VICTOR HUGO </v>
       </c>
       <c r="C176" t="str">
-        <v>59293</v>
+        <v>19000</v>
       </c>
       <c r="D176" t="str">
-        <v>NEUVILLE SUR ESCAUT</v>
+        <v>Tulle</v>
       </c>
       <c r="E176" t="str">
         <v>France</v>
@@ -3393,16 +3393,16 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Pharmacie Du Centre</v>
+        <v>Pharmacie De Jalons</v>
       </c>
       <c r="B177" t="str">
-        <v>10 Rue Fon De L Hospital</v>
+        <v xml:space="preserve">34 Route Nationale </v>
       </c>
       <c r="C177" t="str">
-        <v>34430</v>
+        <v>51150</v>
       </c>
       <c r="D177" t="str">
-        <v>ST JEAN DE VEDAS</v>
+        <v>Jalons</v>
       </c>
       <c r="E177" t="str">
         <v>France</v>
@@ -3410,16 +3410,16 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pharmacie Du Palais Des Sports</v>
+        <v>Pharmacie Doyen Regeon</v>
       </c>
       <c r="B178" t="str">
-        <v>1 Avenue Honore Serres</v>
+        <v>42 Avenue De Picot, 33320 Eysines</v>
       </c>
       <c r="C178" t="str">
-        <v>31000</v>
+        <v>33320</v>
       </c>
       <c r="D178" t="str">
-        <v>TOULOUSE</v>
+        <v>Eysines</v>
       </c>
       <c r="E178" t="str">
         <v>France</v>
@@ -3427,16 +3427,16 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Pharmacie Mariani</v>
+        <v>Grande Pharmacie De L Aa</v>
       </c>
       <c r="B179" t="str">
-        <v>Cc Residence Du Parc - 4 Avenue Anatole France</v>
+        <v xml:space="preserve">33 Rue Roger Salengro </v>
       </c>
       <c r="C179" t="str">
-        <v>94600</v>
+        <v>62575</v>
       </c>
       <c r="D179" t="str">
-        <v>Choisy Le Roi</v>
+        <v>BLENDECQUES</v>
       </c>
       <c r="E179" t="str">
         <v>France</v>
@@ -3444,16 +3444,16 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Pharmacie De Provence</v>
+        <v>Pharmacie Du Couquet</v>
       </c>
       <c r="B180" t="str">
-        <v>92 Avenue De Tarascon</v>
+        <v>Cc Leclerc - Le Couquet</v>
       </c>
       <c r="C180" t="str">
-        <v>84000</v>
+        <v>46100</v>
       </c>
       <c r="D180" t="str">
-        <v>Avignon</v>
+        <v>CAPDENAC</v>
       </c>
       <c r="E180" t="str">
         <v>France</v>
@@ -3461,16 +3461,16 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Pharmacie Du Loing</v>
+        <v>La Pharmacie Du Phenix</v>
       </c>
       <c r="B181" t="str">
-        <v>43 45 Rue Grande</v>
+        <v>43 Rue Du Casino</v>
       </c>
       <c r="C181" t="str">
-        <v>77250</v>
+        <v>57800</v>
       </c>
       <c r="D181" t="str">
-        <v>Moret Sur Loing</v>
+        <v>Freyming-Merlebach</v>
       </c>
       <c r="E181" t="str">
         <v>France</v>
@@ -3478,16 +3478,16 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Pharmacie Auloge</v>
+        <v>Pharmacie De La Moulinelle Mr Brice Genieys</v>
       </c>
       <c r="B182" t="str">
-        <v>1 Avenue Du General De Gaulle</v>
+        <v xml:space="preserve">CENTRE COMMERCIAL ZUP  Rue Jean Bouin </v>
       </c>
       <c r="C182" t="str">
-        <v>57570</v>
+        <v>30300</v>
       </c>
       <c r="D182" t="str">
-        <v>CATTENOM</v>
+        <v>BEAUCAIRE</v>
       </c>
       <c r="E182" t="str">
         <v>France</v>
@@ -3495,16 +3495,16 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Pharmacie Des Ecoles</v>
+        <v>Pharmacie Raspail</v>
       </c>
       <c r="B183" t="str">
-        <v>2 Rue Lucias</v>
+        <v>39 Rue Emile Raspail</v>
       </c>
       <c r="C183" t="str">
-        <v>33240</v>
+        <v>94110</v>
       </c>
       <c r="D183" t="str">
-        <v>St Andre De Cubzac</v>
+        <v>Arcueil</v>
       </c>
       <c r="E183" t="str">
         <v>France</v>
@@ -3512,16 +3512,16 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Pharmacie Du Progrès</v>
+        <v>Pharmacie centrale</v>
       </c>
       <c r="B184" t="str">
-        <v>13 Place du Peuple</v>
+        <v xml:space="preserve">54 Rue De Paris </v>
       </c>
       <c r="C184" t="str">
-        <v>42000</v>
+        <v>94220</v>
       </c>
       <c r="D184" t="str">
-        <v>Saint Etienne</v>
+        <v>CHARENTON LE PONT</v>
       </c>
       <c r="E184" t="str">
         <v>France</v>
@@ -3529,16 +3529,16 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Pharmacie Nature</v>
+        <v>Pharmacie Centrale De Graville</v>
       </c>
       <c r="B185" t="str">
-        <v xml:space="preserve">4 rue de la Papeterie </v>
+        <v xml:space="preserve">175 Rue De Verdun </v>
       </c>
       <c r="C185" t="str">
-        <v>95610</v>
+        <v>76600</v>
       </c>
       <c r="D185" t="str">
-        <v>Eragny Sur Oise</v>
+        <v>Le Havre</v>
       </c>
       <c r="E185" t="str">
         <v>France</v>
@@ -3546,16 +3546,16 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Pharmacie De Brax</v>
+        <v>Pharmacie Du Grand Sud</v>
       </c>
       <c r="B186" t="str">
-        <v>175 A Avenue Des Landes</v>
+        <v>76 Route De Lyon</v>
       </c>
       <c r="C186" t="str">
-        <v>47310</v>
+        <v>71000</v>
       </c>
       <c r="D186" t="str">
-        <v>BRAX</v>
+        <v>Macon</v>
       </c>
       <c r="E186" t="str">
         <v>France</v>
@@ -3563,16 +3563,16 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Pharmacie Du Val De L'erdre</v>
+        <v>Pharmacie De L'aéroport</v>
       </c>
       <c r="B187" t="str">
-        <v>9 Rue d'Anjou</v>
+        <v xml:space="preserve">HALL C, AEROPORT TOULOUSE-BLAGNAC, 31700 BLAGNAC </v>
       </c>
       <c r="C187" t="str">
-        <v>44540</v>
+        <v>31700</v>
       </c>
       <c r="D187" t="str">
-        <v>Vallons-de-L'Erdre</v>
+        <v>Blagnac</v>
       </c>
       <c r="E187" t="str">
         <v>France</v>
@@ -3580,16 +3580,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Pharmacie De Sion</v>
+        <v>Pharmacie Du Clos St Marc</v>
       </c>
       <c r="B188" t="str">
-        <v>Rue Du Marche</v>
+        <v xml:space="preserve">38 Rue Armand Carrel </v>
       </c>
       <c r="C188" t="str">
-        <v>85270</v>
+        <v>76000</v>
       </c>
       <c r="D188" t="str">
-        <v>ST HILAIRE DE RIEZ</v>
+        <v>Rouen</v>
       </c>
       <c r="E188" t="str">
         <v>France</v>
@@ -3597,16 +3597,16 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Pharmacie De Lanveur</v>
+        <v>Pharmacie Du Bourg</v>
       </c>
       <c r="B189" t="str">
-        <v>Rue Alfred Dreyfus Centre Commercial Intermarche De Lanveur</v>
+        <v>Le Bourg</v>
       </c>
       <c r="C189" t="str">
-        <v>56100</v>
+        <v>12600</v>
       </c>
       <c r="D189" t="str">
-        <v>LORIENT</v>
+        <v>THERONDELS</v>
       </c>
       <c r="E189" t="str">
         <v>France</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Pharmacie De La Poste</v>
+        <v>Pharmacie Houlle Libotte</v>
       </c>
       <c r="B190" t="str">
-        <v>67Bis Route Nationale</v>
+        <v>11 Rue De La Houve</v>
       </c>
       <c r="C190" t="str">
-        <v>69330</v>
+        <v>57150</v>
       </c>
       <c r="D190" t="str">
-        <v>Jonage</v>
+        <v>Creutzwald</v>
       </c>
       <c r="E190" t="str">
         <v>France</v>
@@ -3631,16 +3631,16 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Pharmacie De Janval</v>
+        <v>Pharmacie Milcent (Pharmacie De L'océan)</v>
       </c>
       <c r="B191" t="str">
-        <v>32 Rue Léon Rogé</v>
+        <v>25 Rue De L Ocean</v>
       </c>
       <c r="C191" t="str">
-        <v>76200</v>
+        <v>85470</v>
       </c>
       <c r="D191" t="str">
-        <v>DIEPPE</v>
+        <v>BREM SUR MER</v>
       </c>
       <c r="E191" t="str">
         <v>France</v>
@@ -3648,16 +3648,16 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pharmacie De La Poste</v>
+        <v>Grande Pharmacie Catalane</v>
       </c>
       <c r="B192" t="str">
-        <v>14 Avenue De Verdun</v>
+        <v>31 Avenue Du Canigou</v>
       </c>
       <c r="C192" t="str">
-        <v>73100</v>
+        <v>66490</v>
       </c>
       <c r="D192" t="str">
-        <v>Aix Les Bains Cedex</v>
+        <v>ST JEAN PLA DE CORTS</v>
       </c>
       <c r="E192" t="str">
         <v>France</v>
@@ -3665,16 +3665,16 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Pharmacie Paccianus</v>
+        <v>Pharmacie Des Charmes</v>
       </c>
       <c r="B193" t="str">
-        <v>31 Avenue De L Olivier</v>
+        <v>1 Rue Des Frères Lumière</v>
       </c>
       <c r="C193" t="str">
-        <v>66300</v>
+        <v>94510</v>
       </c>
       <c r="D193" t="str">
-        <v>BANYULS DELS ASPRES</v>
+        <v>La Queue En Brie</v>
       </c>
       <c r="E193" t="str">
         <v>France</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Grande Pharmacie Du Rond Point Bourelly</v>
+        <v>Pharmacie De L Hotel De Ville</v>
       </c>
       <c r="B194" t="str">
-        <v>93 Avenue Geoffroy Perret</v>
+        <v>12A Rue Clemenceau</v>
       </c>
       <c r="C194" t="str">
-        <v>30210</v>
+        <v>68700</v>
       </c>
       <c r="D194" t="str">
-        <v>Remoulins</v>
+        <v>CERNAY</v>
       </c>
       <c r="E194" t="str">
         <v>France</v>
@@ -3699,33 +3699,33 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Pharmacie Moreau</v>
+        <v>Pharmacie Des Tortues</v>
       </c>
       <c r="B195" t="str">
-        <v>Place De La Liberation</v>
+        <v xml:space="preserve">82 Rue Tourne Dos </v>
       </c>
       <c r="C195" t="str">
-        <v>23200</v>
+        <v>97660</v>
       </c>
       <c r="D195" t="str">
-        <v>AUBUSSON</v>
+        <v>Bandrélé</v>
       </c>
       <c r="E195" t="str">
-        <v>France</v>
+        <v>Mayotte</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Pharmacie Lacausse</v>
+        <v>Pharmacie De La Hume</v>
       </c>
       <c r="B196" t="str">
-        <v>3 Route De Tercis</v>
+        <v>24 Av Du Mal De Lattre De Tassig</v>
       </c>
       <c r="C196" t="str">
-        <v>40100</v>
+        <v>33470</v>
       </c>
       <c r="D196" t="str">
-        <v>Dax</v>
+        <v>Gujan Mestras</v>
       </c>
       <c r="E196" t="str">
         <v>France</v>
@@ -3733,16 +3733,16 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Pharmacie Du Pont Noir</v>
+        <v>Pharmacie De La Poste</v>
       </c>
       <c r="B197" t="str">
-        <v>2 Rue D Erquelinnes</v>
+        <v>9 Allee Du Commerce</v>
       </c>
       <c r="C197" t="str">
-        <v>59460</v>
+        <v>94000</v>
       </c>
       <c r="D197" t="str">
-        <v>JEUMONT</v>
+        <v>Créteil</v>
       </c>
       <c r="E197" t="str">
         <v>France</v>
@@ -3750,16 +3750,16 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Pharmacie Du Marché</v>
+        <v>Pharmacie Martin Martine</v>
       </c>
       <c r="B198" t="str">
-        <v>35 Avenue andré Maginot</v>
+        <v xml:space="preserve">Cc Elysee - Rue Gauthier </v>
       </c>
       <c r="C198" t="str">
-        <v>01000</v>
+        <v>59400</v>
       </c>
       <c r="D198" t="str">
-        <v>Bourg En Bresse</v>
+        <v>CAMBRAI</v>
       </c>
       <c r="E198" t="str">
         <v>France</v>
@@ -3767,16 +3767,16 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Pharmacie Centrale</v>
+        <v>Pharmacie Maclou</v>
       </c>
       <c r="B199" t="str">
-        <v>19 Boulevard du Portalet</v>
+        <v xml:space="preserve">442 Rue Jules Guesde </v>
       </c>
       <c r="C199" t="str">
-        <v>30500</v>
+        <v>62700</v>
       </c>
       <c r="D199" t="str">
-        <v>St Ambroix</v>
+        <v>Boulogne-Billancourt</v>
       </c>
       <c r="E199" t="str">
         <v>France</v>
@@ -3784,16 +3784,16 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Pharmacie Saint Martin</v>
+        <v>Pharmacie De La Moivre</v>
       </c>
       <c r="B200" t="str">
-        <v>29 Rue Saint Martin</v>
+        <v xml:space="preserve">Centre Commercial Des Crayeres </v>
       </c>
       <c r="C200" t="str">
-        <v>28100</v>
+        <v>51240</v>
       </c>
       <c r="D200" t="str">
-        <v>DREUX</v>
+        <v>Pogny</v>
       </c>
       <c r="E200" t="str">
         <v>France</v>
@@ -3801,16 +3801,16 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Pharmacie Saint Louis</v>
+        <v>Pharmacie Centrale</v>
       </c>
       <c r="B201" t="str">
-        <v xml:space="preserve">236 avenue des martyrs de la résistance  </v>
+        <v xml:space="preserve">127 Route Nationale </v>
       </c>
       <c r="C201" t="str">
-        <v>40000</v>
+        <v>62670</v>
       </c>
       <c r="D201" t="str">
-        <v>Mont De Marsan</v>
+        <v>Mazingarbe</v>
       </c>
       <c r="E201" t="str">
         <v>France</v>
@@ -3818,16 +3818,16 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Pharmacie Agnes Praden</v>
+        <v>Pharmacie De Bessines</v>
       </c>
       <c r="B202" t="str">
-        <v>198 AV DES FRERES LUMIERE</v>
+        <v xml:space="preserve">12 Place De La Liberte </v>
       </c>
       <c r="C202" t="str">
-        <v>30100</v>
+        <v>87250</v>
       </c>
       <c r="D202" t="str">
-        <v>Ales</v>
+        <v>BESSINES SUR GARTEMPE</v>
       </c>
       <c r="E202" t="str">
         <v>France</v>
@@ -3835,16 +3835,16 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Pharmacie Des Aravis</v>
+        <v>Pharmacie De L Omois</v>
       </c>
       <c r="B203" t="str">
-        <v>52 Place Madeleine Lafrance</v>
+        <v xml:space="preserve">62 Rue Carnot </v>
       </c>
       <c r="C203" t="str">
-        <v>74450</v>
+        <v>02400</v>
       </c>
       <c r="D203" t="str">
-        <v>ST JEAN DE SIXT</v>
+        <v>Chateau Thierry</v>
       </c>
       <c r="E203" t="str">
         <v>France</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Pharmacie De La Bernerie</v>
+        <v>Pharmacie Du Riberal</v>
       </c>
       <c r="B204" t="str">
-        <v>21 Rue Du Marechal Foch</v>
+        <v>134 Avenue Jean Jaures</v>
       </c>
       <c r="C204" t="str">
-        <v>44760</v>
+        <v>66170</v>
       </c>
       <c r="D204" t="str">
-        <v>La Bernerie En Retz</v>
+        <v>Millas</v>
       </c>
       <c r="E204" t="str">
         <v>France</v>
@@ -3869,16 +3869,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Pharmacie De Veigy Foncenex</v>
+        <v>Pharmacie De L'eglise</v>
       </c>
       <c r="B205" t="str">
-        <v>453 ROUTE DES VOIRONS</v>
+        <v>132 Avenue Jean Lolive</v>
       </c>
       <c r="C205" t="str">
-        <v>74140</v>
+        <v>93600</v>
       </c>
       <c r="D205" t="str">
-        <v>Veigy Foncenex</v>
+        <v>Pantin</v>
       </c>
       <c r="E205" t="str">
         <v>France</v>
@@ -3886,16 +3886,16 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Nouvelle Pharmacie Centrale</v>
+        <v>Pharmacie Des Alpes</v>
       </c>
       <c r="B206" t="str">
-        <v>22 Rue Du Markstein</v>
+        <v xml:space="preserve">16 Route Des Vallees </v>
       </c>
       <c r="C206" t="str">
-        <v>68270</v>
+        <v>74100</v>
       </c>
       <c r="D206" t="str">
-        <v>WITTENHEIM</v>
+        <v>Annemasse</v>
       </c>
       <c r="E206" t="str">
         <v>France</v>
@@ -3903,16 +3903,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Pharmacie Des Ormeaux</v>
+        <v>Pharmacie Du Flore</v>
       </c>
       <c r="B207" t="str">
-        <v>Boulevard Lucien Dodin</v>
+        <v xml:space="preserve">3 Avenue De La Redoute </v>
       </c>
       <c r="C207" t="str">
-        <v>85300</v>
+        <v>92600</v>
       </c>
       <c r="D207" t="str">
-        <v>CHALLANS</v>
+        <v>Asnières-sur-Seine</v>
       </c>
       <c r="E207" t="str">
         <v>France</v>
@@ -3920,16 +3920,16 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Pharmacie De Merville</v>
+        <v>Pharmacie Cornuel Paladini</v>
       </c>
       <c r="B208" t="str">
-        <v>15 Rue Du 8 Mai 1945</v>
+        <v xml:space="preserve">142 Rue Jean Baptiste Defernez </v>
       </c>
       <c r="C208" t="str">
-        <v>31330</v>
+        <v>62800</v>
       </c>
       <c r="D208" t="str">
-        <v>MERVILLE</v>
+        <v>Lievin</v>
       </c>
       <c r="E208" t="str">
         <v>France</v>
@@ -3937,16 +3937,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Pharmacie Du Village</v>
+        <v>Pharmacie De Bias</v>
       </c>
       <c r="B209" t="str">
-        <v>9 Place De La Republique</v>
+        <v xml:space="preserve">1510 Avenue Serge Dubois </v>
       </c>
       <c r="C209" t="str">
-        <v>69780</v>
+        <v>47300</v>
       </c>
       <c r="D209" t="str">
-        <v>Mions</v>
+        <v>BIAS</v>
       </c>
       <c r="E209" t="str">
         <v>France</v>
@@ -3954,16 +3954,16 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Pharmacie De Bizy</v>
+        <v>Pharmacie De La Garonne</v>
       </c>
       <c r="B210" t="str">
-        <v>Cc Carrefour - 5 Boulevard Isambard</v>
+        <v>1 Avenue De Polignan</v>
       </c>
       <c r="C210" t="str">
-        <v>27200</v>
+        <v>31210</v>
       </c>
       <c r="D210" t="str">
-        <v>Vernon</v>
+        <v>GOURDAN POLIGNAN</v>
       </c>
       <c r="E210" t="str">
         <v>France</v>
@@ -3971,16 +3971,16 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Nouvelle Pharmacie Du Millénaire</v>
+        <v>Pharmacie Pince Vent</v>
       </c>
       <c r="B211" t="str">
-        <v>868 Rue De La Vieille Poste</v>
+        <v xml:space="preserve">49 Mail De Pince Vent </v>
       </c>
       <c r="C211" t="str">
-        <v>34000</v>
+        <v>94430</v>
       </c>
       <c r="D211" t="str">
-        <v>MONTPELLIER</v>
+        <v>Chennevieres Sur Marne</v>
       </c>
       <c r="E211" t="str">
         <v>France</v>
@@ -3988,16 +3988,16 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Pharmacie Lyon Confluence</v>
+        <v>Pharmacie Campart</v>
       </c>
       <c r="B212" t="str">
-        <v>4 Rue Casimir Perier</v>
+        <v>65 67 Rue De La Republique</v>
       </c>
       <c r="C212" t="str">
-        <v>69002</v>
+        <v>27500</v>
       </c>
       <c r="D212" t="str">
-        <v>LYON</v>
+        <v>Pont Audemer</v>
       </c>
       <c r="E212" t="str">
         <v>France</v>
@@ -4005,16 +4005,16 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>M.a Pharmacie</v>
+        <v>Pharmacie Clergue</v>
       </c>
       <c r="B213" t="str">
-        <v>89 Boulevard Georges Brassens</v>
+        <v xml:space="preserve">5 Rue Frederic Mistral </v>
       </c>
       <c r="C213" t="str">
-        <v>12100</v>
+        <v>81000</v>
       </c>
       <c r="D213" t="str">
-        <v>MILLAU</v>
+        <v>Albi</v>
       </c>
       <c r="E213" t="str">
         <v>France</v>
@@ -4022,16 +4022,16 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pharmacie Du Centre</v>
+        <v>Pharmacie De Septeuil</v>
       </c>
       <c r="B214" t="str">
-        <v>4-6 rue de la gare</v>
+        <v>2 Rue George Duhamel</v>
       </c>
       <c r="C214" t="str">
-        <v>91650</v>
+        <v>78790</v>
       </c>
       <c r="D214" t="str">
-        <v>BREUILLET</v>
+        <v>Septeuil</v>
       </c>
       <c r="E214" t="str">
         <v>France</v>
@@ -4039,16 +4039,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Pharmacie Du Vitrail</v>
+        <v>Pharmacie Joue Sur Erdre</v>
       </c>
       <c r="B215" t="str">
-        <v>92 Avenue De La Republique</v>
+        <v xml:space="preserve">137 Rue du Bocage </v>
       </c>
       <c r="C215" t="str">
-        <v>69160</v>
+        <v>44440</v>
       </c>
       <c r="D215" t="str">
-        <v>Tassin La Demi Lune</v>
+        <v>Joué-sur-Erdre</v>
       </c>
       <c r="E215" t="str">
         <v>France</v>
@@ -4056,619 +4056,24 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Pharmacie Des Clouteries</v>
+        <v>Pharmacie Du Pas Du Loup</v>
       </c>
       <c r="B216" t="str">
-        <v>12 Place Victor Hugo</v>
+        <v>31 Chemin Des Oliviers</v>
       </c>
       <c r="C216" t="str">
-        <v>62500</v>
+        <v>83500</v>
       </c>
       <c r="D216" t="str">
-        <v>Saint omer</v>
+        <v>LA SEYNE SUR MER</v>
       </c>
       <c r="E216" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Pharmacie Huyghe</v>
-      </c>
-      <c r="B217" t="str">
-        <v>24 Rue Roger Salengro</v>
-      </c>
-      <c r="C217" t="str">
-        <v>59171</v>
-      </c>
-      <c r="D217" t="str">
-        <v>HELESMES</v>
-      </c>
-      <c r="E217" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Pharmacie Des Chaillots</v>
-      </c>
-      <c r="B218" t="str">
-        <v>2 rue Henry Dunant</v>
-      </c>
-      <c r="C218" t="str">
-        <v>89100</v>
-      </c>
-      <c r="D218" t="str">
-        <v>Sens</v>
-      </c>
-      <c r="E218" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>Pharmacie De Genis</v>
-      </c>
-      <c r="B219" t="str">
-        <v>Grand Place</v>
-      </c>
-      <c r="C219" t="str">
-        <v>24160</v>
-      </c>
-      <c r="D219" t="str">
-        <v>GENIS</v>
-      </c>
-      <c r="E219" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Pharmacie Sauder</v>
-      </c>
-      <c r="B220" t="str">
-        <v>9 Rue Des Canaris</v>
-      </c>
-      <c r="C220" t="str">
-        <v>57150</v>
-      </c>
-      <c r="D220" t="str">
-        <v>CREUTZWALD</v>
-      </c>
-      <c r="E220" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Pharmacie Boissy 2</v>
-      </c>
-      <c r="B221" t="str">
-        <v>Centre Commercial Boissy 2</v>
-      </c>
-      <c r="C221" t="str">
-        <v>94470</v>
-      </c>
-      <c r="D221" t="str">
-        <v>Boissy St Leger</v>
-      </c>
-      <c r="E221" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>Pharmacie Des Alizes</v>
-      </c>
-      <c r="B222" t="str">
-        <v>Place Saint Martin</v>
-      </c>
-      <c r="C222" t="str">
-        <v>53950</v>
-      </c>
-      <c r="D222" t="str">
-        <v>Louverne</v>
-      </c>
-      <c r="E222" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>Pharmacie Notre Dame</v>
-      </c>
-      <c r="B223" t="str">
-        <v>5 Place Notre Dame</v>
-      </c>
-      <c r="C223" t="str">
-        <v>76340</v>
-      </c>
-      <c r="D223" t="str">
-        <v>Blangy Sur Bresle</v>
-      </c>
-      <c r="E223" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>Pharmacie Daunou</v>
-      </c>
-      <c r="B224" t="str">
-        <v>12 Boulevard Pierre Daunou</v>
-      </c>
-      <c r="C224" t="str">
-        <v>62200</v>
-      </c>
-      <c r="D224" t="str">
-        <v>BOULOGNE SUR MER</v>
-      </c>
-      <c r="E224" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>Pharmacie Ferré</v>
-      </c>
-      <c r="B225" t="str">
-        <v>Za De La Metairie</v>
-      </c>
-      <c r="C225" t="str">
-        <v>85250</v>
-      </c>
-      <c r="D225" t="str">
-        <v>St Fulgent</v>
-      </c>
-      <c r="E225" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>Grande Pharmacie De La Rode</v>
-      </c>
-      <c r="B226" t="str">
-        <v>190 Rue Emile Ollivier</v>
-      </c>
-      <c r="C226" t="str">
-        <v>83000</v>
-      </c>
-      <c r="D226" t="str">
-        <v>Toulon</v>
-      </c>
-      <c r="E226" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>Pharmacie Du Père Soulas</v>
-      </c>
-      <c r="B227" t="str">
-        <v>1637 avenue du Père Soulas</v>
-      </c>
-      <c r="C227" t="str">
-        <v>34090</v>
-      </c>
-      <c r="D227" t="str">
-        <v>Montpellier</v>
-      </c>
-      <c r="E227" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>Pharmacie De La Victoire</v>
-      </c>
-      <c r="B228" t="str">
-        <v>104 Place De La Victoire</v>
-      </c>
-      <c r="C228" t="str">
-        <v>44370</v>
-      </c>
-      <c r="D228" t="str">
-        <v>Loireauxence</v>
-      </c>
-      <c r="E228" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>Pharmacie Du Canal</v>
-      </c>
-      <c r="B229" t="str">
-        <v>29 Avenue Andre Bonnet</v>
-      </c>
-      <c r="C229" t="str">
-        <v>82700</v>
-      </c>
-      <c r="D229" t="str">
-        <v>Montech</v>
-      </c>
-      <c r="E229" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
-        <v>Pharmacie Du Patural</v>
-      </c>
-      <c r="B230" t="str">
-        <v>2 Rue Anatole France</v>
-      </c>
-      <c r="C230" t="str">
-        <v>63360</v>
-      </c>
-      <c r="D230" t="str">
-        <v>GERZAT</v>
-      </c>
-      <c r="E230" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v>Pharmacie Lafayette Chartres</v>
-      </c>
-      <c r="B231" t="str">
-        <v>ROUTE DE PATAY CENTRE COMMERCIAL DES 3 PONTS</v>
-      </c>
-      <c r="C231" t="str">
-        <v>28000</v>
-      </c>
-      <c r="D231" t="str">
-        <v>Chartres</v>
-      </c>
-      <c r="E231" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="str">
-        <v>La Pharmacie Frechin</v>
-      </c>
-      <c r="B232" t="str">
-        <v>1 Avenue De La Republique</v>
-      </c>
-      <c r="C232" t="str">
-        <v>70200</v>
-      </c>
-      <c r="D232" t="str">
-        <v>LURE</v>
-      </c>
-      <c r="E232" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="str">
-        <v>Pharmacie De La Riviere</v>
-      </c>
-      <c r="B233" t="str">
-        <v>14 Rue Principale</v>
-      </c>
-      <c r="C233" t="str">
-        <v>19520</v>
-      </c>
-      <c r="D233" t="str">
-        <v>MANSAC</v>
-      </c>
-      <c r="E233" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="str">
-        <v>Pharmacie De L Europe</v>
-      </c>
-      <c r="B234" t="str">
-        <v xml:space="preserve"> 41 AVENUE CHARLES DE GAULLE 15000 AURILLAC</v>
-      </c>
-      <c r="C234" t="str">
-        <v>15000</v>
-      </c>
-      <c r="D234" t="str">
-        <v>AURILLAC</v>
-      </c>
-      <c r="E234" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="str">
-        <v>Pharmacie Nercillac</v>
-      </c>
-      <c r="B235" t="str">
-        <v>274 RTE DE COGNAC</v>
-      </c>
-      <c r="C235" t="str">
-        <v>16200</v>
-      </c>
-      <c r="D235" t="str">
-        <v>Nercillac</v>
-      </c>
-      <c r="E235" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="str">
-        <v>Pharmacie Du Gua</v>
-      </c>
-      <c r="B236" t="str">
-        <v>48 Rue Paul Lafargue</v>
-      </c>
-      <c r="C236" t="str">
-        <v>12110</v>
-      </c>
-      <c r="D236" t="str">
-        <v>Aubin</v>
-      </c>
-      <c r="E236" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="str">
-        <v>Pharmacie Bloch Atelier Santé</v>
-      </c>
-      <c r="B237" t="str">
-        <v>8 Route De Gerardmer</v>
-      </c>
-      <c r="C237" t="str">
-        <v>88600</v>
-      </c>
-      <c r="D237" t="str">
-        <v>BRUYERES</v>
-      </c>
-      <c r="E237" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="str">
-        <v>Pharmacie Les Moissons</v>
-      </c>
-      <c r="B238" t="str">
-        <v>116 Avenue Philippe Bur</v>
-      </c>
-      <c r="C238" t="str">
-        <v>77550</v>
-      </c>
-      <c r="D238" t="str">
-        <v>Moissy Cramayel</v>
-      </c>
-      <c r="E238" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>Pharmacie Du Rond Point Jean Mermoz</v>
-      </c>
-      <c r="B239" t="str">
-        <v>3 Avenue Charles De Gaulle</v>
-      </c>
-      <c r="C239" t="str">
-        <v>91220</v>
-      </c>
-      <c r="D239" t="str">
-        <v>Bretigny Sur Orge</v>
-      </c>
-      <c r="E239" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>Pharmacie Zelmati</v>
-      </c>
-      <c r="B240" t="str">
-        <v>72 Rue Berthie Albrecht</v>
-      </c>
-      <c r="C240" t="str">
-        <v>95210</v>
-      </c>
-      <c r="D240" t="str">
-        <v>St Gratien</v>
-      </c>
-      <c r="E240" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>Pharmacie De La République</v>
-      </c>
-      <c r="B241" t="str">
-        <v>71 Rue De La Republique</v>
-      </c>
-      <c r="C241" t="str">
-        <v>93200</v>
-      </c>
-      <c r="D241" t="str">
-        <v>St Denis</v>
-      </c>
-      <c r="E241" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>Pharmacie Huillet</v>
-      </c>
-      <c r="B242" t="str">
-        <v xml:space="preserve">6, route de Banyuls. </v>
-      </c>
-      <c r="C242" t="str">
-        <v>66290</v>
-      </c>
-      <c r="D242" t="str">
-        <v>CERBERE</v>
-      </c>
-      <c r="E242" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>Pharmacie Du Square</v>
-      </c>
-      <c r="B243" t="str">
-        <v>2 Rue Emile Fontaine</v>
-      </c>
-      <c r="C243" t="str">
-        <v>91700</v>
-      </c>
-      <c r="D243" t="str">
-        <v>VILLIERS SUR ORGE</v>
-      </c>
-      <c r="E243" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>Pharmacie Fontaine - 62680</v>
-      </c>
-      <c r="B244" t="str">
-        <v>61 Rue Robespierre</v>
-      </c>
-      <c r="C244" t="str">
-        <v>62680</v>
-      </c>
-      <c r="D244" t="str">
-        <v>MERICOURT</v>
-      </c>
-      <c r="E244" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>Pharmacie De La Forge</v>
-      </c>
-      <c r="B245" t="str">
-        <v>92 Route De Divonne</v>
-      </c>
-      <c r="C245" t="str">
-        <v>01210</v>
-      </c>
-      <c r="D245" t="str">
-        <v>VERSONNEX</v>
-      </c>
-      <c r="E245" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>Pharmacie Maison Neuve Bitton</v>
-      </c>
-      <c r="B246" t="str">
-        <v>La Maison Neuve</v>
-      </c>
-      <c r="C246" t="str">
-        <v>91220</v>
-      </c>
-      <c r="D246" t="str">
-        <v>Bretigny Sur Orge</v>
-      </c>
-      <c r="E246" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>Pharmacie Karinthi</v>
-      </c>
-      <c r="B247" t="str">
-        <v>7Bis Avenue Jean Jaures</v>
-      </c>
-      <c r="C247" t="str">
-        <v>63114</v>
-      </c>
-      <c r="D247" t="str">
-        <v>COUDES</v>
-      </c>
-      <c r="E247" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>Pharmacie Principale</v>
-      </c>
-      <c r="B248" t="str">
-        <v>56 Rue De La Liberation</v>
-      </c>
-      <c r="C248" t="str">
-        <v>95440</v>
-      </c>
-      <c r="D248" t="str">
-        <v>Ecouen</v>
-      </c>
-      <c r="E248" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>Pharmacie De La Barre</v>
-      </c>
-      <c r="B249" t="str">
-        <v>13 RUE MATHIEU</v>
-      </c>
-      <c r="C249" t="str">
-        <v>71000</v>
-      </c>
-      <c r="D249" t="str">
-        <v>Macon</v>
-      </c>
-      <c r="E249" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>Pharmacie Centrale</v>
-      </c>
-      <c r="B250" t="str">
-        <v>21 Rue Carnot</v>
-      </c>
-      <c r="C250" t="str">
-        <v>71300</v>
-      </c>
-      <c r="D250" t="str">
-        <v>Montceau Les Mines</v>
-      </c>
-      <c r="E250" t="str">
-        <v>France</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>Pharmacie De Bréviandes</v>
-      </c>
-      <c r="B251" t="str">
-        <v>108 Avenue Du Marechal Leclerc</v>
-      </c>
-      <c r="C251" t="str">
-        <v>10450</v>
-      </c>
-      <c r="D251" t="str">
-        <v>BREVIANDES</v>
-      </c>
-      <c r="E251" t="str">
         <v>France</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E251"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E216"/>
   </ignoredErrors>
 </worksheet>
 </file>